--- a/InputData/fuels/BFPIaE/BAU Fuel Production Imports and Exports.xlsx
+++ b/InputData/fuels/BFPIaE/BAU Fuel Production Imports and Exports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\fuels\BFPIaE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E271E7-F6D5-4F4B-AE2D-D6D56F059F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63778DD6-A89E-4B7D-B222-2AB20C24250D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="780" windowWidth="30660" windowHeight="21360" activeTab="7" xr2:uid="{95292E05-0ED3-EF4F-AC15-7BB76D2FFA5A}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" firstSheet="3" activeTab="5" xr2:uid="{95292E05-0ED3-EF4F-AC15-7BB76D2FFA5A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -866,7 +866,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1051,6 +1054,13 @@
       <color rgb="FF0D0D0D"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1579,10 +1589,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="225">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2057,50 +2068,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2108,71 +2125,23 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2186,47 +2155,91 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2560,12 +2573,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD86332E-167D-7340-B188-63BED1427BF8}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="107.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>183</v>
       </c>
@@ -2573,7 +2586,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="38" t="s">
         <v>185</v>
       </c>
@@ -2581,72 +2594,72 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="38" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="51">
+    <row r="15" spans="1:2" ht="48" x14ac:dyDescent="0.4">
       <c r="B15" s="167" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="34">
+    <row r="17" spans="2:2" ht="32" x14ac:dyDescent="0.4">
       <c r="B17" s="166" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="68">
+    <row r="19" spans="2:2" ht="64" x14ac:dyDescent="0.4">
       <c r="B19" s="166" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="51">
+    <row r="20" spans="2:2" ht="48" x14ac:dyDescent="0.4">
       <c r="B20" s="166" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="68">
+    <row r="21" spans="2:2" ht="64" x14ac:dyDescent="0.4">
       <c r="B21" s="166" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="102">
+    <row r="23" spans="2:2" ht="96" x14ac:dyDescent="0.4">
       <c r="B23" s="166" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="136">
+    <row r="25" spans="2:2" ht="128" x14ac:dyDescent="0.4">
       <c r="B25" s="166" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="68">
+    <row r="27" spans="2:2" ht="64" x14ac:dyDescent="0.4">
       <c r="B27" s="166" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="51">
+    <row r="29" spans="2:2" ht="48" x14ac:dyDescent="0.4">
       <c r="B29" s="166" t="s">
         <v>198</v>
       </c>
@@ -2659,13 +2672,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3E92DD-F61D-F349-B35B-C54F2CBA4034}">
   <dimension ref="A1:AH159"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="26" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>35</v>
       </c>
@@ -2673,13 +2686,13 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="25" customHeight="1" thickBot="1">
+    <row r="3" spans="1:25" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="5"/>
-      <c r="B3" s="168"/>
-      <c r="C3" s="169" t="s">
+      <c r="B3" s="221"/>
+      <c r="C3" s="222" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="168"/>
+      <c r="D3" s="221"/>
       <c r="E3" s="5"/>
       <c r="F3" s="10"/>
       <c r="H3" s="26" t="s">
@@ -2709,26 +2722,26 @@
       <c r="Q3" t="s">
         <v>38</v>
       </c>
-      <c r="T3" s="170" t="s">
+      <c r="T3" s="223" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="170"/>
-      <c r="V3" s="171" t="s">
+      <c r="U3" s="223"/>
+      <c r="V3" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="W3" s="172"/>
-      <c r="X3" s="177" t="s">
+      <c r="W3" s="190"/>
+      <c r="X3" s="189" t="s">
         <v>38</v>
       </c>
-      <c r="Y3" s="171"/>
+      <c r="Y3" s="214"/>
     </row>
-    <row r="4" spans="1:25" ht="18" thickTop="1" thickBot="1">
+    <row r="4" spans="1:25" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="168"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="168"/>
+      <c r="B4" s="221"/>
+      <c r="C4" s="222"/>
+      <c r="D4" s="221"/>
       <c r="E4" s="8" t="s">
         <v>24</v>
       </c>
@@ -2747,14 +2760,14 @@
       <c r="K4" s="33">
         <v>55230</v>
       </c>
-      <c r="T4" s="170"/>
-      <c r="U4" s="170"/>
-      <c r="V4" s="173"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="178"/>
-      <c r="Y4" s="173"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="206"/>
+      <c r="W4" s="188"/>
+      <c r="X4" s="187"/>
+      <c r="Y4" s="206"/>
     </row>
-    <row r="5" spans="1:25" ht="24" customHeight="1" thickBot="1">
+    <row r="5" spans="1:25" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="8" t="s">
         <v>26</v>
@@ -2791,16 +2804,16 @@
       <c r="U5" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="V5" s="175" t="s">
+      <c r="V5" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="W5" s="176"/>
-      <c r="X5" s="179" t="s">
+      <c r="W5" s="211"/>
+      <c r="X5" s="210" t="s">
         <v>44</v>
       </c>
-      <c r="Y5" s="175"/>
+      <c r="Y5" s="169"/>
     </row>
-    <row r="6" spans="1:25" ht="18" thickTop="1" thickBot="1">
+    <row r="6" spans="1:25" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="14"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -2856,7 +2869,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="17" customHeight="1" thickBot="1">
+    <row r="7" spans="1:25" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="17">
         <v>2000</v>
       </c>
@@ -2924,7 +2937,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="17" thickBot="1">
+    <row r="8" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="17">
         <v>2001</v>
       </c>
@@ -2992,7 +3005,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="17" thickBot="1">
+    <row r="9" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17">
         <v>2002</v>
       </c>
@@ -3060,7 +3073,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="17" thickBot="1">
+    <row r="10" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17">
         <v>2003</v>
       </c>
@@ -3128,7 +3141,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="17" thickBot="1">
+    <row r="11" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="17">
         <v>2004</v>
       </c>
@@ -3196,7 +3209,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="17" thickBot="1">
+    <row r="12" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="17">
         <v>2005</v>
       </c>
@@ -3264,7 +3277,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="17" thickBot="1">
+    <row r="13" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="17">
         <v>2006</v>
       </c>
@@ -3332,7 +3345,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="17" thickBot="1">
+    <row r="14" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="17">
         <v>2007</v>
       </c>
@@ -3400,7 +3413,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="17" thickBot="1">
+    <row r="15" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="17">
         <v>2008</v>
       </c>
@@ -3456,7 +3469,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="17" thickBot="1">
+    <row r="16" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="17">
         <v>2009</v>
       </c>
@@ -3512,7 +3525,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17" thickBot="1">
+    <row r="17" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="17">
         <v>2010</v>
       </c>
@@ -3550,7 +3563,7 @@
         <v>879.5</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="17">
         <v>2011</v>
       </c>
@@ -3570,12 +3583,12 @@
         <v>42449.21</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="38" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
         <v>54</v>
       </c>
@@ -3598,16 +3611,16 @@
         <v>57</v>
       </c>
       <c r="H24" s="46"/>
-      <c r="I24" s="171" t="s">
+      <c r="I24" s="214" t="s">
         <v>37</v>
       </c>
-      <c r="J24" s="171"/>
-      <c r="K24" s="172"/>
+      <c r="J24" s="214"/>
+      <c r="K24" s="190"/>
       <c r="L24" s="58"/>
-      <c r="M24" s="178"/>
-      <c r="N24" s="173"/>
+      <c r="M24" s="187"/>
+      <c r="N24" s="206"/>
     </row>
-    <row r="25" spans="1:18" ht="17" thickBot="1">
+    <row r="25" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
         <v>2000</v>
       </c>
@@ -3630,14 +3643,14 @@
         <v>834472</v>
       </c>
       <c r="H25" s="46"/>
-      <c r="I25" s="181"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="182"/>
+      <c r="I25" s="215"/>
+      <c r="J25" s="215"/>
+      <c r="K25" s="216"/>
       <c r="L25" s="58"/>
-      <c r="M25" s="178"/>
-      <c r="N25" s="173"/>
+      <c r="M25" s="187"/>
+      <c r="N25" s="206"/>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>2001</v>
       </c>
@@ -3668,12 +3681,12 @@
       <c r="L26" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="196" t="s">
+      <c r="M26" s="202" t="s">
         <v>60</v>
       </c>
-      <c r="N26" s="197"/>
+      <c r="N26" s="217"/>
     </row>
-    <row r="27" spans="1:18" ht="17" thickBot="1">
+    <row r="27" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>2002</v>
       </c>
@@ -3707,9 +3720,9 @@
       </c>
       <c r="L27" s="66"/>
       <c r="M27" s="191"/>
-      <c r="N27" s="198"/>
+      <c r="N27" s="209"/>
     </row>
-    <row r="28" spans="1:18" ht="18" thickTop="1" thickBot="1">
+    <row r="28" spans="1:18" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>2003</v>
       </c>
@@ -3753,7 +3766,7 @@
         <v>3761086</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17" thickBot="1">
+    <row r="29" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>2004</v>
       </c>
@@ -3797,7 +3810,7 @@
         <v>4347465</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17" thickBot="1">
+    <row r="30" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>2005</v>
       </c>
@@ -3841,7 +3854,7 @@
         <v>5030547</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17" thickBot="1">
+    <row r="31" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
         <v>2006</v>
       </c>
@@ -3885,7 +3898,7 @@
         <v>5607430</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17" thickBot="1">
+    <row r="32" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
         <v>2007</v>
       </c>
@@ -3929,7 +3942,7 @@
         <v>6093138</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="17" thickBot="1">
+    <row r="33" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
         <v>2008</v>
       </c>
@@ -3973,7 +3986,7 @@
         <v>6376990</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="17" thickBot="1">
+    <row r="34" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
         <v>2009</v>
       </c>
@@ -4017,7 +4030,7 @@
         <v>6642633</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="17" thickBot="1">
+    <row r="35" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
         <v>2010</v>
       </c>
@@ -4061,7 +4074,7 @@
         <v>7190871</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="17" thickBot="1">
+    <row r="36" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
         <v>2011</v>
       </c>
@@ -4105,7 +4118,7 @@
         <v>7562893</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="17" thickBot="1">
+    <row r="37" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H37" s="70">
         <v>2019</v>
       </c>
@@ -4128,7 +4141,7 @@
         <v>7765541</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="17" thickBot="1">
+    <row r="38" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H38" s="79">
         <v>2020</v>
       </c>
@@ -4151,17 +4164,17 @@
         <v>8020514</v>
       </c>
     </row>
-    <row r="41" spans="1:33">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A41" s="38" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:33">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A42" s="38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="26">
+    <row r="43" spans="1:33" ht="20" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -4206,12 +4219,12 @@
       </c>
       <c r="R43" s="58"/>
       <c r="S43" s="58"/>
-      <c r="T43" s="178"/>
-      <c r="U43" s="174"/>
+      <c r="T43" s="187"/>
+      <c r="U43" s="188"/>
       <c r="V43" s="58"/>
       <c r="W43" s="58"/>
-      <c r="X43" s="178"/>
-      <c r="Y43" s="174"/>
+      <c r="X43" s="187"/>
+      <c r="Y43" s="188"/>
       <c r="Z43" s="58"/>
       <c r="AA43" s="65" t="s">
         <v>89</v>
@@ -4222,7 +4235,7 @@
       </c>
       <c r="AD43" s="46"/>
     </row>
-    <row r="44" spans="1:33" ht="26">
+    <row r="44" spans="1:33" ht="20" x14ac:dyDescent="0.4">
       <c r="A44" s="3">
         <v>2000</v>
       </c>
@@ -4274,20 +4287,20 @@
       <c r="S44" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="T44" s="185" t="s">
+      <c r="T44" s="204" t="s">
         <v>87</v>
       </c>
-      <c r="U44" s="186"/>
+      <c r="U44" s="205"/>
       <c r="V44" s="65" t="s">
         <v>72</v>
       </c>
       <c r="W44" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="X44" s="189" t="s">
+      <c r="X44" s="212" t="s">
         <v>67</v>
       </c>
-      <c r="Y44" s="190"/>
+      <c r="Y44" s="213"/>
       <c r="Z44" s="81" t="s">
         <v>68</v>
       </c>
@@ -4304,7 +4317,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="17" thickBot="1">
+    <row r="45" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
         <v>2001</v>
       </c>
@@ -4352,11 +4365,11 @@
       </c>
       <c r="R45" s="66"/>
       <c r="S45" s="66"/>
-      <c r="T45" s="187">
+      <c r="T45" s="219">
         <f>+ JP5</f>
         <v>0</v>
       </c>
-      <c r="U45" s="188"/>
+      <c r="U45" s="220"/>
       <c r="V45" s="66"/>
       <c r="W45" s="66"/>
       <c r="X45" s="191"/>
@@ -4378,7 +4391,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="18" thickTop="1" thickBot="1">
+    <row r="46" spans="1:33" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
         <v>2002</v>
       </c>
@@ -4442,7 +4455,7 @@
       <c r="W46" s="51">
         <v>107351</v>
       </c>
-      <c r="X46" s="193"/>
+      <c r="X46" s="170"/>
       <c r="Y46" s="31">
         <v>1377</v>
       </c>
@@ -4474,7 +4487,7 @@
         <v>108728</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="17" thickBot="1">
+    <row r="47" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
         <v>2003</v>
       </c>
@@ -4538,7 +4551,7 @@
       <c r="W47" s="87">
         <v>119568</v>
       </c>
-      <c r="X47" s="194"/>
+      <c r="X47" s="171"/>
       <c r="Y47" s="31">
         <v>1352</v>
       </c>
@@ -4570,7 +4583,7 @@
         <v>120920</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="17" thickBot="1">
+    <row r="48" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
         <v>2004</v>
       </c>
@@ -4634,7 +4647,7 @@
       <c r="W48" s="51">
         <v>122099</v>
       </c>
-      <c r="X48" s="194"/>
+      <c r="X48" s="171"/>
       <c r="Y48" s="31">
         <v>1139</v>
       </c>
@@ -4666,7 +4679,7 @@
         <v>123238</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="17" thickBot="1">
+    <row r="49" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
         <v>2005</v>
       </c>
@@ -4730,7 +4743,7 @@
       <c r="W49" s="51">
         <v>122907</v>
       </c>
-      <c r="X49" s="194"/>
+      <c r="X49" s="171"/>
       <c r="Y49" s="84">
         <v>927</v>
       </c>
@@ -4762,7 +4775,7 @@
         <v>123834</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="17" thickBot="1">
+    <row r="50" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
         <v>2006</v>
       </c>
@@ -4826,7 +4839,7 @@
       <c r="W50" s="51">
         <v>129502</v>
       </c>
-      <c r="X50" s="194"/>
+      <c r="X50" s="171"/>
       <c r="Y50" s="31">
         <v>1107</v>
       </c>
@@ -4858,7 +4871,7 @@
         <v>130609</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="17" thickBot="1">
+    <row r="51" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
         <v>2007</v>
       </c>
@@ -4922,7 +4935,7 @@
       <c r="W51" s="87">
         <v>129306</v>
       </c>
-      <c r="X51" s="194"/>
+      <c r="X51" s="171"/>
       <c r="Y51" s="84">
         <v>972</v>
       </c>
@@ -4954,7 +4967,7 @@
         <v>130278</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="17" thickBot="1">
+    <row r="52" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
         <v>2008</v>
       </c>
@@ -5018,7 +5031,7 @@
       <c r="W52" s="51">
         <v>123818</v>
       </c>
-      <c r="X52" s="194"/>
+      <c r="X52" s="171"/>
       <c r="Y52" s="85">
         <v>969</v>
       </c>
@@ -5050,7 +5063,7 @@
         <v>124787</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="17" thickBot="1">
+    <row r="53" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
         <v>2009</v>
       </c>
@@ -5114,7 +5127,7 @@
       <c r="W53" s="51">
         <v>133920</v>
       </c>
-      <c r="X53" s="194"/>
+      <c r="X53" s="171"/>
       <c r="Y53" s="85">
         <v>876</v>
       </c>
@@ -5146,7 +5159,7 @@
         <v>134796</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="17" thickBot="1">
+    <row r="54" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
         <v>2010</v>
       </c>
@@ -5210,7 +5223,7 @@
       <c r="W54" s="51">
         <v>139783</v>
       </c>
-      <c r="X54" s="194"/>
+      <c r="X54" s="171"/>
       <c r="Y54" s="84">
         <v>714</v>
       </c>
@@ -5242,7 +5255,7 @@
         <v>140497</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="17" thickBot="1">
+    <row r="55" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
         <v>2011</v>
       </c>
@@ -5306,7 +5319,7 @@
       <c r="W55" s="92">
         <v>135062</v>
       </c>
-      <c r="X55" s="194"/>
+      <c r="X55" s="171"/>
       <c r="Y55" s="91">
         <v>503</v>
       </c>
@@ -5338,7 +5351,7 @@
         <v>135565</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="17" thickBot="1">
+    <row r="56" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -5368,7 +5381,7 @@
       <c r="W56" s="54">
         <v>121197</v>
       </c>
-      <c r="X56" s="195"/>
+      <c r="X56" s="199"/>
       <c r="Y56" s="91">
         <v>820</v>
       </c>
@@ -5400,7 +5413,7 @@
         <v>122017</v>
       </c>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
         <v>82</v>
       </c>
@@ -5415,7 +5428,7 @@
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
     </row>
-    <row r="58" spans="1:33" ht="17" thickBot="1">
+    <row r="58" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A58" s="3" t="s">
         <v>22</v>
       </c>
@@ -5448,20 +5461,20 @@
       </c>
       <c r="K58" s="3"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="180" t="s">
+      <c r="N58" s="218" t="s">
         <v>95</v>
       </c>
-      <c r="O58" s="181"/>
-      <c r="P58" s="181"/>
-      <c r="Q58" s="182"/>
+      <c r="O58" s="215"/>
+      <c r="P58" s="215"/>
+      <c r="Q58" s="216"/>
       <c r="R58" s="58"/>
-      <c r="S58" s="183"/>
+      <c r="S58" s="185"/>
       <c r="T58" s="58"/>
       <c r="U58" s="58"/>
       <c r="V58" s="58"/>
       <c r="W58" s="46"/>
     </row>
-    <row r="59" spans="1:33" ht="27" thickBot="1">
+    <row r="59" spans="1:33" ht="20.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
         <v>2000</v>
       </c>
@@ -5511,7 +5524,7 @@
       <c r="R59" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="S59" s="184"/>
+      <c r="S59" s="186"/>
       <c r="T59" s="27" t="s">
         <v>97</v>
       </c>
@@ -5525,7 +5538,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="18" thickTop="1" thickBot="1">
+    <row r="60" spans="1:33" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
         <v>2001</v>
       </c>
@@ -5575,7 +5588,7 @@
       <c r="R60" s="97">
         <v>19189</v>
       </c>
-      <c r="S60" s="193"/>
+      <c r="S60" s="170"/>
       <c r="T60" s="31">
         <v>2027</v>
       </c>
@@ -5589,7 +5602,7 @@
         <v>321578</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="17" thickBot="1">
+    <row r="61" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
         <v>2002</v>
       </c>
@@ -5639,7 +5652,7 @@
       <c r="R61" s="98">
         <v>25768</v>
       </c>
-      <c r="S61" s="194"/>
+      <c r="S61" s="171"/>
       <c r="T61" s="83">
         <v>3065</v>
       </c>
@@ -5653,7 +5666,7 @@
         <v>342823</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="17" thickBot="1">
+    <row r="62" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
         <v>2003</v>
       </c>
@@ -5703,7 +5716,7 @@
       <c r="R62" s="97">
         <v>18999</v>
       </c>
-      <c r="S62" s="194"/>
+      <c r="S62" s="171"/>
       <c r="T62" s="31">
         <v>2988</v>
       </c>
@@ -5717,7 +5730,7 @@
         <v>328115</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="17" thickBot="1">
+    <row r="63" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
         <v>2004</v>
       </c>
@@ -5767,7 +5780,7 @@
       <c r="R63" s="98">
         <v>21726</v>
       </c>
-      <c r="S63" s="194"/>
+      <c r="S63" s="171"/>
       <c r="T63" s="83">
         <v>2697</v>
       </c>
@@ -5781,7 +5794,7 @@
         <v>322664</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="17" thickBot="1">
+    <row r="64" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
         <v>2005</v>
       </c>
@@ -5831,7 +5844,7 @@
       <c r="R64" s="98">
         <v>30460</v>
       </c>
-      <c r="S64" s="194"/>
+      <c r="S64" s="171"/>
       <c r="T64" s="31">
         <v>2529</v>
       </c>
@@ -5845,7 +5858,7 @@
         <v>342578</v>
       </c>
     </row>
-    <row r="65" spans="1:32" ht="17" thickBot="1">
+    <row r="65" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
         <v>2006</v>
       </c>
@@ -5895,7 +5908,7 @@
       <c r="R65" s="97">
         <v>27175</v>
       </c>
-      <c r="S65" s="194"/>
+      <c r="S65" s="171"/>
       <c r="T65" s="84">
         <v>0</v>
       </c>
@@ -5909,7 +5922,7 @@
         <v>329536</v>
       </c>
     </row>
-    <row r="66" spans="1:32" ht="17" thickBot="1">
+    <row r="66" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
         <v>2007</v>
       </c>
@@ -5959,7 +5972,7 @@
       <c r="R66" s="97">
         <v>15770</v>
       </c>
-      <c r="S66" s="194"/>
+      <c r="S66" s="171"/>
       <c r="T66" s="31">
         <v>2019</v>
       </c>
@@ -5973,7 +5986,7 @@
         <v>340289</v>
       </c>
     </row>
-    <row r="67" spans="1:32" ht="17" thickBot="1">
+    <row r="67" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
         <v>2008</v>
       </c>
@@ -6023,7 +6036,7 @@
       <c r="R67" s="97">
         <v>22470</v>
       </c>
-      <c r="S67" s="194"/>
+      <c r="S67" s="171"/>
       <c r="T67" s="31">
         <v>2457</v>
       </c>
@@ -6037,7 +6050,7 @@
         <v>356755</v>
       </c>
     </row>
-    <row r="68" spans="1:32" ht="17" thickBot="1">
+    <row r="68" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
         <v>2009</v>
       </c>
@@ -6087,7 +6100,7 @@
       <c r="R68" s="98">
         <v>22656</v>
       </c>
-      <c r="S68" s="194"/>
+      <c r="S68" s="171"/>
       <c r="T68" s="31">
         <v>2787</v>
       </c>
@@ -6101,7 +6114,7 @@
         <v>365576</v>
       </c>
     </row>
-    <row r="69" spans="1:32" ht="17" thickBot="1">
+    <row r="69" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
         <v>2010</v>
       </c>
@@ -6151,7 +6164,7 @@
       <c r="R69" s="100">
         <v>23093</v>
       </c>
-      <c r="S69" s="194"/>
+      <c r="S69" s="171"/>
       <c r="T69" s="34">
         <v>2332</v>
       </c>
@@ -6165,7 +6178,7 @@
         <v>366779</v>
       </c>
     </row>
-    <row r="70" spans="1:32" ht="17" thickBot="1">
+    <row r="70" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
         <v>2011</v>
       </c>
@@ -6215,7 +6228,7 @@
       <c r="R70" s="100">
         <v>27032</v>
       </c>
-      <c r="S70" s="195"/>
+      <c r="S70" s="199"/>
       <c r="T70" s="34">
         <v>2339</v>
       </c>
@@ -6229,12 +6242,12 @@
         <v>334844</v>
       </c>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A72" s="38" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>22</v>
       </c>
@@ -6277,20 +6290,20 @@
       <c r="Q73" s="58"/>
       <c r="R73" s="58"/>
       <c r="S73" s="58"/>
-      <c r="T73" s="177" t="s">
+      <c r="T73" s="189" t="s">
         <v>100</v>
       </c>
-      <c r="U73" s="172"/>
+      <c r="U73" s="190"/>
       <c r="V73" s="58"/>
-      <c r="W73" s="178"/>
-      <c r="X73" s="174"/>
-      <c r="Y73" s="178"/>
-      <c r="Z73" s="174"/>
+      <c r="W73" s="187"/>
+      <c r="X73" s="188"/>
+      <c r="Y73" s="187"/>
+      <c r="Z73" s="188"/>
       <c r="AA73" s="58"/>
-      <c r="AB73" s="178"/>
-      <c r="AC73" s="173"/>
+      <c r="AB73" s="187"/>
+      <c r="AC73" s="206"/>
     </row>
-    <row r="74" spans="1:32" ht="26">
+    <row r="74" spans="1:32" ht="20" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
         <v>2000</v>
       </c>
@@ -6341,28 +6354,28 @@
       <c r="S74" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="T74" s="177" t="s">
+      <c r="T74" s="189" t="s">
         <v>101</v>
       </c>
-      <c r="U74" s="172"/>
+      <c r="U74" s="190"/>
       <c r="V74" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="W74" s="189" t="s">
+      <c r="W74" s="212" t="s">
         <v>103</v>
       </c>
-      <c r="X74" s="190"/>
-      <c r="Y74" s="185" t="s">
+      <c r="X74" s="213"/>
+      <c r="Y74" s="204" t="s">
         <v>104</v>
       </c>
-      <c r="Z74" s="186"/>
+      <c r="Z74" s="205"/>
       <c r="AA74" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="AB74" s="199" t="s">
+      <c r="AB74" s="207" t="s">
         <v>105</v>
       </c>
-      <c r="AC74" s="200"/>
+      <c r="AC74" s="208"/>
       <c r="AD74" t="s">
         <v>115</v>
       </c>
@@ -6373,7 +6386,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="75" spans="1:32" ht="17" thickBot="1">
+    <row r="75" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
         <v>2001</v>
       </c>
@@ -6418,10 +6431,10 @@
       <c r="Q75" s="66"/>
       <c r="R75" s="66"/>
       <c r="S75" s="66"/>
-      <c r="T75" s="179" t="s">
+      <c r="T75" s="210" t="s">
         <v>102</v>
       </c>
-      <c r="U75" s="176"/>
+      <c r="U75" s="211"/>
       <c r="V75" s="66"/>
       <c r="W75" s="191"/>
       <c r="X75" s="192"/>
@@ -6429,9 +6442,9 @@
       <c r="Z75" s="192"/>
       <c r="AA75" s="66"/>
       <c r="AB75" s="191"/>
-      <c r="AC75" s="198"/>
+      <c r="AC75" s="209"/>
     </row>
-    <row r="76" spans="1:32" ht="18" thickTop="1" thickBot="1">
+    <row r="76" spans="1:32" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
         <v>2002</v>
       </c>
@@ -6491,7 +6504,7 @@
       <c r="V76" s="102">
         <v>381</v>
       </c>
-      <c r="W76" s="193"/>
+      <c r="W76" s="170"/>
       <c r="X76" s="84">
         <v>0</v>
       </c>
@@ -6523,7 +6536,7 @@
         <v>10644</v>
       </c>
     </row>
-    <row r="77" spans="1:32" ht="17" thickBot="1">
+    <row r="77" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
         <v>2003</v>
       </c>
@@ -6583,7 +6596,7 @@
       <c r="V77" s="102">
         <v>319</v>
       </c>
-      <c r="W77" s="194"/>
+      <c r="W77" s="171"/>
       <c r="X77" s="84">
         <v>0</v>
       </c>
@@ -6615,7 +6628,7 @@
         <v>13573</v>
       </c>
     </row>
-    <row r="78" spans="1:32" ht="17" thickBot="1">
+    <row r="78" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
         <v>2004</v>
       </c>
@@ -6675,7 +6688,7 @@
       <c r="V78" s="102">
         <v>213</v>
       </c>
-      <c r="W78" s="194"/>
+      <c r="W78" s="171"/>
       <c r="X78" s="84">
         <v>0</v>
       </c>
@@ -6707,7 +6720,7 @@
         <v>12455</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="17" thickBot="1">
+    <row r="79" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
         <v>2005</v>
       </c>
@@ -6767,7 +6780,7 @@
       <c r="V79" s="103">
         <v>268</v>
       </c>
-      <c r="W79" s="194"/>
+      <c r="W79" s="171"/>
       <c r="X79" s="84">
         <v>0</v>
       </c>
@@ -6799,7 +6812,7 @@
         <v>11953</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="17" thickBot="1">
+    <row r="80" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
         <v>2006</v>
       </c>
@@ -6859,7 +6872,7 @@
       <c r="V80" s="103">
         <v>619</v>
       </c>
-      <c r="W80" s="194"/>
+      <c r="W80" s="171"/>
       <c r="X80" s="84">
         <v>0</v>
       </c>
@@ -6891,7 +6904,7 @@
         <v>11482</v>
       </c>
     </row>
-    <row r="81" spans="1:34" ht="17" thickBot="1">
+    <row r="81" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
         <v>2007</v>
       </c>
@@ -6951,7 +6964,7 @@
       <c r="V81" s="97">
         <v>1303</v>
       </c>
-      <c r="W81" s="194"/>
+      <c r="W81" s="171"/>
       <c r="X81" s="84">
         <v>0</v>
       </c>
@@ -6983,7 +6996,7 @@
         <v>7048</v>
       </c>
     </row>
-    <row r="82" spans="1:34" ht="17" thickBot="1">
+    <row r="82" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
         <v>2008</v>
       </c>
@@ -7043,7 +7056,7 @@
       <c r="V82" s="97">
         <v>3783</v>
       </c>
-      <c r="W82" s="194"/>
+      <c r="W82" s="171"/>
       <c r="X82" s="85">
         <v>66</v>
       </c>
@@ -7075,7 +7088,7 @@
         <v>4712</v>
       </c>
     </row>
-    <row r="83" spans="1:34" ht="17" thickBot="1">
+    <row r="83" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
         <v>2009</v>
       </c>
@@ -7135,7 +7148,7 @@
       <c r="V83" s="97">
         <v>7012</v>
       </c>
-      <c r="W83" s="194"/>
+      <c r="W83" s="171"/>
       <c r="X83" s="84">
         <v>0</v>
       </c>
@@ -7167,7 +7180,7 @@
         <v>6941</v>
       </c>
     </row>
-    <row r="84" spans="1:34" ht="17" thickBot="1">
+    <row r="84" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
         <v>2010</v>
       </c>
@@ -7227,7 +7240,7 @@
       <c r="V84" s="97">
         <v>9295</v>
       </c>
-      <c r="W84" s="194"/>
+      <c r="W84" s="171"/>
       <c r="X84" s="84">
         <v>15</v>
       </c>
@@ -7259,7 +7272,7 @@
         <v>6546</v>
       </c>
     </row>
-    <row r="85" spans="1:34" ht="17" thickBot="1">
+    <row r="85" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
         <v>2011</v>
       </c>
@@ -7319,7 +7332,7 @@
       <c r="V85" s="100">
         <v>7954</v>
       </c>
-      <c r="W85" s="194"/>
+      <c r="W85" s="171"/>
       <c r="X85" s="104">
         <v>46</v>
       </c>
@@ -7351,7 +7364,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="86" spans="1:34" ht="17" thickBot="1">
+    <row r="86" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="Q86" s="56">
         <v>2020</v>
       </c>
@@ -7370,7 +7383,7 @@
       <c r="V86" s="105">
         <v>6485</v>
       </c>
-      <c r="W86" s="195"/>
+      <c r="W86" s="199"/>
       <c r="X86" s="34">
         <v>1247</v>
       </c>
@@ -7402,12 +7415,12 @@
         <v>3219</v>
       </c>
     </row>
-    <row r="87" spans="1:34">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A87" s="38" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="1:34">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A88" s="3" t="s">
         <v>22</v>
       </c>
@@ -7447,14 +7460,14 @@
       <c r="Q88" s="58"/>
       <c r="R88" s="58"/>
       <c r="S88" s="58"/>
-      <c r="T88" s="178"/>
-      <c r="U88" s="174"/>
-      <c r="V88" s="178"/>
-      <c r="W88" s="174"/>
+      <c r="T88" s="187"/>
+      <c r="U88" s="188"/>
+      <c r="V88" s="187"/>
+      <c r="W88" s="188"/>
       <c r="X88" s="58"/>
-      <c r="Y88" s="178"/>
-      <c r="Z88" s="174"/>
-      <c r="AA88" s="206" t="s">
+      <c r="Y88" s="187"/>
+      <c r="Z88" s="188"/>
+      <c r="AA88" s="179" t="s">
         <v>112</v>
       </c>
       <c r="AB88" s="58"/>
@@ -7463,7 +7476,7 @@
       <c r="AE88" s="58"/>
       <c r="AF88" s="46"/>
     </row>
-    <row r="89" spans="1:34" ht="26">
+    <row r="89" spans="1:34" ht="20" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
         <v>2000</v>
       </c>
@@ -7506,22 +7519,22 @@
         <v>108</v>
       </c>
       <c r="S89" s="58"/>
-      <c r="T89" s="203" t="s">
+      <c r="T89" s="200" t="s">
         <v>109</v>
       </c>
-      <c r="U89" s="204"/>
-      <c r="V89" s="196" t="s">
+      <c r="U89" s="201"/>
+      <c r="V89" s="202" t="s">
         <v>110</v>
       </c>
-      <c r="W89" s="205"/>
+      <c r="W89" s="203"/>
       <c r="X89" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="Y89" s="177" t="s">
+      <c r="Y89" s="189" t="s">
         <v>111</v>
       </c>
-      <c r="Z89" s="172"/>
-      <c r="AA89" s="206"/>
+      <c r="Z89" s="190"/>
+      <c r="AA89" s="179"/>
       <c r="AB89" s="65" t="s">
         <v>71</v>
       </c>
@@ -7532,7 +7545,7 @@
       </c>
       <c r="AF89" s="46"/>
     </row>
-    <row r="90" spans="1:34" ht="17" thickBot="1">
+    <row r="90" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
         <v>2001</v>
       </c>
@@ -7584,7 +7597,7 @@
       <c r="X90" s="66"/>
       <c r="Y90" s="191"/>
       <c r="Z90" s="192"/>
-      <c r="AA90" s="207"/>
+      <c r="AA90" s="193"/>
       <c r="AB90" s="66"/>
       <c r="AC90" s="96" t="s">
         <v>99</v>
@@ -7603,7 +7616,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="91" spans="1:34" ht="18" thickTop="1" thickBot="1">
+    <row r="91" spans="1:34" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
         <v>2002</v>
       </c>
@@ -7665,7 +7678,7 @@
       <c r="X91" s="103">
         <v>600</v>
       </c>
-      <c r="Y91" s="208"/>
+      <c r="Y91" s="194"/>
       <c r="Z91" s="102">
         <v>0</v>
       </c>
@@ -7696,7 +7709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:34" ht="17" thickBot="1">
+    <row r="92" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
         <v>2003</v>
       </c>
@@ -7758,7 +7771,7 @@
       <c r="X92" s="102">
         <v>0</v>
       </c>
-      <c r="Y92" s="209"/>
+      <c r="Y92" s="195"/>
       <c r="Z92" s="102">
         <v>0</v>
       </c>
@@ -7789,7 +7802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:34" ht="17" thickBot="1">
+    <row r="93" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
         <v>2004</v>
       </c>
@@ -7851,7 +7864,7 @@
       <c r="X93" s="102">
         <v>0</v>
       </c>
-      <c r="Y93" s="209"/>
+      <c r="Y93" s="195"/>
       <c r="Z93" s="103">
         <v>60</v>
       </c>
@@ -7882,7 +7895,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="94" spans="1:34" ht="17" thickBot="1">
+    <row r="94" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
         <v>2005</v>
       </c>
@@ -7944,7 +7957,7 @@
       <c r="X94" s="97">
         <v>4319</v>
       </c>
-      <c r="Y94" s="209"/>
+      <c r="Y94" s="195"/>
       <c r="Z94" s="102">
         <v>84</v>
       </c>
@@ -7975,7 +7988,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="95" spans="1:34" ht="17" thickBot="1">
+    <row r="95" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
         <v>2006</v>
       </c>
@@ -8037,7 +8050,7 @@
       <c r="X95" s="97">
         <v>3215</v>
       </c>
-      <c r="Y95" s="209"/>
+      <c r="Y95" s="195"/>
       <c r="Z95" s="102">
         <v>159</v>
       </c>
@@ -8068,7 +8081,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="1:34" ht="17" thickBot="1">
+    <row r="96" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
         <v>2007</v>
       </c>
@@ -8130,7 +8143,7 @@
       <c r="X96" s="97">
         <v>1377</v>
       </c>
-      <c r="Y96" s="209"/>
+      <c r="Y96" s="195"/>
       <c r="Z96" s="102">
         <v>15</v>
       </c>
@@ -8161,7 +8174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:34" ht="17" thickBot="1">
+    <row r="97" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
         <v>2008</v>
       </c>
@@ -8223,7 +8236,7 @@
       <c r="X97" s="98">
         <v>2167</v>
       </c>
-      <c r="Y97" s="209"/>
+      <c r="Y97" s="195"/>
       <c r="Z97" s="102">
         <v>9</v>
       </c>
@@ -8254,7 +8267,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:34" ht="17" thickBot="1">
+    <row r="98" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
         <v>2009</v>
       </c>
@@ -8316,7 +8329,7 @@
       <c r="X98" s="97">
         <v>2981</v>
       </c>
-      <c r="Y98" s="209"/>
+      <c r="Y98" s="195"/>
       <c r="Z98" s="102">
         <v>4</v>
       </c>
@@ -8347,7 +8360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:34" ht="17" thickBot="1">
+    <row r="99" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
         <v>2010</v>
       </c>
@@ -8409,7 +8422,7 @@
       <c r="X99" s="97">
         <v>2011</v>
       </c>
-      <c r="Y99" s="209"/>
+      <c r="Y99" s="195"/>
       <c r="Z99" s="102">
         <v>0</v>
       </c>
@@ -8440,7 +8453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:34" ht="17" thickBot="1">
+    <row r="100" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
         <v>2011</v>
       </c>
@@ -8502,7 +8515,7 @@
       <c r="X100" s="106">
         <v>0</v>
       </c>
-      <c r="Y100" s="209"/>
+      <c r="Y100" s="195"/>
       <c r="Z100" s="106">
         <v>0</v>
       </c>
@@ -8533,7 +8546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:34" ht="17" thickBot="1">
+    <row r="101" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="Q101" s="56">
         <v>2020</v>
       </c>
@@ -8558,7 +8571,7 @@
       <c r="X101" s="106">
         <v>0</v>
       </c>
-      <c r="Y101" s="210"/>
+      <c r="Y101" s="196"/>
       <c r="Z101" s="106">
         <v>0</v>
       </c>
@@ -8589,19 +8602,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:34">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A104" s="38" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="105" spans="1:34" ht="27" thickBot="1">
+    <row r="105" spans="1:34" ht="20.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A105" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="G105" s="201" t="s">
+      <c r="G105" s="197" t="s">
         <v>140</v>
       </c>
-      <c r="H105" s="202"/>
+      <c r="H105" s="198"/>
       <c r="I105" s="69" t="s">
         <v>141</v>
       </c>
@@ -8609,7 +8622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:34" s="107" customFormat="1" ht="18" thickTop="1" thickBot="1">
+    <row r="106" spans="1:34" s="107" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A106" s="107" t="s">
         <v>22</v>
       </c>
@@ -8635,7 +8648,7 @@
         <v>3407592</v>
       </c>
     </row>
-    <row r="107" spans="1:34" ht="17" thickBot="1">
+    <row r="107" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A107" s="17">
         <v>2000</v>
       </c>
@@ -8661,7 +8674,7 @@
         <v>3256379</v>
       </c>
     </row>
-    <row r="108" spans="1:34" ht="17" thickBot="1">
+    <row r="108" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A108" s="17">
         <v>2001</v>
       </c>
@@ -8687,7 +8700,7 @@
         <v>3174639</v>
       </c>
     </row>
-    <row r="109" spans="1:34" ht="17" thickBot="1">
+    <row r="109" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A109" s="17">
         <v>2002</v>
       </c>
@@ -8713,7 +8726,7 @@
         <v>3120838</v>
       </c>
     </row>
-    <row r="110" spans="1:34" ht="17" thickBot="1">
+    <row r="110" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A110" s="17">
         <v>2003</v>
       </c>
@@ -8739,7 +8752,7 @@
         <v>3175791</v>
       </c>
     </row>
-    <row r="111" spans="1:34" ht="17" thickBot="1">
+    <row r="111" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A111" s="17">
         <v>2004</v>
       </c>
@@ -8765,7 +8778,7 @@
         <v>3116142</v>
       </c>
     </row>
-    <row r="112" spans="1:34" ht="17" thickBot="1">
+    <row r="112" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A112" s="17">
         <v>2005</v>
       </c>
@@ -8791,7 +8804,7 @@
         <v>3070239</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="17" thickBot="1">
+    <row r="113" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A113" s="17">
         <v>2006</v>
       </c>
@@ -8817,7 +8830,7 @@
         <v>2963184</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="17" thickBot="1">
+    <row r="114" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A114" s="17">
         <v>2007</v>
       </c>
@@ -8843,7 +8856,7 @@
         <v>2996802</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="17" thickBot="1">
+    <row r="115" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A115" s="17">
         <v>2008</v>
       </c>
@@ -8869,7 +8882,7 @@
         <v>2809668</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="17" thickBot="1">
+    <row r="116" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A116" s="17">
         <v>2009</v>
       </c>
@@ -8895,7 +8908,7 @@
         <v>2442831</v>
       </c>
     </row>
-    <row r="117" spans="1:28">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A117" s="17">
         <v>2010</v>
       </c>
@@ -8909,7 +8922,7 @@
         <v>3407592</v>
       </c>
     </row>
-    <row r="118" spans="1:28">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A118" s="17">
         <v>2011</v>
       </c>
@@ -8923,18 +8936,18 @@
         <v>3256379</v>
       </c>
     </row>
-    <row r="119" spans="1:28">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A119" s="17"/>
       <c r="B119" s="24"/>
       <c r="C119" s="20"/>
       <c r="D119" s="24"/>
     </row>
-    <row r="120" spans="1:28">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A120" s="38" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="121" spans="1:28">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>22</v>
       </c>
@@ -8949,26 +8962,26 @@
       <c r="J121" s="46"/>
       <c r="K121" s="46"/>
       <c r="L121" s="58"/>
-      <c r="M121" s="206" t="s">
+      <c r="M121" s="179" t="s">
         <v>147</v>
       </c>
-      <c r="N121" s="212" t="s">
+      <c r="N121" s="181" t="s">
         <v>148</v>
       </c>
-      <c r="O121" s="213"/>
-      <c r="P121" s="214"/>
-      <c r="Q121" s="214"/>
-      <c r="R121" s="214"/>
-      <c r="S121" s="214"/>
-      <c r="T121" s="215" t="s">
+      <c r="O121" s="182"/>
+      <c r="P121" s="183"/>
+      <c r="Q121" s="183"/>
+      <c r="R121" s="183"/>
+      <c r="S121" s="183"/>
+      <c r="T121" s="176" t="s">
         <v>148</v>
       </c>
-      <c r="U121" s="216"/>
+      <c r="U121" s="184"/>
       <c r="V121" s="46"/>
       <c r="W121" s="46"/>
       <c r="X121" s="46"/>
     </row>
-    <row r="122" spans="1:28" ht="26">
+    <row r="122" spans="1:28" ht="20" x14ac:dyDescent="0.4">
       <c r="B122" t="s">
         <v>126</v>
       </c>
@@ -8993,15 +9006,15 @@
       </c>
       <c r="K122" s="46"/>
       <c r="L122" s="58"/>
-      <c r="M122" s="206"/>
-      <c r="N122" s="212"/>
-      <c r="O122" s="213"/>
-      <c r="P122" s="214"/>
-      <c r="Q122" s="214"/>
-      <c r="R122" s="214"/>
-      <c r="S122" s="214"/>
-      <c r="T122" s="215"/>
-      <c r="U122" s="216"/>
+      <c r="M122" s="179"/>
+      <c r="N122" s="181"/>
+      <c r="O122" s="182"/>
+      <c r="P122" s="183"/>
+      <c r="Q122" s="183"/>
+      <c r="R122" s="183"/>
+      <c r="S122" s="183"/>
+      <c r="T122" s="176"/>
+      <c r="U122" s="184"/>
       <c r="V122" s="45" t="s">
         <v>149</v>
       </c>
@@ -9010,7 +9023,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="123" spans="1:28" ht="27" thickBot="1">
+    <row r="123" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A123" s="17">
         <v>2000</v>
       </c>
@@ -9041,15 +9054,15 @@
       <c r="L123" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="M123" s="206"/>
-      <c r="N123" s="212"/>
-      <c r="O123" s="213"/>
-      <c r="P123" s="214"/>
-      <c r="Q123" s="214"/>
-      <c r="R123" s="214"/>
-      <c r="S123" s="214"/>
-      <c r="T123" s="215"/>
-      <c r="U123" s="216"/>
+      <c r="M123" s="179"/>
+      <c r="N123" s="181"/>
+      <c r="O123" s="182"/>
+      <c r="P123" s="183"/>
+      <c r="Q123" s="183"/>
+      <c r="R123" s="183"/>
+      <c r="S123" s="183"/>
+      <c r="T123" s="176"/>
+      <c r="U123" s="184"/>
       <c r="V123" s="45" t="s">
         <v>150</v>
       </c>
@@ -9060,7 +9073,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="124" spans="1:28" ht="17" thickBot="1">
+    <row r="124" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A124" s="17">
         <v>2001</v>
       </c>
@@ -9087,20 +9100,20 @@
       <c r="J124" s="63"/>
       <c r="K124" s="63"/>
       <c r="L124" s="116"/>
-      <c r="M124" s="206"/>
-      <c r="N124" s="212"/>
-      <c r="O124" s="213"/>
-      <c r="P124" s="214"/>
-      <c r="Q124" s="214"/>
-      <c r="R124" s="214"/>
-      <c r="S124" s="214"/>
-      <c r="T124" s="215"/>
-      <c r="U124" s="216"/>
+      <c r="M124" s="179"/>
+      <c r="N124" s="181"/>
+      <c r="O124" s="182"/>
+      <c r="P124" s="183"/>
+      <c r="Q124" s="183"/>
+      <c r="R124" s="183"/>
+      <c r="S124" s="183"/>
+      <c r="T124" s="176"/>
+      <c r="U124" s="184"/>
       <c r="V124" s="63"/>
       <c r="W124" s="63"/>
       <c r="X124" s="63"/>
     </row>
-    <row r="125" spans="1:28" ht="17" thickBot="1">
+    <row r="125" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A125" s="17">
         <v>2002</v>
       </c>
@@ -9127,22 +9140,22 @@
       <c r="J125" s="63"/>
       <c r="K125" s="63"/>
       <c r="L125" s="116"/>
-      <c r="M125" s="206"/>
+      <c r="M125" s="179"/>
       <c r="N125" s="119"/>
       <c r="O125" s="58"/>
-      <c r="P125" s="183"/>
+      <c r="P125" s="185"/>
       <c r="Q125" s="58"/>
       <c r="R125" s="46"/>
       <c r="S125" s="46"/>
       <c r="T125" s="58"/>
-      <c r="U125" s="206" t="s">
+      <c r="U125" s="179" t="s">
         <v>158</v>
       </c>
       <c r="V125" s="63"/>
       <c r="W125" s="63"/>
       <c r="X125" s="63"/>
     </row>
-    <row r="126" spans="1:28" ht="17" thickBot="1">
+    <row r="126" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A126" s="17">
         <v>2003</v>
       </c>
@@ -9171,14 +9184,14 @@
       <c r="J126" s="63"/>
       <c r="K126" s="63"/>
       <c r="L126" s="116"/>
-      <c r="M126" s="206"/>
+      <c r="M126" s="179"/>
       <c r="N126" s="81" t="s">
         <v>149</v>
       </c>
       <c r="O126" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="P126" s="183"/>
+      <c r="P126" s="185"/>
       <c r="Q126" s="94" t="s">
         <v>154</v>
       </c>
@@ -9191,12 +9204,12 @@
       <c r="T126" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="U126" s="206"/>
+      <c r="U126" s="179"/>
       <c r="V126" s="63"/>
       <c r="W126" s="63"/>
       <c r="X126" s="63"/>
     </row>
-    <row r="127" spans="1:28" ht="17" thickBot="1">
+    <row r="127" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A127" s="17">
         <v>2004</v>
       </c>
@@ -9223,19 +9236,19 @@
       <c r="J127" s="118"/>
       <c r="K127" s="118"/>
       <c r="L127" s="117"/>
-      <c r="M127" s="211"/>
+      <c r="M127" s="180"/>
       <c r="N127" s="120" t="s">
         <v>153</v>
       </c>
       <c r="O127" s="120" t="s">
         <v>153</v>
       </c>
-      <c r="P127" s="183"/>
+      <c r="P127" s="185"/>
       <c r="Q127" s="117"/>
       <c r="R127" s="118"/>
       <c r="S127" s="118"/>
       <c r="T127" s="117"/>
-      <c r="U127" s="211"/>
+      <c r="U127" s="180"/>
       <c r="V127" s="118"/>
       <c r="W127" s="118"/>
       <c r="X127" s="118"/>
@@ -9252,7 +9265,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="128" spans="1:28" ht="17" thickBot="1">
+    <row r="128" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A128" s="17">
         <v>2005</v>
       </c>
@@ -9282,19 +9295,19 @@
       <c r="M128" s="58"/>
       <c r="N128" s="58"/>
       <c r="O128" s="58"/>
-      <c r="P128" s="183"/>
+      <c r="P128" s="185"/>
       <c r="Q128" s="58"/>
       <c r="R128" s="46"/>
       <c r="S128" s="46"/>
       <c r="T128" s="58"/>
       <c r="U128" s="58"/>
       <c r="V128" s="46"/>
-      <c r="W128" s="217" t="s">
+      <c r="W128" s="168" t="s">
         <v>160</v>
       </c>
       <c r="X128" s="46"/>
     </row>
-    <row r="129" spans="1:28" ht="17" thickBot="1">
+    <row r="129" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A129" s="17">
         <v>2006</v>
       </c>
@@ -9338,7 +9351,7 @@
       <c r="O129" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="P129" s="184"/>
+      <c r="P129" s="186"/>
       <c r="Q129" s="96" t="s">
         <v>159</v>
       </c>
@@ -9357,12 +9370,12 @@
       <c r="V129" s="47" t="s">
         <v>159</v>
       </c>
-      <c r="W129" s="175"/>
+      <c r="W129" s="169"/>
       <c r="X129" s="121" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="130" spans="1:28" ht="18" thickTop="1" thickBot="1">
+    <row r="130" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A130" s="17">
         <v>2007</v>
       </c>
@@ -9408,7 +9421,7 @@
       <c r="O130" s="125">
         <v>20866</v>
       </c>
-      <c r="P130" s="193"/>
+      <c r="P130" s="170"/>
       <c r="Q130" s="124">
         <v>34038</v>
       </c>
@@ -9450,7 +9463,7 @@
         <v>228606.22396603454</v>
       </c>
     </row>
-    <row r="131" spans="1:28" ht="17" thickBot="1">
+    <row r="131" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A131" s="17">
         <v>2008</v>
       </c>
@@ -9496,7 +9509,7 @@
       <c r="O131" s="131">
         <v>14289</v>
       </c>
-      <c r="P131" s="194"/>
+      <c r="P131" s="171"/>
       <c r="Q131" s="126">
         <v>37476</v>
       </c>
@@ -9538,7 +9551,7 @@
         <v>207689.09055137934</v>
       </c>
     </row>
-    <row r="132" spans="1:28" ht="17" thickBot="1">
+    <row r="132" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A132" s="17">
         <v>2009</v>
       </c>
@@ -9584,7 +9597,7 @@
       <c r="O132" s="131">
         <v>28141</v>
       </c>
-      <c r="P132" s="194"/>
+      <c r="P132" s="171"/>
       <c r="Q132" s="124">
         <v>39782</v>
       </c>
@@ -9626,7 +9639,7 @@
         <v>172153.40889672414</v>
       </c>
     </row>
-    <row r="133" spans="1:28" ht="17" thickBot="1">
+    <row r="133" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A133" s="17">
         <v>2010</v>
       </c>
@@ -9672,7 +9685,7 @@
       <c r="O133" s="125">
         <v>26647</v>
       </c>
-      <c r="P133" s="194"/>
+      <c r="P133" s="171"/>
       <c r="Q133" s="126">
         <v>38866</v>
       </c>
@@ -9714,7 +9727,7 @@
         <v>181963.32992655176</v>
       </c>
     </row>
-    <row r="134" spans="1:28" ht="17" thickBot="1">
+    <row r="134" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A134" s="17">
         <v>2011</v>
       </c>
@@ -9760,7 +9773,7 @@
       <c r="O134" s="131">
         <v>29757</v>
       </c>
-      <c r="P134" s="194"/>
+      <c r="P134" s="171"/>
       <c r="Q134" s="124">
         <v>41992</v>
       </c>
@@ -9802,7 +9815,7 @@
         <v>171909.49223500001</v>
       </c>
     </row>
-    <row r="135" spans="1:28" ht="17" thickBot="1">
+    <row r="135" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H135" s="122">
         <v>2015</v>
       </c>
@@ -9827,7 +9840,7 @@
       <c r="O135" s="131">
         <v>24801</v>
       </c>
-      <c r="P135" s="194"/>
+      <c r="P135" s="171"/>
       <c r="Q135" s="124">
         <v>47384</v>
       </c>
@@ -9869,7 +9882,7 @@
         <v>180273.10103500003</v>
       </c>
     </row>
-    <row r="136" spans="1:28" ht="17" thickBot="1">
+    <row r="136" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>130</v>
       </c>
@@ -9900,7 +9913,7 @@
       <c r="O136" s="131">
         <v>24805</v>
       </c>
-      <c r="P136" s="194"/>
+      <c r="P136" s="171"/>
       <c r="Q136" s="124">
         <v>105138</v>
       </c>
@@ -9942,7 +9955,7 @@
         <v>191215.04051327589</v>
       </c>
     </row>
-    <row r="137" spans="1:28" ht="17" thickBot="1">
+    <row r="137" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>131</v>
       </c>
@@ -9973,7 +9986,7 @@
       <c r="O137" s="131">
         <v>22418</v>
       </c>
-      <c r="P137" s="194"/>
+      <c r="P137" s="171"/>
       <c r="Q137" s="124">
         <v>50033</v>
       </c>
@@ -10015,7 +10028,7 @@
         <v>181684.91566931037</v>
       </c>
     </row>
-    <row r="138" spans="1:28" ht="17" thickBot="1">
+    <row r="138" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H138" s="122">
         <v>2018</v>
       </c>
@@ -10040,7 +10053,7 @@
       <c r="O138" s="131">
         <v>29842</v>
       </c>
-      <c r="P138" s="194"/>
+      <c r="P138" s="171"/>
       <c r="Q138" s="124">
         <v>42322</v>
       </c>
@@ -10082,7 +10095,7 @@
         <v>180173.76245862071</v>
       </c>
     </row>
-    <row r="139" spans="1:28" ht="17" thickBot="1">
+    <row r="139" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>164</v>
       </c>
@@ -10113,7 +10126,7 @@
       <c r="O139" s="139">
         <v>20167</v>
       </c>
-      <c r="P139" s="194"/>
+      <c r="P139" s="171"/>
       <c r="Q139" s="137">
         <v>40917</v>
       </c>
@@ -10155,7 +10168,7 @@
         <v>155360.19476500002</v>
       </c>
     </row>
-    <row r="140" spans="1:28" ht="17" thickBot="1">
+    <row r="140" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H140" s="142">
         <v>2020</v>
       </c>
@@ -10180,7 +10193,7 @@
       <c r="O140" s="139">
         <v>18468</v>
       </c>
-      <c r="P140" s="218"/>
+      <c r="P140" s="172"/>
       <c r="Q140" s="137">
         <v>13897</v>
       </c>
@@ -10222,34 +10235,34 @@
         <v>145904.43348810347</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A146" s="38" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A147" s="58"/>
-      <c r="B147" s="219" t="s">
+      <c r="B147" s="173" t="s">
         <v>167</v>
       </c>
-      <c r="C147" s="219" t="s">
+      <c r="C147" s="173" t="s">
         <v>168</v>
       </c>
-      <c r="D147" s="221" t="s">
+      <c r="D147" s="175" t="s">
         <v>169</v>
       </c>
-      <c r="E147" s="215"/>
+      <c r="E147" s="176"/>
     </row>
-    <row r="148" spans="1:5" ht="17" thickBot="1">
+    <row r="148" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A148" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B148" s="220"/>
-      <c r="C148" s="220"/>
-      <c r="D148" s="222"/>
-      <c r="E148" s="223"/>
+      <c r="B148" s="174"/>
+      <c r="C148" s="174"/>
+      <c r="D148" s="177"/>
+      <c r="E148" s="178"/>
     </row>
-    <row r="149" spans="1:5" ht="18" thickTop="1" thickBot="1">
+    <row r="149" spans="1:5" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A149" s="145">
         <v>2010</v>
       </c>
@@ -10266,7 +10279,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="17" thickBot="1">
+    <row r="150" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A150" s="145">
         <v>2011</v>
       </c>
@@ -10283,7 +10296,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="17" thickBot="1">
+    <row r="151" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A151" s="145">
         <v>2012</v>
       </c>
@@ -10300,7 +10313,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="17" thickBot="1">
+    <row r="152" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A152" s="145">
         <v>2013</v>
       </c>
@@ -10317,7 +10330,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="17" thickBot="1">
+    <row r="153" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A153" s="145">
         <v>2014</v>
       </c>
@@ -10334,7 +10347,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="17" thickBot="1">
+    <row r="154" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A154" s="145">
         <v>2015</v>
       </c>
@@ -10351,7 +10364,7 @@
         <v>18953</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="17" thickBot="1">
+    <row r="155" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A155" s="145">
         <v>2016</v>
       </c>
@@ -10368,7 +10381,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="17" thickBot="1">
+    <row r="156" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A156" s="145">
         <v>2017</v>
       </c>
@@ -10385,7 +10398,7 @@
         <v>24786</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="17" thickBot="1">
+    <row r="157" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A157" s="145">
         <v>2018</v>
       </c>
@@ -10402,7 +10415,7 @@
         <v>25670</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="17" thickBot="1">
+    <row r="158" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A158" s="145">
         <v>2019</v>
       </c>
@@ -10419,7 +10432,7 @@
         <v>26277</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="17" thickBot="1">
+    <row r="159" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A159" s="145">
         <v>2020</v>
       </c>
@@ -10438,49 +10451,12 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="W128:W129"/>
-    <mergeCell ref="P130:P140"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:C148"/>
-    <mergeCell ref="D147:E148"/>
-    <mergeCell ref="M121:M127"/>
-    <mergeCell ref="N121:O124"/>
-    <mergeCell ref="P121:R124"/>
-    <mergeCell ref="S121:S124"/>
-    <mergeCell ref="T121:U124"/>
-    <mergeCell ref="P125:P129"/>
-    <mergeCell ref="U125:U127"/>
-    <mergeCell ref="Y88:Z88"/>
-    <mergeCell ref="Y89:Z89"/>
-    <mergeCell ref="Y90:Z90"/>
-    <mergeCell ref="AA88:AA90"/>
-    <mergeCell ref="Y91:Y101"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="W76:W86"/>
-    <mergeCell ref="T88:U88"/>
-    <mergeCell ref="T89:U89"/>
-    <mergeCell ref="T90:U90"/>
-    <mergeCell ref="V88:W88"/>
-    <mergeCell ref="V89:W89"/>
-    <mergeCell ref="V90:W90"/>
-    <mergeCell ref="Y73:Z73"/>
-    <mergeCell ref="Y74:Z74"/>
-    <mergeCell ref="Y75:Z75"/>
-    <mergeCell ref="AB73:AC73"/>
-    <mergeCell ref="AB74:AC74"/>
-    <mergeCell ref="AB75:AC75"/>
-    <mergeCell ref="S60:S70"/>
-    <mergeCell ref="T73:U73"/>
-    <mergeCell ref="T74:U74"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="W73:X73"/>
-    <mergeCell ref="W74:X74"/>
-    <mergeCell ref="W75:X75"/>
-    <mergeCell ref="I24:K25"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="T3:U4"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="V4:W4"/>
     <mergeCell ref="V5:W5"/>
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="X4:Y4"/>
@@ -10494,12 +10470,49 @@
     <mergeCell ref="X44:Y44"/>
     <mergeCell ref="X45:Y45"/>
     <mergeCell ref="X46:X56"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="T3:U4"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="I24:K25"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="S60:S70"/>
+    <mergeCell ref="T73:U73"/>
+    <mergeCell ref="T74:U74"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="W73:X73"/>
+    <mergeCell ref="W74:X74"/>
+    <mergeCell ref="W75:X75"/>
+    <mergeCell ref="Y73:Z73"/>
+    <mergeCell ref="Y74:Z74"/>
+    <mergeCell ref="Y75:Z75"/>
+    <mergeCell ref="AB73:AC73"/>
+    <mergeCell ref="AB74:AC74"/>
+    <mergeCell ref="AB75:AC75"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="W76:W86"/>
+    <mergeCell ref="T88:U88"/>
+    <mergeCell ref="T89:U89"/>
+    <mergeCell ref="T90:U90"/>
+    <mergeCell ref="V88:W88"/>
+    <mergeCell ref="V89:W89"/>
+    <mergeCell ref="V90:W90"/>
+    <mergeCell ref="Y88:Z88"/>
+    <mergeCell ref="Y89:Z89"/>
+    <mergeCell ref="Y90:Z90"/>
+    <mergeCell ref="AA88:AA90"/>
+    <mergeCell ref="Y91:Y101"/>
+    <mergeCell ref="M121:M127"/>
+    <mergeCell ref="N121:O124"/>
+    <mergeCell ref="P121:R124"/>
+    <mergeCell ref="S121:S124"/>
+    <mergeCell ref="T121:U124"/>
+    <mergeCell ref="P125:P129"/>
+    <mergeCell ref="U125:U127"/>
+    <mergeCell ref="W128:W129"/>
+    <mergeCell ref="P130:P140"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:C148"/>
+    <mergeCell ref="D147:E148"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10508,7 +10521,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4A1704-7464-DB42-ADE9-F63DB066BC0B}">
   <dimension ref="A1:AZ81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="48.1640625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -10517,7 +10530,7 @@
     <col min="14" max="22" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A1" s="146" t="s">
         <v>29</v>
       </c>
@@ -10675,7 +10688,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A2" s="146" t="s">
         <v>1</v>
       </c>
@@ -10863,7 +10876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:52">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A3" s="146" t="s">
         <v>36</v>
       </c>
@@ -11051,7 +11064,7 @@
         <v>1425398165.242424</v>
       </c>
     </row>
-    <row r="4" spans="1:52">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A4" s="146" t="s">
         <v>133</v>
       </c>
@@ -11239,7 +11252,7 @@
         <v>2873408.359307359</v>
       </c>
     </row>
-    <row r="5" spans="1:52">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A5" s="146" t="s">
         <v>4</v>
       </c>
@@ -11427,7 +11440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:52">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A6" s="146" t="s">
         <v>5</v>
       </c>
@@ -11615,7 +11628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A7" s="146" t="s">
         <v>6</v>
       </c>
@@ -11803,7 +11816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:52">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A8" s="146" t="s">
         <v>7</v>
       </c>
@@ -11991,7 +12004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A9" s="146" t="s">
         <v>8</v>
       </c>
@@ -12179,7 +12192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:52">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A10" s="146" t="s">
         <v>137</v>
       </c>
@@ -12367,7 +12380,7 @@
         <v>96719.874458874576</v>
       </c>
     </row>
-    <row r="11" spans="1:52">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A11" s="146" t="s">
         <v>138</v>
       </c>
@@ -12555,7 +12568,7 @@
         <v>194630.45454545459</v>
       </c>
     </row>
-    <row r="12" spans="1:52">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A12" s="146" t="s">
         <v>11</v>
       </c>
@@ -12743,7 +12756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:52">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A13" s="146" t="s">
         <v>171</v>
       </c>
@@ -12911,7 +12924,7 @@
         <v>29628.045454545412</v>
       </c>
     </row>
-    <row r="14" spans="1:52">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A14" s="146" t="s">
         <v>114</v>
       </c>
@@ -13076,7 +13089,7 @@
         <v>1657.1650562770665</v>
       </c>
     </row>
-    <row r="15" spans="1:52">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A15" s="146" t="s">
         <v>14</v>
       </c>
@@ -13264,7 +13277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:52">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A16" s="146" t="s">
         <v>15</v>
       </c>
@@ -13452,7 +13465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:52">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A17" s="146" t="s">
         <v>16</v>
       </c>
@@ -13640,7 +13653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:52">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A18" s="146" t="s">
         <v>51</v>
       </c>
@@ -13819,7 +13832,7 @@
         <v>9803.0688311681151</v>
       </c>
     </row>
-    <row r="19" spans="1:52">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A19" s="146" t="s">
         <v>139</v>
       </c>
@@ -13982,7 +13995,7 @@
         <v>733.15367965353653</v>
       </c>
     </row>
-    <row r="20" spans="1:52">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A20" s="146" t="s">
         <v>59</v>
       </c>
@@ -14170,7 +14183,7 @@
         <v>2385989.4632034618</v>
       </c>
     </row>
-    <row r="21" spans="1:52">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A21" s="146" t="s">
         <v>20</v>
       </c>
@@ -14358,7 +14371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:52">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A22" s="146" t="s">
         <v>21</v>
       </c>
@@ -14546,7 +14559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:52">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A23" s="149"/>
       <c r="B23" s="149"/>
       <c r="C23" s="149"/>
@@ -14591,7 +14604,7 @@
       <c r="AP23" s="149"/>
       <c r="AQ23" s="149"/>
     </row>
-    <row r="24" spans="1:52">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A24" s="149"/>
       <c r="B24" s="149"/>
       <c r="C24" s="149"/>
@@ -14636,7 +14649,7 @@
       <c r="AP24" s="149"/>
       <c r="AQ24" s="149"/>
     </row>
-    <row r="25" spans="1:52">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A25" s="149"/>
       <c r="B25" s="149"/>
       <c r="C25" s="149"/>
@@ -14681,7 +14694,7 @@
       <c r="AP25" s="149"/>
       <c r="AQ25" s="149"/>
     </row>
-    <row r="26" spans="1:52">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A26" s="146" t="s">
         <v>30</v>
       </c>
@@ -14839,7 +14852,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="27" spans="1:52">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A27" s="146" t="s">
         <v>1</v>
       </c>
@@ -15027,7 +15040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:52">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A28" s="146" t="s">
         <v>36</v>
       </c>
@@ -15215,7 +15228,7 @@
         <v>1021634133.9307404</v>
       </c>
     </row>
-    <row r="29" spans="1:52">
+    <row r="29" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A29" s="146" t="s">
         <v>132</v>
       </c>
@@ -15373,7 +15386,7 @@
         <v>145904.43348810347</v>
       </c>
     </row>
-    <row r="30" spans="1:52">
+    <row r="30" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A30" s="146" t="s">
         <v>4</v>
       </c>
@@ -15561,7 +15574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:52">
+    <row r="31" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A31" s="146" t="s">
         <v>5</v>
       </c>
@@ -15749,7 +15762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:52">
+    <row r="32" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A32" s="146" t="s">
         <v>6</v>
       </c>
@@ -15937,7 +15950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:52">
+    <row r="33" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A33" s="146" t="s">
         <v>7</v>
       </c>
@@ -16125,7 +16138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:52">
+    <row r="34" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A34" s="146" t="s">
         <v>8</v>
       </c>
@@ -16313,7 +16326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:52">
+    <row r="35" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A35" s="146" t="s">
         <v>137</v>
       </c>
@@ -16501,7 +16514,7 @@
         <v>63.348051948051989</v>
       </c>
     </row>
-    <row r="36" spans="1:52">
+    <row r="36" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A36" s="146" t="s">
         <v>138</v>
       </c>
@@ -16689,7 +16702,7 @@
         <v>284.22510822510833</v>
       </c>
     </row>
-    <row r="37" spans="1:52">
+    <row r="37" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A37" s="146" t="s">
         <v>11</v>
       </c>
@@ -16877,7 +16890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:52">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A38" s="146" t="s">
         <v>171</v>
       </c>
@@ -17036,7 +17049,7 @@
         <v>15.818181818191078</v>
       </c>
     </row>
-    <row r="39" spans="1:52">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A39" s="146" t="s">
         <v>116</v>
       </c>
@@ -17224,7 +17237,7 @@
         <v>3313.6212121211865</v>
       </c>
     </row>
-    <row r="40" spans="1:52">
+    <row r="40" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A40" s="146" t="s">
         <v>14</v>
       </c>
@@ -17412,7 +17425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:52">
+    <row r="41" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A41" s="146" t="s">
         <v>15</v>
       </c>
@@ -17600,7 +17613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:52">
+    <row r="42" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A42" s="146" t="s">
         <v>16</v>
       </c>
@@ -17758,7 +17771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:52">
+    <row r="43" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A43" s="146" t="s">
         <v>51</v>
       </c>
@@ -17921,7 +17934,7 @@
         <v>7180.0173160172999</v>
       </c>
     </row>
-    <row r="44" spans="1:52">
+    <row r="44" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A44" s="146" t="s">
         <v>139</v>
       </c>
@@ -18109,7 +18122,7 @@
         <v>881.63809523809323</v>
       </c>
     </row>
-    <row r="45" spans="1:52">
+    <row r="45" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A45" s="146" t="s">
         <v>59</v>
       </c>
@@ -18267,7 +18280,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:52">
+    <row r="46" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A46" s="146" t="s">
         <v>20</v>
       </c>
@@ -18455,7 +18468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:52">
+    <row r="47" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A47" s="146" t="s">
         <v>21</v>
       </c>
@@ -18643,7 +18656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:52">
+    <row r="48" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A48" s="149"/>
       <c r="B48" s="149"/>
       <c r="C48" s="149"/>
@@ -18688,7 +18701,7 @@
       <c r="AP48" s="149"/>
       <c r="AQ48" s="149"/>
     </row>
-    <row r="49" spans="1:52">
+    <row r="49" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A49" s="149"/>
       <c r="B49" s="149"/>
       <c r="C49" s="149"/>
@@ -18733,7 +18746,7 @@
       <c r="AP49" s="149"/>
       <c r="AQ49" s="149"/>
     </row>
-    <row r="50" spans="1:52">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A50" s="149"/>
       <c r="B50" s="149"/>
       <c r="C50" s="149"/>
@@ -18778,7 +18791,7 @@
       <c r="AP50" s="149"/>
       <c r="AQ50" s="149"/>
     </row>
-    <row r="51" spans="1:52">
+    <row r="51" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A51" s="146" t="s">
         <v>31</v>
       </c>
@@ -18936,7 +18949,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="52" spans="1:52">
+    <row r="52" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A52" s="146" t="s">
         <v>1</v>
       </c>
@@ -19124,7 +19137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:52">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A53" s="146" t="s">
         <v>36</v>
       </c>
@@ -19312,7 +19325,7 @@
         <v>16249341.611082315</v>
       </c>
     </row>
-    <row r="54" spans="1:52">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A54" s="146" t="s">
         <v>3</v>
       </c>
@@ -19500,7 +19513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:52">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A55" s="146" t="s">
         <v>4</v>
       </c>
@@ -19688,7 +19701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:52">
+    <row r="56" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A56" s="146" t="s">
         <v>5</v>
       </c>
@@ -19876,7 +19889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:52">
+    <row r="57" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A57" s="146" t="s">
         <v>6</v>
       </c>
@@ -20064,7 +20077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:52">
+    <row r="58" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A58" s="146" t="s">
         <v>7</v>
       </c>
@@ -20252,7 +20265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:52">
+    <row r="59" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A59" s="146" t="s">
         <v>8</v>
       </c>
@@ -20440,7 +20453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:52">
+    <row r="60" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A60" s="146" t="s">
         <v>134</v>
       </c>
@@ -20628,7 +20641,7 @@
         <v>56642.645021644887</v>
       </c>
     </row>
-    <row r="61" spans="1:52">
+    <row r="61" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A61" s="146" t="s">
         <v>135</v>
       </c>
@@ -20799,7 +20812,7 @@
         <v>252.61731601727661</v>
       </c>
     </row>
-    <row r="62" spans="1:52">
+    <row r="62" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A62" s="146" t="s">
         <v>11</v>
       </c>
@@ -20987,7 +21000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:52">
+    <row r="63" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A63" s="146" t="s">
         <v>171</v>
       </c>
@@ -21155,7 +21168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:52">
+    <row r="64" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A64" s="146" t="s">
         <v>114</v>
       </c>
@@ -21343,7 +21356,7 @@
         <v>2387.9870129870251</v>
       </c>
     </row>
-    <row r="65" spans="1:52">
+    <row r="65" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A65" s="146" t="s">
         <v>14</v>
       </c>
@@ -21531,7 +21544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:52">
+    <row r="66" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A66" s="146" t="s">
         <v>15</v>
       </c>
@@ -21719,7 +21732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:52">
+    <row r="67" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A67" s="146" t="s">
         <v>16</v>
       </c>
@@ -21907,7 +21920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:52">
+    <row r="68" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A68" s="146" t="s">
         <v>51</v>
       </c>
@@ -22095,7 +22108,7 @@
         <v>101052.20346320339</v>
       </c>
     </row>
-    <row r="69" spans="1:52">
+    <row r="69" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A69" s="146" t="s">
         <v>136</v>
       </c>
@@ -22255,7 +22268,7 @@
         <v>22.458008658024482</v>
       </c>
     </row>
-    <row r="70" spans="1:52">
+    <row r="70" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A70" s="146" t="s">
         <v>59</v>
       </c>
@@ -22443,7 +22456,7 @@
         <v>16462405.359307408</v>
       </c>
     </row>
-    <row r="71" spans="1:52">
+    <row r="71" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A71" s="146" t="s">
         <v>20</v>
       </c>
@@ -22631,7 +22644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:52">
+    <row r="72" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A72" s="146" t="s">
         <v>21</v>
       </c>
@@ -22819,7 +22832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:52">
+    <row r="73" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A73" s="149"/>
       <c r="B73" s="149"/>
       <c r="C73" s="149"/>
@@ -22864,7 +22877,7 @@
       <c r="AP73" s="149"/>
       <c r="AQ73" s="149"/>
     </row>
-    <row r="74" spans="1:52">
+    <row r="74" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A74" s="149"/>
       <c r="B74" s="149"/>
       <c r="C74" s="149"/>
@@ -22909,7 +22922,7 @@
       <c r="AP74" s="149"/>
       <c r="AQ74" s="149"/>
     </row>
-    <row r="75" spans="1:52">
+    <row r="75" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A75" s="149"/>
       <c r="B75" s="149"/>
       <c r="C75" s="149"/>
@@ -22954,7 +22967,7 @@
       <c r="AP75" s="149"/>
       <c r="AQ75" s="149"/>
     </row>
-    <row r="76" spans="1:52" ht="68" customHeight="1">
+    <row r="76" spans="1:52" ht="68" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="153"/>
       <c r="B76" s="154" t="s">
         <v>172</v>
@@ -23001,7 +23014,7 @@
       <c r="AP76" s="149"/>
       <c r="AQ76" s="149"/>
     </row>
-    <row r="77" spans="1:52">
+    <row r="77" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A77" s="149"/>
       <c r="B77" s="149"/>
       <c r="C77" s="149"/>
@@ -23046,7 +23059,7 @@
       <c r="AP77" s="149"/>
       <c r="AQ77" s="149"/>
     </row>
-    <row r="78" spans="1:52" ht="71" customHeight="1">
+    <row r="78" spans="1:52" ht="71" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="156"/>
       <c r="B78" s="159" t="s">
         <v>173</v>
@@ -23093,7 +23106,7 @@
       <c r="AP78" s="149"/>
       <c r="AQ78" s="149"/>
     </row>
-    <row r="79" spans="1:52">
+    <row r="79" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A79" s="149"/>
       <c r="B79" s="149"/>
       <c r="C79" s="149"/>
@@ -23138,7 +23151,7 @@
       <c r="AP79" s="149"/>
       <c r="AQ79" s="149"/>
     </row>
-    <row r="80" spans="1:52" ht="78" customHeight="1">
+    <row r="80" spans="1:52" ht="78" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="158"/>
       <c r="B80" s="159" t="s">
         <v>174</v>
@@ -23185,7 +23198,7 @@
       <c r="AP80" s="149"/>
       <c r="AQ80" s="149"/>
     </row>
-    <row r="81" spans="1:43">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.4">
       <c r="A81" s="149"/>
       <c r="B81" s="149"/>
       <c r="C81" s="149"/>
@@ -23238,25 +23251,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DC08D71-B78F-774E-8A28-46D984F940EA}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>175</v>
       </c>
       <c r="B2" s="161">
-        <v>0.17960000000000001</v>
+        <v>179.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>177</v>
       </c>
@@ -23264,7 +23278,7 @@
         <v>4.2766000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>178</v>
       </c>
@@ -23272,7 +23286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>179</v>
       </c>
@@ -23280,7 +23294,7 @@
         <v>5.9273999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>180</v>
       </c>
@@ -23288,10 +23302,10 @@
         <v>8.5245999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B7" s="162"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="38" t="s">
         <v>182</v>
       </c>
@@ -23299,21 +23313,21 @@
         <v>5800000</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="38" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="162">
+      <c r="B12" s="224">
         <f>B2*$B$8</f>
-        <v>1041680</v>
+        <v>1041680000</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>177</v>
       </c>
@@ -23322,7 +23336,7 @@
         <v>24804280</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>178</v>
       </c>
@@ -23331,7 +23345,7 @@
         <v>5800000</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>179</v>
       </c>
@@ -23340,7 +23354,7 @@
         <v>34378920</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>180</v>
       </c>
@@ -23357,7 +23371,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B189A75B-B529-A24C-89B4-38ED16AFA0A9}">
   <dimension ref="A1:AH73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
@@ -23365,12 +23379,12 @@
     <col min="4" max="33" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -23471,7 +23485,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -23604,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -23737,140 +23751,140 @@
         <v>3.5355975202159352E+16</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="164">
         <f>'Data Computation and Processing'!U4*Conversion!$B$12</f>
-        <v>2926774962240</v>
+        <v>2926774962240000</v>
       </c>
       <c r="C5" s="164">
         <f>'Data Computation and Processing'!V4*Conversion!$B$12</f>
-        <v>2544648196080</v>
+        <v>2544648196080000</v>
       </c>
       <c r="D5" s="164">
         <f>'Data Computation and Processing'!W4*Conversion!$B$12</f>
-        <v>3093384465846.0942</v>
+        <v>3093384465846094.5</v>
       </c>
       <c r="E5" s="164">
         <f>'Data Computation and Processing'!X4*Conversion!$B$12</f>
-        <v>3089928864255.6533</v>
+        <v>3089928864255653.5</v>
       </c>
       <c r="F5" s="164">
         <f>'Data Computation and Processing'!Y4*Conversion!$B$12</f>
-        <v>3086473262665.2114</v>
+        <v>3086473262665211.5</v>
       </c>
       <c r="G5" s="164">
         <f>'Data Computation and Processing'!Z4*Conversion!$B$12</f>
-        <v>3083017661074.7705</v>
+        <v>3083017661074770.5</v>
       </c>
       <c r="H5" s="164">
         <f>'Data Computation and Processing'!AA4*Conversion!$B$12</f>
-        <v>3079562059484.3281</v>
+        <v>3079562059484328.5</v>
       </c>
       <c r="I5" s="164">
         <f>'Data Computation and Processing'!AB4*Conversion!$B$12</f>
-        <v>3076106457893.8872</v>
+        <v>3076106457893887.5</v>
       </c>
       <c r="J5" s="164">
         <f>'Data Computation and Processing'!AC4*Conversion!$B$12</f>
-        <v>3072650856303.4453</v>
+        <v>3072650856303445</v>
       </c>
       <c r="K5" s="164">
         <f>'Data Computation and Processing'!AD4*Conversion!$B$12</f>
-        <v>3069195254713.0044</v>
+        <v>3069195254713004</v>
       </c>
       <c r="L5" s="164">
         <f>'Data Computation and Processing'!AE4*Conversion!$B$12</f>
-        <v>3065739653122.562</v>
+        <v>3065739653122562</v>
       </c>
       <c r="M5" s="164">
         <f>'Data Computation and Processing'!AF4*Conversion!$B$12</f>
-        <v>3062284051532.1211</v>
+        <v>3062284051532121</v>
       </c>
       <c r="N5" s="164">
         <f>'Data Computation and Processing'!AG4*Conversion!$B$12</f>
-        <v>3058828449941.6792</v>
+        <v>3058828449941679</v>
       </c>
       <c r="O5" s="164">
         <f>'Data Computation and Processing'!AH4*Conversion!$B$12</f>
-        <v>3055372848351.2383</v>
+        <v>3055372848351238</v>
       </c>
       <c r="P5" s="164">
         <f>'Data Computation and Processing'!AI4*Conversion!$B$12</f>
-        <v>3051917246760.7959</v>
+        <v>3051917246760796</v>
       </c>
       <c r="Q5" s="164">
         <f>'Data Computation and Processing'!AJ4*Conversion!$B$12</f>
-        <v>3048461645170.354</v>
+        <v>3048461645170354</v>
       </c>
       <c r="R5" s="164">
         <f>'Data Computation and Processing'!AK4*Conversion!$B$12</f>
-        <v>3045006043579.9131</v>
+        <v>3045006043579913</v>
       </c>
       <c r="S5" s="164">
         <f>'Data Computation and Processing'!AL4*Conversion!$B$12</f>
-        <v>3041550441989.4712</v>
+        <v>3041550441989471</v>
       </c>
       <c r="T5" s="164">
         <f>'Data Computation and Processing'!AM4*Conversion!$B$12</f>
-        <v>3038094840399.0298</v>
+        <v>3038094840399030</v>
       </c>
       <c r="U5" s="164">
         <f>'Data Computation and Processing'!AN4*Conversion!$B$12</f>
-        <v>3034639238808.5879</v>
+        <v>3034639238808588</v>
       </c>
       <c r="V5" s="164">
         <f>'Data Computation and Processing'!AO4*Conversion!$B$12</f>
-        <v>3031183637218.147</v>
+        <v>3031183637218147</v>
       </c>
       <c r="W5" s="164">
         <f>'Data Computation and Processing'!AP4*Conversion!$B$12</f>
-        <v>3027728035627.7051</v>
+        <v>3027728035627705</v>
       </c>
       <c r="X5" s="164">
         <f>'Data Computation and Processing'!AQ4*Conversion!$B$12</f>
-        <v>3024272434037.2637</v>
+        <v>3024272434037264</v>
       </c>
       <c r="Y5" s="164">
         <f>'Data Computation and Processing'!AR4*Conversion!$B$12</f>
-        <v>3020816832446.8218</v>
+        <v>3020816832446822</v>
       </c>
       <c r="Z5" s="164">
         <f>'Data Computation and Processing'!AS4*Conversion!$B$12</f>
-        <v>3017361230856.3809</v>
+        <v>3017361230856381</v>
       </c>
       <c r="AA5" s="164">
         <f>'Data Computation and Processing'!AT4*Conversion!$B$12</f>
-        <v>3013905629265.939</v>
+        <v>3013905629265939</v>
       </c>
       <c r="AB5" s="164">
         <f>'Data Computation and Processing'!AU4*Conversion!$B$12</f>
-        <v>3010450027675.4976</v>
+        <v>3010450027675498</v>
       </c>
       <c r="AC5" s="164">
         <f>'Data Computation and Processing'!AV4*Conversion!$B$12</f>
-        <v>3006994426085.0557</v>
+        <v>3006994426085056</v>
       </c>
       <c r="AD5" s="164">
         <f>'Data Computation and Processing'!AW4*Conversion!$B$12</f>
-        <v>3003538824494.6147</v>
+        <v>3003538824494615</v>
       </c>
       <c r="AE5" s="164">
         <f>'Data Computation and Processing'!AX4*Conversion!$B$12</f>
-        <v>3000083222904.1729</v>
+        <v>3000083222904172.5</v>
       </c>
       <c r="AF5" s="164">
         <f>'Data Computation and Processing'!AY4*Conversion!$B$12</f>
-        <v>2996627621313.731</v>
+        <v>2996627621313730.5</v>
       </c>
       <c r="AG5" s="164">
         <f>'Data Computation and Processing'!AZ4*Conversion!$B$12</f>
-        <v>2993172019723.2896</v>
+        <v>2993172019723289.5</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -23971,7 +23985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -24072,7 +24086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -24173,7 +24187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -24274,7 +24288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -24375,7 +24389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -24461,7 +24475,7 @@
       </c>
       <c r="V11" s="164">
         <f>'Data Computation and Processing'!AO10*Conversion!$B$14</f>
-        <v>424952429004.32812</v>
+        <v>424952429004.32813</v>
       </c>
       <c r="W11" s="164">
         <f>'Data Computation and Processing'!AP10*Conversion!$B$14</f>
@@ -24509,7 +24523,7 @@
       </c>
       <c r="AH11" s="3"/>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -24643,7 +24657,7 @@
       </c>
       <c r="AH12" s="3"/>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -24745,7 +24759,7 @@
       </c>
       <c r="AH13" s="3"/>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -24879,7 +24893,7 @@
       </c>
       <c r="AH14" s="3"/>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -25013,7 +25027,7 @@
       </c>
       <c r="AH15" s="3"/>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -25115,7 +25129,7 @@
       </c>
       <c r="AH16" s="3"/>
     </row>
-    <row r="17" spans="1:34">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -25217,7 +25231,7 @@
       </c>
       <c r="AH17" s="3"/>
     </row>
-    <row r="18" spans="1:34">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -25319,7 +25333,7 @@
       </c>
       <c r="AH18" s="3"/>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -25453,7 +25467,7 @@
       </c>
       <c r="AH19" s="3"/>
     </row>
-    <row r="20" spans="1:34">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -25587,7 +25601,7 @@
       </c>
       <c r="AH20" s="3"/>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -25649,7 +25663,7 @@
       </c>
       <c r="P21" s="164">
         <f>'Data Computation and Processing'!AI20*Conversion!$B$16</f>
-        <v>110524569519487.62</v>
+        <v>110524569519487.63</v>
       </c>
       <c r="Q21" s="164">
         <f>'Data Computation and Processing'!AJ20*Conversion!$B$16</f>
@@ -25705,7 +25719,7 @@
       </c>
       <c r="AD21" s="164">
         <f>'Data Computation and Processing'!AW20*Conversion!$B$16</f>
-        <v>116655864572590.12</v>
+        <v>116655864572590.13</v>
       </c>
       <c r="AE21" s="164">
         <f>'Data Computation and Processing'!AX20*Conversion!$B$16</f>
@@ -25721,7 +25735,7 @@
       </c>
       <c r="AH21" s="3"/>
     </row>
-    <row r="22" spans="1:34">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -25823,7 +25837,7 @@
       </c>
       <c r="AH22" s="3"/>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -25925,7 +25939,7 @@
       </c>
       <c r="AH23" s="3"/>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.4">
       <c r="B24" s="165"/>
       <c r="C24" s="165"/>
       <c r="D24" s="165"/>
@@ -25960,7 +25974,7 @@
       <c r="AG24" s="165"/>
       <c r="AH24" s="3"/>
     </row>
-    <row r="25" spans="1:34">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.4">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -25995,7 +26009,7 @@
       <c r="AG25" s="3"/>
       <c r="AH25" s="3"/>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>55</v>
       </c>
@@ -26033,7 +26047,7 @@
       <c r="AG26" s="3"/>
       <c r="AH26" s="3"/>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -26135,7 +26149,7 @@
       </c>
       <c r="AH27" s="3"/>
     </row>
-    <row r="28" spans="1:34">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
@@ -26269,7 +26283,7 @@
       </c>
       <c r="AH28" s="3"/>
     </row>
-    <row r="29" spans="1:34">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>2</v>
       </c>
@@ -26403,141 +26417,141 @@
       </c>
       <c r="AH29" s="3"/>
     </row>
-    <row r="30" spans="1:34">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B30" s="164">
         <f>'Data Computation and Processing'!U29*Conversion!$B$12</f>
-        <v>161835607682.80524</v>
+        <v>161835607682805.22</v>
       </c>
       <c r="C30" s="164">
         <f>'Data Computation and Processing'!V29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="D30" s="164">
         <f>'Data Computation and Processing'!W29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="E30" s="164">
         <f>'Data Computation and Processing'!X29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="F30" s="164">
         <f>'Data Computation and Processing'!Y29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="G30" s="164">
         <f>'Data Computation and Processing'!Z29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="H30" s="164">
         <f>'Data Computation and Processing'!AA29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="I30" s="164">
         <f>'Data Computation and Processing'!AB29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="J30" s="164">
         <f>'Data Computation and Processing'!AC29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="K30" s="164">
         <f>'Data Computation and Processing'!AD29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="L30" s="164">
         <f>'Data Computation and Processing'!AE29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="M30" s="164">
         <f>'Data Computation and Processing'!AF29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="N30" s="164">
         <f>'Data Computation and Processing'!AG29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="O30" s="164">
         <f>'Data Computation and Processing'!AH29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="P30" s="164">
         <f>'Data Computation and Processing'!AI29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Q30" s="164">
         <f>'Data Computation and Processing'!AJ29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="R30" s="164">
         <f>'Data Computation and Processing'!AK29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="S30" s="164">
         <f>'Data Computation and Processing'!AL29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="T30" s="164">
         <f>'Data Computation and Processing'!AM29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="U30" s="164">
         <f>'Data Computation and Processing'!AN29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="V30" s="164">
         <f>'Data Computation and Processing'!AO29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="W30" s="164">
         <f>'Data Computation and Processing'!AP29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="X30" s="164">
         <f>'Data Computation and Processing'!AQ29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Y30" s="164">
         <f>'Data Computation and Processing'!AR29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Z30" s="164">
         <f>'Data Computation and Processing'!AS29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AA30" s="164">
         <f>'Data Computation and Processing'!AT29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AB30" s="164">
         <f>'Data Computation and Processing'!AU29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AC30" s="164">
         <f>'Data Computation and Processing'!AV29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AD30" s="164">
         <f>'Data Computation and Processing'!AW29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AE30" s="164">
         <f>'Data Computation and Processing'!AX29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AF30" s="164">
         <f>'Data Computation and Processing'!AY29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AG30" s="164">
         <f>'Data Computation and Processing'!AZ29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AH30" s="3"/>
     </row>
-    <row r="31" spans="1:34">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
@@ -26639,7 +26653,7 @@
       </c>
       <c r="AH31" s="3"/>
     </row>
-    <row r="32" spans="1:34">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
@@ -26741,7 +26755,7 @@
       </c>
       <c r="AH32" s="3"/>
     </row>
-    <row r="33" spans="1:34">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -26843,7 +26857,7 @@
       </c>
       <c r="AH33" s="3"/>
     </row>
-    <row r="34" spans="1:34">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
@@ -26945,7 +26959,7 @@
       </c>
       <c r="AH34" s="3"/>
     </row>
-    <row r="35" spans="1:34">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>8</v>
       </c>
@@ -27047,7 +27061,7 @@
       </c>
       <c r="AH35" s="3"/>
     </row>
-    <row r="36" spans="1:34">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>9</v>
       </c>
@@ -27181,7 +27195,7 @@
       </c>
       <c r="AH36" s="3"/>
     </row>
-    <row r="37" spans="1:34">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>10</v>
       </c>
@@ -27315,7 +27329,7 @@
       </c>
       <c r="AH37" s="3"/>
     </row>
-    <row r="38" spans="1:34">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>11</v>
       </c>
@@ -27417,7 +27431,7 @@
       </c>
       <c r="AH38" s="3"/>
     </row>
-    <row r="39" spans="1:34">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
@@ -27551,7 +27565,7 @@
       </c>
       <c r="AH39" s="3"/>
     </row>
-    <row r="40" spans="1:34">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
@@ -27685,7 +27699,7 @@
       </c>
       <c r="AH40" s="3"/>
     </row>
-    <row r="41" spans="1:34">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
@@ -27787,7 +27801,7 @@
       </c>
       <c r="AH41" s="3"/>
     </row>
-    <row r="42" spans="1:34">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -27888,7 +27902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:34">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
@@ -28021,7 +28035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:34">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>17</v>
       </c>
@@ -28154,7 +28168,7 @@
         <v>41644100432.900337</v>
       </c>
     </row>
-    <row r="45" spans="1:34">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>18</v>
       </c>
@@ -28287,7 +28301,7 @@
         <v>5113500952.3809404</v>
       </c>
     </row>
-    <row r="46" spans="1:34">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -28420,7 +28434,7 @@
         <v>13893393080</v>
       </c>
     </row>
-    <row r="47" spans="1:34">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
         <v>20</v>
       </c>
@@ -28521,7 +28535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:34">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
@@ -28622,12 +28636,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:33">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:33">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
@@ -28728,7 +28742,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="53" spans="1:33">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>1</v>
       </c>
@@ -28861,7 +28875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>2</v>
       </c>
@@ -28895,7 +28909,7 @@
       </c>
       <c r="I54" s="164">
         <f>'Data Computation and Processing'!AB53*Conversion!$B$13</f>
-        <v>187791097922324.62</v>
+        <v>187791097922324.63</v>
       </c>
       <c r="J54" s="164">
         <f>'Data Computation and Processing'!AC53*Conversion!$B$13</f>
@@ -28915,7 +28929,7 @@
       </c>
       <c r="N54" s="164">
         <f>'Data Computation and Processing'!AG53*Conversion!$B$13</f>
-        <v>232637373175367.12</v>
+        <v>232637373175367.13</v>
       </c>
       <c r="O54" s="164">
         <f>'Data Computation and Processing'!AH53*Conversion!$B$13</f>
@@ -28959,7 +28973,7 @@
       </c>
       <c r="Y54" s="164">
         <f>'Data Computation and Processing'!AR53*Conversion!$B$13</f>
-        <v>331299178732064.12</v>
+        <v>331299178732064.13</v>
       </c>
       <c r="Z54" s="164">
         <f>'Data Computation and Processing'!AS53*Conversion!$B$13</f>
@@ -28994,7 +29008,7 @@
         <v>403053219136936.88</v>
       </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
         <v>3</v>
       </c>
@@ -29127,7 +29141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:33">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
         <v>4</v>
       </c>
@@ -29228,7 +29242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
         <v>5</v>
       </c>
@@ -29329,7 +29343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:33">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>6</v>
       </c>
@@ -29430,7 +29444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:33">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>7</v>
       </c>
@@ -29531,7 +29545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:33">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
         <v>8</v>
       </c>
@@ -29632,7 +29646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:33">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>9</v>
       </c>
@@ -29765,7 +29779,7 @@
         <v>328527341125.54034</v>
       </c>
     </row>
-    <row r="62" spans="1:33">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>10</v>
       </c>
@@ -29898,7 +29912,7 @@
         <v>1465180432.9002044</v>
       </c>
     </row>
-    <row r="63" spans="1:33">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>11</v>
       </c>
@@ -29999,7 +30013,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:33">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>12</v>
       </c>
@@ -30132,7 +30146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:33">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>13</v>
       </c>
@@ -30265,7 +30279,7 @@
         <v>82096414480.519897</v>
       </c>
     </row>
-    <row r="66" spans="1:33">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>14</v>
       </c>
@@ -30366,7 +30380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:33">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>15</v>
       </c>
@@ -30467,7 +30481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:33">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>16</v>
       </c>
@@ -30568,7 +30582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:33">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>17</v>
       </c>
@@ -30701,7 +30715,7 @@
         <v>586102780086.57971</v>
       </c>
     </row>
-    <row r="70" spans="1:33">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
         <v>18</v>
       </c>
@@ -30834,7 +30848,7 @@
         <v>130256450.21654201</v>
       </c>
     </row>
-    <row r="71" spans="1:33">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -30880,7 +30894,7 @@
       </c>
       <c r="L71" s="164">
         <f>'Data Computation and Processing'!AE70*Conversion!$B$16</f>
-        <v>444290582369335.12</v>
+        <v>444290582369335.13</v>
       </c>
       <c r="M71" s="164">
         <f>'Data Computation and Processing'!AF70*Conversion!$B$16</f>
@@ -30916,7 +30930,7 @@
       </c>
       <c r="U71" s="164">
         <f>'Data Computation and Processing'!AN70*Conversion!$B$16</f>
-        <v>602714092872700.62</v>
+        <v>602714092872700.63</v>
       </c>
       <c r="V71" s="164">
         <f>'Data Computation and Processing'!AO70*Conversion!$B$16</f>
@@ -30924,7 +30938,7 @@
       </c>
       <c r="W71" s="164">
         <f>'Data Computation and Processing'!AP70*Conversion!$B$16</f>
-        <v>637919317429000.12</v>
+        <v>637919317429000.13</v>
       </c>
       <c r="X71" s="164">
         <f>'Data Computation and Processing'!AQ70*Conversion!$B$16</f>
@@ -30944,7 +30958,7 @@
       </c>
       <c r="AB71" s="164">
         <f>'Data Computation and Processing'!AU70*Conversion!$B$16</f>
-        <v>725932378819760.62</v>
+        <v>725932378819760.63</v>
       </c>
       <c r="AC71" s="164">
         <f>'Data Computation and Processing'!AV70*Conversion!$B$16</f>
@@ -30960,14 +30974,14 @@
       </c>
       <c r="AF71" s="164">
         <f>'Data Computation and Processing'!AY70*Conversion!$B$16</f>
-        <v>796342827932365.62</v>
+        <v>796342827932365.63</v>
       </c>
       <c r="AG71" s="164">
         <f>'Data Computation and Processing'!AZ70*Conversion!$B$16</f>
         <v>813945440210521.25</v>
       </c>
     </row>
-    <row r="72" spans="1:33">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
         <v>20</v>
       </c>
@@ -31068,7 +31082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:33">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
         <v>21</v>
       </c>
@@ -31180,12 +31194,12 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AG23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="38" customFormat="1">
+    <row r="1" spans="1:33" s="38" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -31286,7 +31300,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -31419,7 +31433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -31552,140 +31566,140 @@
         <v>3.5355975202159352E+16</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="162">
         <f>BFPIaE!B5</f>
-        <v>2926774962240</v>
+        <v>2926774962240000</v>
       </c>
       <c r="C4" s="162">
         <f>BFPIaE!C5</f>
-        <v>2544648196080</v>
+        <v>2544648196080000</v>
       </c>
       <c r="D4" s="162">
         <f>BFPIaE!D5</f>
-        <v>3093384465846.0942</v>
+        <v>3093384465846094.5</v>
       </c>
       <c r="E4" s="162">
         <f>BFPIaE!E5</f>
-        <v>3089928864255.6533</v>
+        <v>3089928864255653.5</v>
       </c>
       <c r="F4" s="162">
         <f>BFPIaE!F5</f>
-        <v>3086473262665.2114</v>
+        <v>3086473262665211.5</v>
       </c>
       <c r="G4" s="162">
         <f>BFPIaE!G5</f>
-        <v>3083017661074.7705</v>
+        <v>3083017661074770.5</v>
       </c>
       <c r="H4" s="162">
         <f>BFPIaE!H5</f>
-        <v>3079562059484.3281</v>
+        <v>3079562059484328.5</v>
       </c>
       <c r="I4" s="162">
         <f>BFPIaE!I5</f>
-        <v>3076106457893.8872</v>
+        <v>3076106457893887.5</v>
       </c>
       <c r="J4" s="162">
         <f>BFPIaE!J5</f>
-        <v>3072650856303.4453</v>
+        <v>3072650856303445</v>
       </c>
       <c r="K4" s="162">
         <f>BFPIaE!K5</f>
-        <v>3069195254713.0044</v>
+        <v>3069195254713004</v>
       </c>
       <c r="L4" s="162">
         <f>BFPIaE!L5</f>
-        <v>3065739653122.562</v>
+        <v>3065739653122562</v>
       </c>
       <c r="M4" s="162">
         <f>BFPIaE!M5</f>
-        <v>3062284051532.1211</v>
+        <v>3062284051532121</v>
       </c>
       <c r="N4" s="162">
         <f>BFPIaE!N5</f>
-        <v>3058828449941.6792</v>
+        <v>3058828449941679</v>
       </c>
       <c r="O4" s="162">
         <f>BFPIaE!O5</f>
-        <v>3055372848351.2383</v>
+        <v>3055372848351238</v>
       </c>
       <c r="P4" s="162">
         <f>BFPIaE!P5</f>
-        <v>3051917246760.7959</v>
+        <v>3051917246760796</v>
       </c>
       <c r="Q4" s="162">
         <f>BFPIaE!Q5</f>
-        <v>3048461645170.354</v>
+        <v>3048461645170354</v>
       </c>
       <c r="R4" s="162">
         <f>BFPIaE!R5</f>
-        <v>3045006043579.9131</v>
+        <v>3045006043579913</v>
       </c>
       <c r="S4" s="162">
         <f>BFPIaE!S5</f>
-        <v>3041550441989.4712</v>
+        <v>3041550441989471</v>
       </c>
       <c r="T4" s="162">
         <f>BFPIaE!T5</f>
-        <v>3038094840399.0298</v>
+        <v>3038094840399030</v>
       </c>
       <c r="U4" s="162">
         <f>BFPIaE!U5</f>
-        <v>3034639238808.5879</v>
+        <v>3034639238808588</v>
       </c>
       <c r="V4" s="162">
         <f>BFPIaE!V5</f>
-        <v>3031183637218.147</v>
+        <v>3031183637218147</v>
       </c>
       <c r="W4" s="162">
         <f>BFPIaE!W5</f>
-        <v>3027728035627.7051</v>
+        <v>3027728035627705</v>
       </c>
       <c r="X4" s="162">
         <f>BFPIaE!X5</f>
-        <v>3024272434037.2637</v>
+        <v>3024272434037264</v>
       </c>
       <c r="Y4" s="162">
         <f>BFPIaE!Y5</f>
-        <v>3020816832446.8218</v>
+        <v>3020816832446822</v>
       </c>
       <c r="Z4" s="162">
         <f>BFPIaE!Z5</f>
-        <v>3017361230856.3809</v>
+        <v>3017361230856381</v>
       </c>
       <c r="AA4" s="162">
         <f>BFPIaE!AA5</f>
-        <v>3013905629265.939</v>
+        <v>3013905629265939</v>
       </c>
       <c r="AB4" s="162">
         <f>BFPIaE!AB5</f>
-        <v>3010450027675.4976</v>
+        <v>3010450027675498</v>
       </c>
       <c r="AC4" s="162">
         <f>BFPIaE!AC5</f>
-        <v>3006994426085.0557</v>
+        <v>3006994426085056</v>
       </c>
       <c r="AD4" s="162">
         <f>BFPIaE!AD5</f>
-        <v>3003538824494.6147</v>
+        <v>3003538824494615</v>
       </c>
       <c r="AE4" s="162">
         <f>BFPIaE!AE5</f>
-        <v>3000083222904.1729</v>
+        <v>3000083222904172.5</v>
       </c>
       <c r="AF4" s="162">
         <f>BFPIaE!AF5</f>
-        <v>2996627621313.731</v>
+        <v>2996627621313730.5</v>
       </c>
       <c r="AG4" s="162">
         <f>BFPIaE!AG5</f>
-        <v>2993172019723.2896</v>
+        <v>2993172019723289.5</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -31818,7 +31832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -31951,7 +31965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -32084,7 +32098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -32217,7 +32231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -32350,7 +32364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -32436,7 +32450,7 @@
       </c>
       <c r="V10" s="162">
         <f>BFPIaE!V11</f>
-        <v>424952429004.32812</v>
+        <v>424952429004.32813</v>
       </c>
       <c r="W10" s="162">
         <f>BFPIaE!W11</f>
@@ -32483,7 +32497,7 @@
         <v>560975271861.47253</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -32616,7 +32630,7 @@
         <v>1128856636363.6367</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -32749,7 +32763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
@@ -32882,7 +32896,7 @@
         <v>1018580204438.1804</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -33015,7 +33029,7 @@
         <v>56971544896.544769</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
@@ -33148,7 +33162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -33281,7 +33295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -33414,7 +33428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -33547,7 +33561,7 @@
         <v>56857799220.77507</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
@@ -33680,7 +33694,7 @@
         <v>4252291341.9905119</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
@@ -33742,7 +33756,7 @@
       </c>
       <c r="P20" s="162">
         <f>BFPIaE!P21</f>
-        <v>110524569519487.62</v>
+        <v>110524569519487.63</v>
       </c>
       <c r="Q20" s="162">
         <f>BFPIaE!Q21</f>
@@ -33798,7 +33812,7 @@
       </c>
       <c r="AD20" s="162">
         <f>BFPIaE!AD21</f>
-        <v>116655864572590.12</v>
+        <v>116655864572590.13</v>
       </c>
       <c r="AE20" s="162">
         <f>BFPIaE!AE21</f>
@@ -33813,7 +33827,7 @@
         <v>117969713512540.53</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
@@ -33946,7 +33960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -34079,7 +34093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B23" s="162"/>
       <c r="C23" s="162"/>
       <c r="D23" s="162"/>
@@ -34124,12 +34138,12 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AG24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -34230,7 +34244,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -34363,7 +34377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -34397,7 +34411,7 @@
       </c>
       <c r="I3" s="163">
         <f>BFPIaE!I54</f>
-        <v>187791097922324.62</v>
+        <v>187791097922324.63</v>
       </c>
       <c r="J3" s="163">
         <f>BFPIaE!J54</f>
@@ -34417,7 +34431,7 @@
       </c>
       <c r="N3" s="163">
         <f>BFPIaE!N54</f>
-        <v>232637373175367.12</v>
+        <v>232637373175367.13</v>
       </c>
       <c r="O3" s="163">
         <f>BFPIaE!O54</f>
@@ -34461,7 +34475,7 @@
       </c>
       <c r="Y3" s="163">
         <f>BFPIaE!Y54</f>
-        <v>331299178732064.12</v>
+        <v>331299178732064.13</v>
       </c>
       <c r="Z3" s="163">
         <f>BFPIaE!Z54</f>
@@ -34496,7 +34510,7 @@
         <v>403053219136936.88</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -34629,7 +34643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -34762,7 +34776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -34895,7 +34909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -35028,7 +35042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -35161,7 +35175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -35294,7 +35308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -35427,7 +35441,7 @@
         <v>328527341125.54034</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -35560,7 +35574,7 @@
         <v>1465180432.9002044</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -35693,7 +35707,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -35826,7 +35840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -35959,7 +35973,7 @@
         <v>82096414480.519897</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -36092,7 +36106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -36225,7 +36239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -36358,7 +36372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -36491,7 +36505,7 @@
         <v>586102780086.57971</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -36624,7 +36638,7 @@
         <v>130256450.21654201</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -36670,7 +36684,7 @@
       </c>
       <c r="L20" s="163">
         <f>BFPIaE!L71</f>
-        <v>444290582369335.12</v>
+        <v>444290582369335.13</v>
       </c>
       <c r="M20" s="163">
         <f>BFPIaE!M71</f>
@@ -36706,7 +36720,7 @@
       </c>
       <c r="U20" s="163">
         <f>BFPIaE!U71</f>
-        <v>602714092872700.62</v>
+        <v>602714092872700.63</v>
       </c>
       <c r="V20" s="163">
         <f>BFPIaE!V71</f>
@@ -36714,7 +36728,7 @@
       </c>
       <c r="W20" s="163">
         <f>BFPIaE!W71</f>
-        <v>637919317429000.12</v>
+        <v>637919317429000.13</v>
       </c>
       <c r="X20" s="163">
         <f>BFPIaE!X71</f>
@@ -36734,7 +36748,7 @@
       </c>
       <c r="AB20" s="163">
         <f>BFPIaE!AB71</f>
-        <v>725932378819760.62</v>
+        <v>725932378819760.63</v>
       </c>
       <c r="AC20" s="163">
         <f>BFPIaE!AC71</f>
@@ -36750,14 +36764,14 @@
       </c>
       <c r="AF20" s="163">
         <f>BFPIaE!AF71</f>
-        <v>796342827932365.62</v>
+        <v>796342827932365.63</v>
       </c>
       <c r="AG20" s="163">
         <f>BFPIaE!AG71</f>
         <v>813945440210521.25</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -36890,7 +36904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -37023,7 +37037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B23" s="163"/>
       <c r="C23" s="163"/>
       <c r="D23" s="163"/>
@@ -37057,7 +37071,7 @@
       <c r="AF23" s="163"/>
       <c r="AG23" s="163"/>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B24" s="163"/>
       <c r="C24" s="163"/>
       <c r="D24" s="163"/>
@@ -37102,12 +37116,12 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AG23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -37208,7 +37222,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -37341,7 +37355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -37474,140 +37488,140 @@
         <v>2.5340899115575584E+16</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="163">
         <f>BFPIaE!B30</f>
-        <v>161835607682.80524</v>
+        <v>161835607682805.22</v>
       </c>
       <c r="C4" s="163">
         <f>BFPIaE!C30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="D4" s="163">
         <f>BFPIaE!D30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="E4" s="163">
         <f>BFPIaE!E30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="F4" s="163">
         <f>BFPIaE!F30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="G4" s="163">
         <f>BFPIaE!G30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="H4" s="163">
         <f>BFPIaE!H30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="I4" s="163">
         <f>BFPIaE!I30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="J4" s="163">
         <f>BFPIaE!J30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="K4" s="163">
         <f>BFPIaE!K30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="L4" s="163">
         <f>BFPIaE!L30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="M4" s="163">
         <f>BFPIaE!M30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="N4" s="163">
         <f>BFPIaE!N30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="O4" s="163">
         <f>BFPIaE!O30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="P4" s="163">
         <f>BFPIaE!P30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Q4" s="163">
         <f>BFPIaE!Q30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="R4" s="163">
         <f>BFPIaE!R30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="S4" s="163">
         <f>BFPIaE!S30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="T4" s="163">
         <f>BFPIaE!T30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="U4" s="163">
         <f>BFPIaE!U30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="V4" s="163">
         <f>BFPIaE!V30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="W4" s="163">
         <f>BFPIaE!W30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="X4" s="163">
         <f>BFPIaE!X30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Y4" s="163">
         <f>BFPIaE!Y30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Z4" s="163">
         <f>BFPIaE!Z30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AA4" s="163">
         <f>BFPIaE!AA30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AB4" s="163">
         <f>BFPIaE!AB30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AC4" s="163">
         <f>BFPIaE!AC30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AD4" s="163">
         <f>BFPIaE!AD30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AE4" s="163">
         <f>BFPIaE!AE30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AF4" s="163">
         <f>BFPIaE!AF30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AG4" s="163">
         <f>BFPIaE!AG30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -37740,7 +37754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -37873,7 +37887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -38006,7 +38020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -38139,7 +38153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -38272,7 +38286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -38405,7 +38419,7 @@
         <v>367418701.29870152</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -38538,7 +38552,7 @@
         <v>1648505627.7056284</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -38671,7 +38685,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -38804,7 +38818,7 @@
         <v>543812007.27304566</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -38937,7 +38951,7 @@
         <v>113918718561.81731</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -39070,7 +39084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -39203,7 +39217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -39336,7 +39350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -39469,7 +39483,7 @@
         <v>41644100432.900337</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -39602,7 +39616,7 @@
         <v>5113500952.3809404</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -39735,7 +39749,7 @@
         <v>13893393080</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -39868,7 +39882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -40001,7 +40015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B23" s="163"/>
       <c r="C23" s="163"/>
       <c r="D23" s="163"/>

--- a/InputData/fuels/BFPIaE/BAU Fuel Production Imports and Exports.xlsx
+++ b/InputData/fuels/BFPIaE/BAU Fuel Production Imports and Exports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\fuels\BFPIaE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E271E7-F6D5-4F4B-AE2D-D6D56F059F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2A693B-B327-4B6A-A2BF-D020ED5BF009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="780" windowWidth="30660" windowHeight="21360" activeTab="7" xr2:uid="{95292E05-0ED3-EF4F-AC15-7BB76D2FFA5A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="5" xr2:uid="{95292E05-0ED3-EF4F-AC15-7BB76D2FFA5A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -866,7 +866,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2057,50 +2057,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2108,71 +2114,23 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2186,44 +2144,86 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2560,12 +2560,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD86332E-167D-7340-B188-63BED1427BF8}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="107.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>183</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="38" t="s">
         <v>185</v>
       </c>
@@ -2581,72 +2581,72 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="38" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="51">
+    <row r="15" spans="1:2" ht="48" x14ac:dyDescent="0.4">
       <c r="B15" s="167" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="34">
+    <row r="17" spans="2:2" ht="32" x14ac:dyDescent="0.4">
       <c r="B17" s="166" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="68">
+    <row r="19" spans="2:2" ht="64" x14ac:dyDescent="0.4">
       <c r="B19" s="166" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="51">
+    <row r="20" spans="2:2" ht="48" x14ac:dyDescent="0.4">
       <c r="B20" s="166" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="68">
+    <row r="21" spans="2:2" ht="64" x14ac:dyDescent="0.4">
       <c r="B21" s="166" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="102">
+    <row r="23" spans="2:2" ht="96" x14ac:dyDescent="0.4">
       <c r="B23" s="166" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="136">
+    <row r="25" spans="2:2" ht="128" x14ac:dyDescent="0.4">
       <c r="B25" s="166" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="68">
+    <row r="27" spans="2:2" ht="64" x14ac:dyDescent="0.4">
       <c r="B27" s="166" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="51">
+    <row r="29" spans="2:2" ht="48" x14ac:dyDescent="0.4">
       <c r="B29" s="166" t="s">
         <v>198</v>
       </c>
@@ -2659,13 +2659,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3E92DD-F61D-F349-B35B-C54F2CBA4034}">
   <dimension ref="A1:AH159"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="26" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>35</v>
       </c>
@@ -2673,13 +2673,13 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="25" customHeight="1" thickBot="1">
+    <row r="3" spans="1:25" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="5"/>
-      <c r="B3" s="168"/>
-      <c r="C3" s="169" t="s">
+      <c r="B3" s="221"/>
+      <c r="C3" s="222" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="168"/>
+      <c r="D3" s="221"/>
       <c r="E3" s="5"/>
       <c r="F3" s="10"/>
       <c r="H3" s="26" t="s">
@@ -2709,26 +2709,26 @@
       <c r="Q3" t="s">
         <v>38</v>
       </c>
-      <c r="T3" s="170" t="s">
+      <c r="T3" s="223" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="170"/>
-      <c r="V3" s="171" t="s">
+      <c r="U3" s="223"/>
+      <c r="V3" s="214" t="s">
         <v>42</v>
       </c>
-      <c r="W3" s="172"/>
-      <c r="X3" s="177" t="s">
+      <c r="W3" s="190"/>
+      <c r="X3" s="189" t="s">
         <v>38</v>
       </c>
-      <c r="Y3" s="171"/>
+      <c r="Y3" s="214"/>
     </row>
-    <row r="4" spans="1:25" ht="18" thickTop="1" thickBot="1">
+    <row r="4" spans="1:25" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="168"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="168"/>
+      <c r="B4" s="221"/>
+      <c r="C4" s="222"/>
+      <c r="D4" s="221"/>
       <c r="E4" s="8" t="s">
         <v>24</v>
       </c>
@@ -2747,14 +2747,14 @@
       <c r="K4" s="33">
         <v>55230</v>
       </c>
-      <c r="T4" s="170"/>
-      <c r="U4" s="170"/>
-      <c r="V4" s="173"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="178"/>
-      <c r="Y4" s="173"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="206"/>
+      <c r="W4" s="188"/>
+      <c r="X4" s="187"/>
+      <c r="Y4" s="206"/>
     </row>
-    <row r="5" spans="1:25" ht="24" customHeight="1" thickBot="1">
+    <row r="5" spans="1:25" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="8" t="s">
         <v>26</v>
@@ -2791,16 +2791,16 @@
       <c r="U5" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="V5" s="175" t="s">
+      <c r="V5" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="W5" s="176"/>
-      <c r="X5" s="179" t="s">
+      <c r="W5" s="211"/>
+      <c r="X5" s="210" t="s">
         <v>44</v>
       </c>
-      <c r="Y5" s="175"/>
+      <c r="Y5" s="169"/>
     </row>
-    <row r="6" spans="1:25" ht="18" thickTop="1" thickBot="1">
+    <row r="6" spans="1:25" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="14"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -2856,7 +2856,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="17" customHeight="1" thickBot="1">
+    <row r="7" spans="1:25" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="17">
         <v>2000</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="17" thickBot="1">
+    <row r="8" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="17">
         <v>2001</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="17" thickBot="1">
+    <row r="9" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17">
         <v>2002</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="17" thickBot="1">
+    <row r="10" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17">
         <v>2003</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="17" thickBot="1">
+    <row r="11" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="17">
         <v>2004</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="17" thickBot="1">
+    <row r="12" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="17">
         <v>2005</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="17" thickBot="1">
+    <row r="13" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="17">
         <v>2006</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="17" thickBot="1">
+    <row r="14" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="17">
         <v>2007</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="17" thickBot="1">
+    <row r="15" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="17">
         <v>2008</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="17" thickBot="1">
+    <row r="16" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="17">
         <v>2009</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17" thickBot="1">
+    <row r="17" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="17">
         <v>2010</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>879.5</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A18" s="17">
         <v>2011</v>
       </c>
@@ -3570,12 +3570,12 @@
         <v>42449.21</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="38" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
         <v>54</v>
       </c>
@@ -3598,16 +3598,16 @@
         <v>57</v>
       </c>
       <c r="H24" s="46"/>
-      <c r="I24" s="171" t="s">
+      <c r="I24" s="214" t="s">
         <v>37</v>
       </c>
-      <c r="J24" s="171"/>
-      <c r="K24" s="172"/>
+      <c r="J24" s="214"/>
+      <c r="K24" s="190"/>
       <c r="L24" s="58"/>
-      <c r="M24" s="178"/>
-      <c r="N24" s="173"/>
+      <c r="M24" s="187"/>
+      <c r="N24" s="206"/>
     </row>
-    <row r="25" spans="1:18" ht="17" thickBot="1">
+    <row r="25" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
         <v>2000</v>
       </c>
@@ -3630,14 +3630,14 @@
         <v>834472</v>
       </c>
       <c r="H25" s="46"/>
-      <c r="I25" s="181"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="182"/>
+      <c r="I25" s="215"/>
+      <c r="J25" s="215"/>
+      <c r="K25" s="216"/>
       <c r="L25" s="58"/>
-      <c r="M25" s="178"/>
-      <c r="N25" s="173"/>
+      <c r="M25" s="187"/>
+      <c r="N25" s="206"/>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>2001</v>
       </c>
@@ -3668,12 +3668,12 @@
       <c r="L26" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="196" t="s">
+      <c r="M26" s="202" t="s">
         <v>60</v>
       </c>
-      <c r="N26" s="197"/>
+      <c r="N26" s="217"/>
     </row>
-    <row r="27" spans="1:18" ht="17" thickBot="1">
+    <row r="27" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>2002</v>
       </c>
@@ -3707,9 +3707,9 @@
       </c>
       <c r="L27" s="66"/>
       <c r="M27" s="191"/>
-      <c r="N27" s="198"/>
+      <c r="N27" s="209"/>
     </row>
-    <row r="28" spans="1:18" ht="18" thickTop="1" thickBot="1">
+    <row r="28" spans="1:18" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>2003</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>3761086</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17" thickBot="1">
+    <row r="29" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>2004</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>4347465</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17" thickBot="1">
+    <row r="30" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>2005</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>5030547</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17" thickBot="1">
+    <row r="31" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
         <v>2006</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>5607430</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17" thickBot="1">
+    <row r="32" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
         <v>2007</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>6093138</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="17" thickBot="1">
+    <row r="33" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
         <v>2008</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>6376990</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="17" thickBot="1">
+    <row r="34" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
         <v>2009</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>6642633</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="17" thickBot="1">
+    <row r="35" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
         <v>2010</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>7190871</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="17" thickBot="1">
+    <row r="36" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
         <v>2011</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>7562893</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="17" thickBot="1">
+    <row r="37" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H37" s="70">
         <v>2019</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>7765541</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="17" thickBot="1">
+    <row r="38" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H38" s="79">
         <v>2020</v>
       </c>
@@ -4151,17 +4151,17 @@
         <v>8020514</v>
       </c>
     </row>
-    <row r="41" spans="1:33">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A41" s="38" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:33">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A42" s="38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="26">
+    <row r="43" spans="1:33" ht="20" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -4206,12 +4206,12 @@
       </c>
       <c r="R43" s="58"/>
       <c r="S43" s="58"/>
-      <c r="T43" s="178"/>
-      <c r="U43" s="174"/>
+      <c r="T43" s="187"/>
+      <c r="U43" s="188"/>
       <c r="V43" s="58"/>
       <c r="W43" s="58"/>
-      <c r="X43" s="178"/>
-      <c r="Y43" s="174"/>
+      <c r="X43" s="187"/>
+      <c r="Y43" s="188"/>
       <c r="Z43" s="58"/>
       <c r="AA43" s="65" t="s">
         <v>89</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AD43" s="46"/>
     </row>
-    <row r="44" spans="1:33" ht="26">
+    <row r="44" spans="1:33" ht="20" x14ac:dyDescent="0.4">
       <c r="A44" s="3">
         <v>2000</v>
       </c>
@@ -4274,20 +4274,20 @@
       <c r="S44" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="T44" s="185" t="s">
+      <c r="T44" s="204" t="s">
         <v>87</v>
       </c>
-      <c r="U44" s="186"/>
+      <c r="U44" s="205"/>
       <c r="V44" s="65" t="s">
         <v>72</v>
       </c>
       <c r="W44" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="X44" s="189" t="s">
+      <c r="X44" s="212" t="s">
         <v>67</v>
       </c>
-      <c r="Y44" s="190"/>
+      <c r="Y44" s="213"/>
       <c r="Z44" s="81" t="s">
         <v>68</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="17" thickBot="1">
+    <row r="45" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
         <v>2001</v>
       </c>
@@ -4352,11 +4352,11 @@
       </c>
       <c r="R45" s="66"/>
       <c r="S45" s="66"/>
-      <c r="T45" s="187">
+      <c r="T45" s="219">
         <f>+ JP5</f>
         <v>0</v>
       </c>
-      <c r="U45" s="188"/>
+      <c r="U45" s="220"/>
       <c r="V45" s="66"/>
       <c r="W45" s="66"/>
       <c r="X45" s="191"/>
@@ -4378,7 +4378,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="18" thickTop="1" thickBot="1">
+    <row r="46" spans="1:33" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
         <v>2002</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="W46" s="51">
         <v>107351</v>
       </c>
-      <c r="X46" s="193"/>
+      <c r="X46" s="170"/>
       <c r="Y46" s="31">
         <v>1377</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>108728</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="17" thickBot="1">
+    <row r="47" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
         <v>2003</v>
       </c>
@@ -4538,7 +4538,7 @@
       <c r="W47" s="87">
         <v>119568</v>
       </c>
-      <c r="X47" s="194"/>
+      <c r="X47" s="171"/>
       <c r="Y47" s="31">
         <v>1352</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>120920</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="17" thickBot="1">
+    <row r="48" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
         <v>2004</v>
       </c>
@@ -4634,7 +4634,7 @@
       <c r="W48" s="51">
         <v>122099</v>
       </c>
-      <c r="X48" s="194"/>
+      <c r="X48" s="171"/>
       <c r="Y48" s="31">
         <v>1139</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>123238</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="17" thickBot="1">
+    <row r="49" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
         <v>2005</v>
       </c>
@@ -4730,7 +4730,7 @@
       <c r="W49" s="51">
         <v>122907</v>
       </c>
-      <c r="X49" s="194"/>
+      <c r="X49" s="171"/>
       <c r="Y49" s="84">
         <v>927</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>123834</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="17" thickBot="1">
+    <row r="50" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
         <v>2006</v>
       </c>
@@ -4826,7 +4826,7 @@
       <c r="W50" s="51">
         <v>129502</v>
       </c>
-      <c r="X50" s="194"/>
+      <c r="X50" s="171"/>
       <c r="Y50" s="31">
         <v>1107</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>130609</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="17" thickBot="1">
+    <row r="51" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
         <v>2007</v>
       </c>
@@ -4922,7 +4922,7 @@
       <c r="W51" s="87">
         <v>129306</v>
       </c>
-      <c r="X51" s="194"/>
+      <c r="X51" s="171"/>
       <c r="Y51" s="84">
         <v>972</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>130278</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="17" thickBot="1">
+    <row r="52" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
         <v>2008</v>
       </c>
@@ -5018,7 +5018,7 @@
       <c r="W52" s="51">
         <v>123818</v>
       </c>
-      <c r="X52" s="194"/>
+      <c r="X52" s="171"/>
       <c r="Y52" s="85">
         <v>969</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>124787</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="17" thickBot="1">
+    <row r="53" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
         <v>2009</v>
       </c>
@@ -5114,7 +5114,7 @@
       <c r="W53" s="51">
         <v>133920</v>
       </c>
-      <c r="X53" s="194"/>
+      <c r="X53" s="171"/>
       <c r="Y53" s="85">
         <v>876</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>134796</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="17" thickBot="1">
+    <row r="54" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
         <v>2010</v>
       </c>
@@ -5210,7 +5210,7 @@
       <c r="W54" s="51">
         <v>139783</v>
       </c>
-      <c r="X54" s="194"/>
+      <c r="X54" s="171"/>
       <c r="Y54" s="84">
         <v>714</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>140497</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="17" thickBot="1">
+    <row r="55" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
         <v>2011</v>
       </c>
@@ -5306,7 +5306,7 @@
       <c r="W55" s="92">
         <v>135062</v>
       </c>
-      <c r="X55" s="194"/>
+      <c r="X55" s="171"/>
       <c r="Y55" s="91">
         <v>503</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>135565</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="17" thickBot="1">
+    <row r="56" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -5368,7 +5368,7 @@
       <c r="W56" s="54">
         <v>121197</v>
       </c>
-      <c r="X56" s="195"/>
+      <c r="X56" s="199"/>
       <c r="Y56" s="91">
         <v>820</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>122017</v>
       </c>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
         <v>82</v>
       </c>
@@ -5415,7 +5415,7 @@
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
     </row>
-    <row r="58" spans="1:33" ht="17" thickBot="1">
+    <row r="58" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A58" s="3" t="s">
         <v>22</v>
       </c>
@@ -5448,20 +5448,20 @@
       </c>
       <c r="K58" s="3"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="180" t="s">
+      <c r="N58" s="218" t="s">
         <v>95</v>
       </c>
-      <c r="O58" s="181"/>
-      <c r="P58" s="181"/>
-      <c r="Q58" s="182"/>
+      <c r="O58" s="215"/>
+      <c r="P58" s="215"/>
+      <c r="Q58" s="216"/>
       <c r="R58" s="58"/>
-      <c r="S58" s="183"/>
+      <c r="S58" s="185"/>
       <c r="T58" s="58"/>
       <c r="U58" s="58"/>
       <c r="V58" s="58"/>
       <c r="W58" s="46"/>
     </row>
-    <row r="59" spans="1:33" ht="27" thickBot="1">
+    <row r="59" spans="1:33" ht="20.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
         <v>2000</v>
       </c>
@@ -5511,7 +5511,7 @@
       <c r="R59" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="S59" s="184"/>
+      <c r="S59" s="186"/>
       <c r="T59" s="27" t="s">
         <v>97</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="18" thickTop="1" thickBot="1">
+    <row r="60" spans="1:33" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
         <v>2001</v>
       </c>
@@ -5575,7 +5575,7 @@
       <c r="R60" s="97">
         <v>19189</v>
       </c>
-      <c r="S60" s="193"/>
+      <c r="S60" s="170"/>
       <c r="T60" s="31">
         <v>2027</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>321578</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="17" thickBot="1">
+    <row r="61" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
         <v>2002</v>
       </c>
@@ -5639,7 +5639,7 @@
       <c r="R61" s="98">
         <v>25768</v>
       </c>
-      <c r="S61" s="194"/>
+      <c r="S61" s="171"/>
       <c r="T61" s="83">
         <v>3065</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>342823</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="17" thickBot="1">
+    <row r="62" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
         <v>2003</v>
       </c>
@@ -5703,7 +5703,7 @@
       <c r="R62" s="97">
         <v>18999</v>
       </c>
-      <c r="S62" s="194"/>
+      <c r="S62" s="171"/>
       <c r="T62" s="31">
         <v>2988</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>328115</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="17" thickBot="1">
+    <row r="63" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
         <v>2004</v>
       </c>
@@ -5767,7 +5767,7 @@
       <c r="R63" s="98">
         <v>21726</v>
       </c>
-      <c r="S63" s="194"/>
+      <c r="S63" s="171"/>
       <c r="T63" s="83">
         <v>2697</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>322664</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="17" thickBot="1">
+    <row r="64" spans="1:33" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
         <v>2005</v>
       </c>
@@ -5831,7 +5831,7 @@
       <c r="R64" s="98">
         <v>30460</v>
       </c>
-      <c r="S64" s="194"/>
+      <c r="S64" s="171"/>
       <c r="T64" s="31">
         <v>2529</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>342578</v>
       </c>
     </row>
-    <row r="65" spans="1:32" ht="17" thickBot="1">
+    <row r="65" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
         <v>2006</v>
       </c>
@@ -5895,7 +5895,7 @@
       <c r="R65" s="97">
         <v>27175</v>
       </c>
-      <c r="S65" s="194"/>
+      <c r="S65" s="171"/>
       <c r="T65" s="84">
         <v>0</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>329536</v>
       </c>
     </row>
-    <row r="66" spans="1:32" ht="17" thickBot="1">
+    <row r="66" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
         <v>2007</v>
       </c>
@@ -5959,7 +5959,7 @@
       <c r="R66" s="97">
         <v>15770</v>
       </c>
-      <c r="S66" s="194"/>
+      <c r="S66" s="171"/>
       <c r="T66" s="31">
         <v>2019</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>340289</v>
       </c>
     </row>
-    <row r="67" spans="1:32" ht="17" thickBot="1">
+    <row r="67" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
         <v>2008</v>
       </c>
@@ -6023,7 +6023,7 @@
       <c r="R67" s="97">
         <v>22470</v>
       </c>
-      <c r="S67" s="194"/>
+      <c r="S67" s="171"/>
       <c r="T67" s="31">
         <v>2457</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>356755</v>
       </c>
     </row>
-    <row r="68" spans="1:32" ht="17" thickBot="1">
+    <row r="68" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
         <v>2009</v>
       </c>
@@ -6087,7 +6087,7 @@
       <c r="R68" s="98">
         <v>22656</v>
       </c>
-      <c r="S68" s="194"/>
+      <c r="S68" s="171"/>
       <c r="T68" s="31">
         <v>2787</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>365576</v>
       </c>
     </row>
-    <row r="69" spans="1:32" ht="17" thickBot="1">
+    <row r="69" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
         <v>2010</v>
       </c>
@@ -6151,7 +6151,7 @@
       <c r="R69" s="100">
         <v>23093</v>
       </c>
-      <c r="S69" s="194"/>
+      <c r="S69" s="171"/>
       <c r="T69" s="34">
         <v>2332</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>366779</v>
       </c>
     </row>
-    <row r="70" spans="1:32" ht="17" thickBot="1">
+    <row r="70" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
         <v>2011</v>
       </c>
@@ -6215,7 +6215,7 @@
       <c r="R70" s="100">
         <v>27032</v>
       </c>
-      <c r="S70" s="195"/>
+      <c r="S70" s="199"/>
       <c r="T70" s="34">
         <v>2339</v>
       </c>
@@ -6229,12 +6229,12 @@
         <v>334844</v>
       </c>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A72" s="38" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>22</v>
       </c>
@@ -6277,20 +6277,20 @@
       <c r="Q73" s="58"/>
       <c r="R73" s="58"/>
       <c r="S73" s="58"/>
-      <c r="T73" s="177" t="s">
+      <c r="T73" s="189" t="s">
         <v>100</v>
       </c>
-      <c r="U73" s="172"/>
+      <c r="U73" s="190"/>
       <c r="V73" s="58"/>
-      <c r="W73" s="178"/>
-      <c r="X73" s="174"/>
-      <c r="Y73" s="178"/>
-      <c r="Z73" s="174"/>
+      <c r="W73" s="187"/>
+      <c r="X73" s="188"/>
+      <c r="Y73" s="187"/>
+      <c r="Z73" s="188"/>
       <c r="AA73" s="58"/>
-      <c r="AB73" s="178"/>
-      <c r="AC73" s="173"/>
+      <c r="AB73" s="187"/>
+      <c r="AC73" s="206"/>
     </row>
-    <row r="74" spans="1:32" ht="26">
+    <row r="74" spans="1:32" ht="20" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
         <v>2000</v>
       </c>
@@ -6341,28 +6341,28 @@
       <c r="S74" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="T74" s="177" t="s">
+      <c r="T74" s="189" t="s">
         <v>101</v>
       </c>
-      <c r="U74" s="172"/>
+      <c r="U74" s="190"/>
       <c r="V74" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="W74" s="189" t="s">
+      <c r="W74" s="212" t="s">
         <v>103</v>
       </c>
-      <c r="X74" s="190"/>
-      <c r="Y74" s="185" t="s">
+      <c r="X74" s="213"/>
+      <c r="Y74" s="204" t="s">
         <v>104</v>
       </c>
-      <c r="Z74" s="186"/>
+      <c r="Z74" s="205"/>
       <c r="AA74" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="AB74" s="199" t="s">
+      <c r="AB74" s="207" t="s">
         <v>105</v>
       </c>
-      <c r="AC74" s="200"/>
+      <c r="AC74" s="208"/>
       <c r="AD74" t="s">
         <v>115</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="75" spans="1:32" ht="17" thickBot="1">
+    <row r="75" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
         <v>2001</v>
       </c>
@@ -6418,10 +6418,10 @@
       <c r="Q75" s="66"/>
       <c r="R75" s="66"/>
       <c r="S75" s="66"/>
-      <c r="T75" s="179" t="s">
+      <c r="T75" s="210" t="s">
         <v>102</v>
       </c>
-      <c r="U75" s="176"/>
+      <c r="U75" s="211"/>
       <c r="V75" s="66"/>
       <c r="W75" s="191"/>
       <c r="X75" s="192"/>
@@ -6429,9 +6429,9 @@
       <c r="Z75" s="192"/>
       <c r="AA75" s="66"/>
       <c r="AB75" s="191"/>
-      <c r="AC75" s="198"/>
+      <c r="AC75" s="209"/>
     </row>
-    <row r="76" spans="1:32" ht="18" thickTop="1" thickBot="1">
+    <row r="76" spans="1:32" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
         <v>2002</v>
       </c>
@@ -6491,7 +6491,7 @@
       <c r="V76" s="102">
         <v>381</v>
       </c>
-      <c r="W76" s="193"/>
+      <c r="W76" s="170"/>
       <c r="X76" s="84">
         <v>0</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>10644</v>
       </c>
     </row>
-    <row r="77" spans="1:32" ht="17" thickBot="1">
+    <row r="77" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
         <v>2003</v>
       </c>
@@ -6583,7 +6583,7 @@
       <c r="V77" s="102">
         <v>319</v>
       </c>
-      <c r="W77" s="194"/>
+      <c r="W77" s="171"/>
       <c r="X77" s="84">
         <v>0</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>13573</v>
       </c>
     </row>
-    <row r="78" spans="1:32" ht="17" thickBot="1">
+    <row r="78" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
         <v>2004</v>
       </c>
@@ -6675,7 +6675,7 @@
       <c r="V78" s="102">
         <v>213</v>
       </c>
-      <c r="W78" s="194"/>
+      <c r="W78" s="171"/>
       <c r="X78" s="84">
         <v>0</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>12455</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="17" thickBot="1">
+    <row r="79" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
         <v>2005</v>
       </c>
@@ -6767,7 +6767,7 @@
       <c r="V79" s="103">
         <v>268</v>
       </c>
-      <c r="W79" s="194"/>
+      <c r="W79" s="171"/>
       <c r="X79" s="84">
         <v>0</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>11953</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="17" thickBot="1">
+    <row r="80" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
         <v>2006</v>
       </c>
@@ -6859,7 +6859,7 @@
       <c r="V80" s="103">
         <v>619</v>
       </c>
-      <c r="W80" s="194"/>
+      <c r="W80" s="171"/>
       <c r="X80" s="84">
         <v>0</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>11482</v>
       </c>
     </row>
-    <row r="81" spans="1:34" ht="17" thickBot="1">
+    <row r="81" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
         <v>2007</v>
       </c>
@@ -6951,7 +6951,7 @@
       <c r="V81" s="97">
         <v>1303</v>
       </c>
-      <c r="W81" s="194"/>
+      <c r="W81" s="171"/>
       <c r="X81" s="84">
         <v>0</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>7048</v>
       </c>
     </row>
-    <row r="82" spans="1:34" ht="17" thickBot="1">
+    <row r="82" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
         <v>2008</v>
       </c>
@@ -7043,7 +7043,7 @@
       <c r="V82" s="97">
         <v>3783</v>
       </c>
-      <c r="W82" s="194"/>
+      <c r="W82" s="171"/>
       <c r="X82" s="85">
         <v>66</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>4712</v>
       </c>
     </row>
-    <row r="83" spans="1:34" ht="17" thickBot="1">
+    <row r="83" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
         <v>2009</v>
       </c>
@@ -7135,7 +7135,7 @@
       <c r="V83" s="97">
         <v>7012</v>
       </c>
-      <c r="W83" s="194"/>
+      <c r="W83" s="171"/>
       <c r="X83" s="84">
         <v>0</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>6941</v>
       </c>
     </row>
-    <row r="84" spans="1:34" ht="17" thickBot="1">
+    <row r="84" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
         <v>2010</v>
       </c>
@@ -7227,7 +7227,7 @@
       <c r="V84" s="97">
         <v>9295</v>
       </c>
-      <c r="W84" s="194"/>
+      <c r="W84" s="171"/>
       <c r="X84" s="84">
         <v>15</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>6546</v>
       </c>
     </row>
-    <row r="85" spans="1:34" ht="17" thickBot="1">
+    <row r="85" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
         <v>2011</v>
       </c>
@@ -7319,7 +7319,7 @@
       <c r="V85" s="100">
         <v>7954</v>
       </c>
-      <c r="W85" s="194"/>
+      <c r="W85" s="171"/>
       <c r="X85" s="104">
         <v>46</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="86" spans="1:34" ht="17" thickBot="1">
+    <row r="86" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="Q86" s="56">
         <v>2020</v>
       </c>
@@ -7370,7 +7370,7 @@
       <c r="V86" s="105">
         <v>6485</v>
       </c>
-      <c r="W86" s="195"/>
+      <c r="W86" s="199"/>
       <c r="X86" s="34">
         <v>1247</v>
       </c>
@@ -7402,12 +7402,12 @@
         <v>3219</v>
       </c>
     </row>
-    <row r="87" spans="1:34">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A87" s="38" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="1:34">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A88" s="3" t="s">
         <v>22</v>
       </c>
@@ -7447,14 +7447,14 @@
       <c r="Q88" s="58"/>
       <c r="R88" s="58"/>
       <c r="S88" s="58"/>
-      <c r="T88" s="178"/>
-      <c r="U88" s="174"/>
-      <c r="V88" s="178"/>
-      <c r="W88" s="174"/>
+      <c r="T88" s="187"/>
+      <c r="U88" s="188"/>
+      <c r="V88" s="187"/>
+      <c r="W88" s="188"/>
       <c r="X88" s="58"/>
-      <c r="Y88" s="178"/>
-      <c r="Z88" s="174"/>
-      <c r="AA88" s="206" t="s">
+      <c r="Y88" s="187"/>
+      <c r="Z88" s="188"/>
+      <c r="AA88" s="179" t="s">
         <v>112</v>
       </c>
       <c r="AB88" s="58"/>
@@ -7463,7 +7463,7 @@
       <c r="AE88" s="58"/>
       <c r="AF88" s="46"/>
     </row>
-    <row r="89" spans="1:34" ht="26">
+    <row r="89" spans="1:34" ht="20" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
         <v>2000</v>
       </c>
@@ -7506,22 +7506,22 @@
         <v>108</v>
       </c>
       <c r="S89" s="58"/>
-      <c r="T89" s="203" t="s">
+      <c r="T89" s="200" t="s">
         <v>109</v>
       </c>
-      <c r="U89" s="204"/>
-      <c r="V89" s="196" t="s">
+      <c r="U89" s="201"/>
+      <c r="V89" s="202" t="s">
         <v>110</v>
       </c>
-      <c r="W89" s="205"/>
+      <c r="W89" s="203"/>
       <c r="X89" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="Y89" s="177" t="s">
+      <c r="Y89" s="189" t="s">
         <v>111</v>
       </c>
-      <c r="Z89" s="172"/>
-      <c r="AA89" s="206"/>
+      <c r="Z89" s="190"/>
+      <c r="AA89" s="179"/>
       <c r="AB89" s="65" t="s">
         <v>71</v>
       </c>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AF89" s="46"/>
     </row>
-    <row r="90" spans="1:34" ht="17" thickBot="1">
+    <row r="90" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
         <v>2001</v>
       </c>
@@ -7584,7 +7584,7 @@
       <c r="X90" s="66"/>
       <c r="Y90" s="191"/>
       <c r="Z90" s="192"/>
-      <c r="AA90" s="207"/>
+      <c r="AA90" s="193"/>
       <c r="AB90" s="66"/>
       <c r="AC90" s="96" t="s">
         <v>99</v>
@@ -7603,7 +7603,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="91" spans="1:34" ht="18" thickTop="1" thickBot="1">
+    <row r="91" spans="1:34" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
         <v>2002</v>
       </c>
@@ -7665,7 +7665,7 @@
       <c r="X91" s="103">
         <v>600</v>
       </c>
-      <c r="Y91" s="208"/>
+      <c r="Y91" s="194"/>
       <c r="Z91" s="102">
         <v>0</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:34" ht="17" thickBot="1">
+    <row r="92" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
         <v>2003</v>
       </c>
@@ -7758,7 +7758,7 @@
       <c r="X92" s="102">
         <v>0</v>
       </c>
-      <c r="Y92" s="209"/>
+      <c r="Y92" s="195"/>
       <c r="Z92" s="102">
         <v>0</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:34" ht="17" thickBot="1">
+    <row r="93" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
         <v>2004</v>
       </c>
@@ -7851,7 +7851,7 @@
       <c r="X93" s="102">
         <v>0</v>
       </c>
-      <c r="Y93" s="209"/>
+      <c r="Y93" s="195"/>
       <c r="Z93" s="103">
         <v>60</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="94" spans="1:34" ht="17" thickBot="1">
+    <row r="94" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
         <v>2005</v>
       </c>
@@ -7944,7 +7944,7 @@
       <c r="X94" s="97">
         <v>4319</v>
       </c>
-      <c r="Y94" s="209"/>
+      <c r="Y94" s="195"/>
       <c r="Z94" s="102">
         <v>84</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="95" spans="1:34" ht="17" thickBot="1">
+    <row r="95" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
         <v>2006</v>
       </c>
@@ -8037,7 +8037,7 @@
       <c r="X95" s="97">
         <v>3215</v>
       </c>
-      <c r="Y95" s="209"/>
+      <c r="Y95" s="195"/>
       <c r="Z95" s="102">
         <v>159</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="1:34" ht="17" thickBot="1">
+    <row r="96" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
         <v>2007</v>
       </c>
@@ -8130,7 +8130,7 @@
       <c r="X96" s="97">
         <v>1377</v>
       </c>
-      <c r="Y96" s="209"/>
+      <c r="Y96" s="195"/>
       <c r="Z96" s="102">
         <v>15</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:34" ht="17" thickBot="1">
+    <row r="97" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
         <v>2008</v>
       </c>
@@ -8223,7 +8223,7 @@
       <c r="X97" s="98">
         <v>2167</v>
       </c>
-      <c r="Y97" s="209"/>
+      <c r="Y97" s="195"/>
       <c r="Z97" s="102">
         <v>9</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:34" ht="17" thickBot="1">
+    <row r="98" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
         <v>2009</v>
       </c>
@@ -8316,7 +8316,7 @@
       <c r="X98" s="97">
         <v>2981</v>
       </c>
-      <c r="Y98" s="209"/>
+      <c r="Y98" s="195"/>
       <c r="Z98" s="102">
         <v>4</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:34" ht="17" thickBot="1">
+    <row r="99" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
         <v>2010</v>
       </c>
@@ -8409,7 +8409,7 @@
       <c r="X99" s="97">
         <v>2011</v>
       </c>
-      <c r="Y99" s="209"/>
+      <c r="Y99" s="195"/>
       <c r="Z99" s="102">
         <v>0</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:34" ht="17" thickBot="1">
+    <row r="100" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
         <v>2011</v>
       </c>
@@ -8502,7 +8502,7 @@
       <c r="X100" s="106">
         <v>0</v>
       </c>
-      <c r="Y100" s="209"/>
+      <c r="Y100" s="195"/>
       <c r="Z100" s="106">
         <v>0</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:34" ht="17" thickBot="1">
+    <row r="101" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="Q101" s="56">
         <v>2020</v>
       </c>
@@ -8558,7 +8558,7 @@
       <c r="X101" s="106">
         <v>0</v>
       </c>
-      <c r="Y101" s="210"/>
+      <c r="Y101" s="196"/>
       <c r="Z101" s="106">
         <v>0</v>
       </c>
@@ -8589,19 +8589,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:34">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A104" s="38" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="105" spans="1:34" ht="27" thickBot="1">
+    <row r="105" spans="1:34" ht="20.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A105" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="G105" s="201" t="s">
+      <c r="G105" s="197" t="s">
         <v>140</v>
       </c>
-      <c r="H105" s="202"/>
+      <c r="H105" s="198"/>
       <c r="I105" s="69" t="s">
         <v>141</v>
       </c>
@@ -8609,7 +8609,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:34" s="107" customFormat="1" ht="18" thickTop="1" thickBot="1">
+    <row r="106" spans="1:34" s="107" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A106" s="107" t="s">
         <v>22</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>3407592</v>
       </c>
     </row>
-    <row r="107" spans="1:34" ht="17" thickBot="1">
+    <row r="107" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A107" s="17">
         <v>2000</v>
       </c>
@@ -8661,7 +8661,7 @@
         <v>3256379</v>
       </c>
     </row>
-    <row r="108" spans="1:34" ht="17" thickBot="1">
+    <row r="108" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A108" s="17">
         <v>2001</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>3174639</v>
       </c>
     </row>
-    <row r="109" spans="1:34" ht="17" thickBot="1">
+    <row r="109" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A109" s="17">
         <v>2002</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>3120838</v>
       </c>
     </row>
-    <row r="110" spans="1:34" ht="17" thickBot="1">
+    <row r="110" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A110" s="17">
         <v>2003</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>3175791</v>
       </c>
     </row>
-    <row r="111" spans="1:34" ht="17" thickBot="1">
+    <row r="111" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A111" s="17">
         <v>2004</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>3116142</v>
       </c>
     </row>
-    <row r="112" spans="1:34" ht="17" thickBot="1">
+    <row r="112" spans="1:34" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A112" s="17">
         <v>2005</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>3070239</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="17" thickBot="1">
+    <row r="113" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A113" s="17">
         <v>2006</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>2963184</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="17" thickBot="1">
+    <row r="114" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A114" s="17">
         <v>2007</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>2996802</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="17" thickBot="1">
+    <row r="115" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A115" s="17">
         <v>2008</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>2809668</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="17" thickBot="1">
+    <row r="116" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A116" s="17">
         <v>2009</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>2442831</v>
       </c>
     </row>
-    <row r="117" spans="1:28">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A117" s="17">
         <v>2010</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>3407592</v>
       </c>
     </row>
-    <row r="118" spans="1:28">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A118" s="17">
         <v>2011</v>
       </c>
@@ -8923,18 +8923,18 @@
         <v>3256379</v>
       </c>
     </row>
-    <row r="119" spans="1:28">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A119" s="17"/>
       <c r="B119" s="24"/>
       <c r="C119" s="20"/>
       <c r="D119" s="24"/>
     </row>
-    <row r="120" spans="1:28">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A120" s="38" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="121" spans="1:28">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>22</v>
       </c>
@@ -8949,26 +8949,26 @@
       <c r="J121" s="46"/>
       <c r="K121" s="46"/>
       <c r="L121" s="58"/>
-      <c r="M121" s="206" t="s">
+      <c r="M121" s="179" t="s">
         <v>147</v>
       </c>
-      <c r="N121" s="212" t="s">
+      <c r="N121" s="181" t="s">
         <v>148</v>
       </c>
-      <c r="O121" s="213"/>
-      <c r="P121" s="214"/>
-      <c r="Q121" s="214"/>
-      <c r="R121" s="214"/>
-      <c r="S121" s="214"/>
-      <c r="T121" s="215" t="s">
+      <c r="O121" s="182"/>
+      <c r="P121" s="183"/>
+      <c r="Q121" s="183"/>
+      <c r="R121" s="183"/>
+      <c r="S121" s="183"/>
+      <c r="T121" s="176" t="s">
         <v>148</v>
       </c>
-      <c r="U121" s="216"/>
+      <c r="U121" s="184"/>
       <c r="V121" s="46"/>
       <c r="W121" s="46"/>
       <c r="X121" s="46"/>
     </row>
-    <row r="122" spans="1:28" ht="26">
+    <row r="122" spans="1:28" ht="20" x14ac:dyDescent="0.4">
       <c r="B122" t="s">
         <v>126</v>
       </c>
@@ -8993,15 +8993,15 @@
       </c>
       <c r="K122" s="46"/>
       <c r="L122" s="58"/>
-      <c r="M122" s="206"/>
-      <c r="N122" s="212"/>
-      <c r="O122" s="213"/>
-      <c r="P122" s="214"/>
-      <c r="Q122" s="214"/>
-      <c r="R122" s="214"/>
-      <c r="S122" s="214"/>
-      <c r="T122" s="215"/>
-      <c r="U122" s="216"/>
+      <c r="M122" s="179"/>
+      <c r="N122" s="181"/>
+      <c r="O122" s="182"/>
+      <c r="P122" s="183"/>
+      <c r="Q122" s="183"/>
+      <c r="R122" s="183"/>
+      <c r="S122" s="183"/>
+      <c r="T122" s="176"/>
+      <c r="U122" s="184"/>
       <c r="V122" s="45" t="s">
         <v>149</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="123" spans="1:28" ht="27" thickBot="1">
+    <row r="123" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A123" s="17">
         <v>2000</v>
       </c>
@@ -9041,15 +9041,15 @@
       <c r="L123" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="M123" s="206"/>
-      <c r="N123" s="212"/>
-      <c r="O123" s="213"/>
-      <c r="P123" s="214"/>
-      <c r="Q123" s="214"/>
-      <c r="R123" s="214"/>
-      <c r="S123" s="214"/>
-      <c r="T123" s="215"/>
-      <c r="U123" s="216"/>
+      <c r="M123" s="179"/>
+      <c r="N123" s="181"/>
+      <c r="O123" s="182"/>
+      <c r="P123" s="183"/>
+      <c r="Q123" s="183"/>
+      <c r="R123" s="183"/>
+      <c r="S123" s="183"/>
+      <c r="T123" s="176"/>
+      <c r="U123" s="184"/>
       <c r="V123" s="45" t="s">
         <v>150</v>
       </c>
@@ -9060,7 +9060,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="124" spans="1:28" ht="17" thickBot="1">
+    <row r="124" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A124" s="17">
         <v>2001</v>
       </c>
@@ -9087,20 +9087,20 @@
       <c r="J124" s="63"/>
       <c r="K124" s="63"/>
       <c r="L124" s="116"/>
-      <c r="M124" s="206"/>
-      <c r="N124" s="212"/>
-      <c r="O124" s="213"/>
-      <c r="P124" s="214"/>
-      <c r="Q124" s="214"/>
-      <c r="R124" s="214"/>
-      <c r="S124" s="214"/>
-      <c r="T124" s="215"/>
-      <c r="U124" s="216"/>
+      <c r="M124" s="179"/>
+      <c r="N124" s="181"/>
+      <c r="O124" s="182"/>
+      <c r="P124" s="183"/>
+      <c r="Q124" s="183"/>
+      <c r="R124" s="183"/>
+      <c r="S124" s="183"/>
+      <c r="T124" s="176"/>
+      <c r="U124" s="184"/>
       <c r="V124" s="63"/>
       <c r="W124" s="63"/>
       <c r="X124" s="63"/>
     </row>
-    <row r="125" spans="1:28" ht="17" thickBot="1">
+    <row r="125" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A125" s="17">
         <v>2002</v>
       </c>
@@ -9127,22 +9127,22 @@
       <c r="J125" s="63"/>
       <c r="K125" s="63"/>
       <c r="L125" s="116"/>
-      <c r="M125" s="206"/>
+      <c r="M125" s="179"/>
       <c r="N125" s="119"/>
       <c r="O125" s="58"/>
-      <c r="P125" s="183"/>
+      <c r="P125" s="185"/>
       <c r="Q125" s="58"/>
       <c r="R125" s="46"/>
       <c r="S125" s="46"/>
       <c r="T125" s="58"/>
-      <c r="U125" s="206" t="s">
+      <c r="U125" s="179" t="s">
         <v>158</v>
       </c>
       <c r="V125" s="63"/>
       <c r="W125" s="63"/>
       <c r="X125" s="63"/>
     </row>
-    <row r="126" spans="1:28" ht="17" thickBot="1">
+    <row r="126" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A126" s="17">
         <v>2003</v>
       </c>
@@ -9171,14 +9171,14 @@
       <c r="J126" s="63"/>
       <c r="K126" s="63"/>
       <c r="L126" s="116"/>
-      <c r="M126" s="206"/>
+      <c r="M126" s="179"/>
       <c r="N126" s="81" t="s">
         <v>149</v>
       </c>
       <c r="O126" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="P126" s="183"/>
+      <c r="P126" s="185"/>
       <c r="Q126" s="94" t="s">
         <v>154</v>
       </c>
@@ -9191,12 +9191,12 @@
       <c r="T126" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="U126" s="206"/>
+      <c r="U126" s="179"/>
       <c r="V126" s="63"/>
       <c r="W126" s="63"/>
       <c r="X126" s="63"/>
     </row>
-    <row r="127" spans="1:28" ht="17" thickBot="1">
+    <row r="127" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A127" s="17">
         <v>2004</v>
       </c>
@@ -9223,19 +9223,19 @@
       <c r="J127" s="118"/>
       <c r="K127" s="118"/>
       <c r="L127" s="117"/>
-      <c r="M127" s="211"/>
+      <c r="M127" s="180"/>
       <c r="N127" s="120" t="s">
         <v>153</v>
       </c>
       <c r="O127" s="120" t="s">
         <v>153</v>
       </c>
-      <c r="P127" s="183"/>
+      <c r="P127" s="185"/>
       <c r="Q127" s="117"/>
       <c r="R127" s="118"/>
       <c r="S127" s="118"/>
       <c r="T127" s="117"/>
-      <c r="U127" s="211"/>
+      <c r="U127" s="180"/>
       <c r="V127" s="118"/>
       <c r="W127" s="118"/>
       <c r="X127" s="118"/>
@@ -9252,7 +9252,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="128" spans="1:28" ht="17" thickBot="1">
+    <row r="128" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A128" s="17">
         <v>2005</v>
       </c>
@@ -9282,19 +9282,19 @@
       <c r="M128" s="58"/>
       <c r="N128" s="58"/>
       <c r="O128" s="58"/>
-      <c r="P128" s="183"/>
+      <c r="P128" s="185"/>
       <c r="Q128" s="58"/>
       <c r="R128" s="46"/>
       <c r="S128" s="46"/>
       <c r="T128" s="58"/>
       <c r="U128" s="58"/>
       <c r="V128" s="46"/>
-      <c r="W128" s="217" t="s">
+      <c r="W128" s="168" t="s">
         <v>160</v>
       </c>
       <c r="X128" s="46"/>
     </row>
-    <row r="129" spans="1:28" ht="17" thickBot="1">
+    <row r="129" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A129" s="17">
         <v>2006</v>
       </c>
@@ -9338,7 +9338,7 @@
       <c r="O129" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="P129" s="184"/>
+      <c r="P129" s="186"/>
       <c r="Q129" s="96" t="s">
         <v>159</v>
       </c>
@@ -9357,12 +9357,12 @@
       <c r="V129" s="47" t="s">
         <v>159</v>
       </c>
-      <c r="W129" s="175"/>
+      <c r="W129" s="169"/>
       <c r="X129" s="121" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="130" spans="1:28" ht="18" thickTop="1" thickBot="1">
+    <row r="130" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A130" s="17">
         <v>2007</v>
       </c>
@@ -9408,7 +9408,7 @@
       <c r="O130" s="125">
         <v>20866</v>
       </c>
-      <c r="P130" s="193"/>
+      <c r="P130" s="170"/>
       <c r="Q130" s="124">
         <v>34038</v>
       </c>
@@ -9450,7 +9450,7 @@
         <v>228606.22396603454</v>
       </c>
     </row>
-    <row r="131" spans="1:28" ht="17" thickBot="1">
+    <row r="131" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A131" s="17">
         <v>2008</v>
       </c>
@@ -9496,7 +9496,7 @@
       <c r="O131" s="131">
         <v>14289</v>
       </c>
-      <c r="P131" s="194"/>
+      <c r="P131" s="171"/>
       <c r="Q131" s="126">
         <v>37476</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>207689.09055137934</v>
       </c>
     </row>
-    <row r="132" spans="1:28" ht="17" thickBot="1">
+    <row r="132" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A132" s="17">
         <v>2009</v>
       </c>
@@ -9584,7 +9584,7 @@
       <c r="O132" s="131">
         <v>28141</v>
       </c>
-      <c r="P132" s="194"/>
+      <c r="P132" s="171"/>
       <c r="Q132" s="124">
         <v>39782</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>172153.40889672414</v>
       </c>
     </row>
-    <row r="133" spans="1:28" ht="17" thickBot="1">
+    <row r="133" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A133" s="17">
         <v>2010</v>
       </c>
@@ -9672,7 +9672,7 @@
       <c r="O133" s="125">
         <v>26647</v>
       </c>
-      <c r="P133" s="194"/>
+      <c r="P133" s="171"/>
       <c r="Q133" s="126">
         <v>38866</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>181963.32992655176</v>
       </c>
     </row>
-    <row r="134" spans="1:28" ht="17" thickBot="1">
+    <row r="134" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A134" s="17">
         <v>2011</v>
       </c>
@@ -9760,7 +9760,7 @@
       <c r="O134" s="131">
         <v>29757</v>
       </c>
-      <c r="P134" s="194"/>
+      <c r="P134" s="171"/>
       <c r="Q134" s="124">
         <v>41992</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>171909.49223500001</v>
       </c>
     </row>
-    <row r="135" spans="1:28" ht="17" thickBot="1">
+    <row r="135" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H135" s="122">
         <v>2015</v>
       </c>
@@ -9827,7 +9827,7 @@
       <c r="O135" s="131">
         <v>24801</v>
       </c>
-      <c r="P135" s="194"/>
+      <c r="P135" s="171"/>
       <c r="Q135" s="124">
         <v>47384</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>180273.10103500003</v>
       </c>
     </row>
-    <row r="136" spans="1:28" ht="17" thickBot="1">
+    <row r="136" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>130</v>
       </c>
@@ -9900,7 +9900,7 @@
       <c r="O136" s="131">
         <v>24805</v>
       </c>
-      <c r="P136" s="194"/>
+      <c r="P136" s="171"/>
       <c r="Q136" s="124">
         <v>105138</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>191215.04051327589</v>
       </c>
     </row>
-    <row r="137" spans="1:28" ht="17" thickBot="1">
+    <row r="137" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>131</v>
       </c>
@@ -9973,7 +9973,7 @@
       <c r="O137" s="131">
         <v>22418</v>
       </c>
-      <c r="P137" s="194"/>
+      <c r="P137" s="171"/>
       <c r="Q137" s="124">
         <v>50033</v>
       </c>
@@ -10015,7 +10015,7 @@
         <v>181684.91566931037</v>
       </c>
     </row>
-    <row r="138" spans="1:28" ht="17" thickBot="1">
+    <row r="138" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H138" s="122">
         <v>2018</v>
       </c>
@@ -10040,7 +10040,7 @@
       <c r="O138" s="131">
         <v>29842</v>
       </c>
-      <c r="P138" s="194"/>
+      <c r="P138" s="171"/>
       <c r="Q138" s="124">
         <v>42322</v>
       </c>
@@ -10082,7 +10082,7 @@
         <v>180173.76245862071</v>
       </c>
     </row>
-    <row r="139" spans="1:28" ht="17" thickBot="1">
+    <row r="139" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>164</v>
       </c>
@@ -10113,7 +10113,7 @@
       <c r="O139" s="139">
         <v>20167</v>
       </c>
-      <c r="P139" s="194"/>
+      <c r="P139" s="171"/>
       <c r="Q139" s="137">
         <v>40917</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>155360.19476500002</v>
       </c>
     </row>
-    <row r="140" spans="1:28" ht="17" thickBot="1">
+    <row r="140" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="H140" s="142">
         <v>2020</v>
       </c>
@@ -10180,7 +10180,7 @@
       <c r="O140" s="139">
         <v>18468</v>
       </c>
-      <c r="P140" s="218"/>
+      <c r="P140" s="172"/>
       <c r="Q140" s="137">
         <v>13897</v>
       </c>
@@ -10222,34 +10222,34 @@
         <v>145904.43348810347</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A146" s="38" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A147" s="58"/>
-      <c r="B147" s="219" t="s">
+      <c r="B147" s="173" t="s">
         <v>167</v>
       </c>
-      <c r="C147" s="219" t="s">
+      <c r="C147" s="173" t="s">
         <v>168</v>
       </c>
-      <c r="D147" s="221" t="s">
+      <c r="D147" s="175" t="s">
         <v>169</v>
       </c>
-      <c r="E147" s="215"/>
+      <c r="E147" s="176"/>
     </row>
-    <row r="148" spans="1:5" ht="17" thickBot="1">
+    <row r="148" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A148" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B148" s="220"/>
-      <c r="C148" s="220"/>
-      <c r="D148" s="222"/>
-      <c r="E148" s="223"/>
+      <c r="B148" s="174"/>
+      <c r="C148" s="174"/>
+      <c r="D148" s="177"/>
+      <c r="E148" s="178"/>
     </row>
-    <row r="149" spans="1:5" ht="18" thickTop="1" thickBot="1">
+    <row r="149" spans="1:5" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A149" s="145">
         <v>2010</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="17" thickBot="1">
+    <row r="150" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A150" s="145">
         <v>2011</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="17" thickBot="1">
+    <row r="151" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A151" s="145">
         <v>2012</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="17" thickBot="1">
+    <row r="152" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A152" s="145">
         <v>2013</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="17" thickBot="1">
+    <row r="153" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A153" s="145">
         <v>2014</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="17" thickBot="1">
+    <row r="154" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A154" s="145">
         <v>2015</v>
       </c>
@@ -10351,7 +10351,7 @@
         <v>18953</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="17" thickBot="1">
+    <row r="155" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A155" s="145">
         <v>2016</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="17" thickBot="1">
+    <row r="156" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A156" s="145">
         <v>2017</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>24786</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="17" thickBot="1">
+    <row r="157" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A157" s="145">
         <v>2018</v>
       </c>
@@ -10402,7 +10402,7 @@
         <v>25670</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="17" thickBot="1">
+    <row r="158" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A158" s="145">
         <v>2019</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>26277</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="17" thickBot="1">
+    <row r="159" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A159" s="145">
         <v>2020</v>
       </c>
@@ -10438,49 +10438,12 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="W128:W129"/>
-    <mergeCell ref="P130:P140"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:C148"/>
-    <mergeCell ref="D147:E148"/>
-    <mergeCell ref="M121:M127"/>
-    <mergeCell ref="N121:O124"/>
-    <mergeCell ref="P121:R124"/>
-    <mergeCell ref="S121:S124"/>
-    <mergeCell ref="T121:U124"/>
-    <mergeCell ref="P125:P129"/>
-    <mergeCell ref="U125:U127"/>
-    <mergeCell ref="Y88:Z88"/>
-    <mergeCell ref="Y89:Z89"/>
-    <mergeCell ref="Y90:Z90"/>
-    <mergeCell ref="AA88:AA90"/>
-    <mergeCell ref="Y91:Y101"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="W76:W86"/>
-    <mergeCell ref="T88:U88"/>
-    <mergeCell ref="T89:U89"/>
-    <mergeCell ref="T90:U90"/>
-    <mergeCell ref="V88:W88"/>
-    <mergeCell ref="V89:W89"/>
-    <mergeCell ref="V90:W90"/>
-    <mergeCell ref="Y73:Z73"/>
-    <mergeCell ref="Y74:Z74"/>
-    <mergeCell ref="Y75:Z75"/>
-    <mergeCell ref="AB73:AC73"/>
-    <mergeCell ref="AB74:AC74"/>
-    <mergeCell ref="AB75:AC75"/>
-    <mergeCell ref="S60:S70"/>
-    <mergeCell ref="T73:U73"/>
-    <mergeCell ref="T74:U74"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="W73:X73"/>
-    <mergeCell ref="W74:X74"/>
-    <mergeCell ref="W75:X75"/>
-    <mergeCell ref="I24:K25"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="T3:U4"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="V4:W4"/>
     <mergeCell ref="V5:W5"/>
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="X4:Y4"/>
@@ -10494,12 +10457,49 @@
     <mergeCell ref="X44:Y44"/>
     <mergeCell ref="X45:Y45"/>
     <mergeCell ref="X46:X56"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="T3:U4"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="I24:K25"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="S60:S70"/>
+    <mergeCell ref="T73:U73"/>
+    <mergeCell ref="T74:U74"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="W73:X73"/>
+    <mergeCell ref="W74:X74"/>
+    <mergeCell ref="W75:X75"/>
+    <mergeCell ref="Y73:Z73"/>
+    <mergeCell ref="Y74:Z74"/>
+    <mergeCell ref="Y75:Z75"/>
+    <mergeCell ref="AB73:AC73"/>
+    <mergeCell ref="AB74:AC74"/>
+    <mergeCell ref="AB75:AC75"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="W76:W86"/>
+    <mergeCell ref="T88:U88"/>
+    <mergeCell ref="T89:U89"/>
+    <mergeCell ref="T90:U90"/>
+    <mergeCell ref="V88:W88"/>
+    <mergeCell ref="V89:W89"/>
+    <mergeCell ref="V90:W90"/>
+    <mergeCell ref="Y88:Z88"/>
+    <mergeCell ref="Y89:Z89"/>
+    <mergeCell ref="Y90:Z90"/>
+    <mergeCell ref="AA88:AA90"/>
+    <mergeCell ref="Y91:Y101"/>
+    <mergeCell ref="M121:M127"/>
+    <mergeCell ref="N121:O124"/>
+    <mergeCell ref="P121:R124"/>
+    <mergeCell ref="S121:S124"/>
+    <mergeCell ref="T121:U124"/>
+    <mergeCell ref="P125:P129"/>
+    <mergeCell ref="U125:U127"/>
+    <mergeCell ref="W128:W129"/>
+    <mergeCell ref="P130:P140"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:C148"/>
+    <mergeCell ref="D147:E148"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10508,7 +10508,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4A1704-7464-DB42-ADE9-F63DB066BC0B}">
   <dimension ref="A1:AZ81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="48.1640625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -10517,7 +10517,7 @@
     <col min="14" max="22" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A1" s="146" t="s">
         <v>29</v>
       </c>
@@ -10675,7 +10675,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A2" s="146" t="s">
         <v>1</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:52">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A3" s="146" t="s">
         <v>36</v>
       </c>
@@ -11051,7 +11051,7 @@
         <v>1425398165.242424</v>
       </c>
     </row>
-    <row r="4" spans="1:52">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A4" s="146" t="s">
         <v>133</v>
       </c>
@@ -11239,7 +11239,7 @@
         <v>2873408.359307359</v>
       </c>
     </row>
-    <row r="5" spans="1:52">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A5" s="146" t="s">
         <v>4</v>
       </c>
@@ -11427,7 +11427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:52">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A6" s="146" t="s">
         <v>5</v>
       </c>
@@ -11615,7 +11615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A7" s="146" t="s">
         <v>6</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:52">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A8" s="146" t="s">
         <v>7</v>
       </c>
@@ -11991,7 +11991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A9" s="146" t="s">
         <v>8</v>
       </c>
@@ -12179,7 +12179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:52">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A10" s="146" t="s">
         <v>137</v>
       </c>
@@ -12367,7 +12367,7 @@
         <v>96719.874458874576</v>
       </c>
     </row>
-    <row r="11" spans="1:52">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A11" s="146" t="s">
         <v>138</v>
       </c>
@@ -12555,7 +12555,7 @@
         <v>194630.45454545459</v>
       </c>
     </row>
-    <row r="12" spans="1:52">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A12" s="146" t="s">
         <v>11</v>
       </c>
@@ -12743,7 +12743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:52">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A13" s="146" t="s">
         <v>171</v>
       </c>
@@ -12911,7 +12911,7 @@
         <v>29628.045454545412</v>
       </c>
     </row>
-    <row r="14" spans="1:52">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A14" s="146" t="s">
         <v>114</v>
       </c>
@@ -13076,7 +13076,7 @@
         <v>1657.1650562770665</v>
       </c>
     </row>
-    <row r="15" spans="1:52">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A15" s="146" t="s">
         <v>14</v>
       </c>
@@ -13264,7 +13264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:52">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A16" s="146" t="s">
         <v>15</v>
       </c>
@@ -13452,7 +13452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:52">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A17" s="146" t="s">
         <v>16</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:52">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A18" s="146" t="s">
         <v>51</v>
       </c>
@@ -13819,7 +13819,7 @@
         <v>9803.0688311681151</v>
       </c>
     </row>
-    <row r="19" spans="1:52">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A19" s="146" t="s">
         <v>139</v>
       </c>
@@ -13982,7 +13982,7 @@
         <v>733.15367965353653</v>
       </c>
     </row>
-    <row r="20" spans="1:52">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A20" s="146" t="s">
         <v>59</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>2385989.4632034618</v>
       </c>
     </row>
-    <row r="21" spans="1:52">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A21" s="146" t="s">
         <v>20</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:52">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A22" s="146" t="s">
         <v>21</v>
       </c>
@@ -14546,7 +14546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:52">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A23" s="149"/>
       <c r="B23" s="149"/>
       <c r="C23" s="149"/>
@@ -14591,7 +14591,7 @@
       <c r="AP23" s="149"/>
       <c r="AQ23" s="149"/>
     </row>
-    <row r="24" spans="1:52">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A24" s="149"/>
       <c r="B24" s="149"/>
       <c r="C24" s="149"/>
@@ -14636,7 +14636,7 @@
       <c r="AP24" s="149"/>
       <c r="AQ24" s="149"/>
     </row>
-    <row r="25" spans="1:52">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A25" s="149"/>
       <c r="B25" s="149"/>
       <c r="C25" s="149"/>
@@ -14681,7 +14681,7 @@
       <c r="AP25" s="149"/>
       <c r="AQ25" s="149"/>
     </row>
-    <row r="26" spans="1:52">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A26" s="146" t="s">
         <v>30</v>
       </c>
@@ -14839,7 +14839,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="27" spans="1:52">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A27" s="146" t="s">
         <v>1</v>
       </c>
@@ -15027,7 +15027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:52">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A28" s="146" t="s">
         <v>36</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>1021634133.9307404</v>
       </c>
     </row>
-    <row r="29" spans="1:52">
+    <row r="29" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A29" s="146" t="s">
         <v>132</v>
       </c>
@@ -15373,7 +15373,7 @@
         <v>145904.43348810347</v>
       </c>
     </row>
-    <row r="30" spans="1:52">
+    <row r="30" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A30" s="146" t="s">
         <v>4</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:52">
+    <row r="31" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A31" s="146" t="s">
         <v>5</v>
       </c>
@@ -15749,7 +15749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:52">
+    <row r="32" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A32" s="146" t="s">
         <v>6</v>
       </c>
@@ -15937,7 +15937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:52">
+    <row r="33" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A33" s="146" t="s">
         <v>7</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:52">
+    <row r="34" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A34" s="146" t="s">
         <v>8</v>
       </c>
@@ -16313,7 +16313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:52">
+    <row r="35" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A35" s="146" t="s">
         <v>137</v>
       </c>
@@ -16501,7 +16501,7 @@
         <v>63.348051948051989</v>
       </c>
     </row>
-    <row r="36" spans="1:52">
+    <row r="36" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A36" s="146" t="s">
         <v>138</v>
       </c>
@@ -16689,7 +16689,7 @@
         <v>284.22510822510833</v>
       </c>
     </row>
-    <row r="37" spans="1:52">
+    <row r="37" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A37" s="146" t="s">
         <v>11</v>
       </c>
@@ -16877,7 +16877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:52">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A38" s="146" t="s">
         <v>171</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>15.818181818191078</v>
       </c>
     </row>
-    <row r="39" spans="1:52">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A39" s="146" t="s">
         <v>116</v>
       </c>
@@ -17224,7 +17224,7 @@
         <v>3313.6212121211865</v>
       </c>
     </row>
-    <row r="40" spans="1:52">
+    <row r="40" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A40" s="146" t="s">
         <v>14</v>
       </c>
@@ -17412,7 +17412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:52">
+    <row r="41" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A41" s="146" t="s">
         <v>15</v>
       </c>
@@ -17600,7 +17600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:52">
+    <row r="42" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A42" s="146" t="s">
         <v>16</v>
       </c>
@@ -17758,7 +17758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:52">
+    <row r="43" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A43" s="146" t="s">
         <v>51</v>
       </c>
@@ -17921,7 +17921,7 @@
         <v>7180.0173160172999</v>
       </c>
     </row>
-    <row r="44" spans="1:52">
+    <row r="44" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A44" s="146" t="s">
         <v>139</v>
       </c>
@@ -18109,7 +18109,7 @@
         <v>881.63809523809323</v>
       </c>
     </row>
-    <row r="45" spans="1:52">
+    <row r="45" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A45" s="146" t="s">
         <v>59</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:52">
+    <row r="46" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A46" s="146" t="s">
         <v>20</v>
       </c>
@@ -18455,7 +18455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:52">
+    <row r="47" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A47" s="146" t="s">
         <v>21</v>
       </c>
@@ -18643,7 +18643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:52">
+    <row r="48" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A48" s="149"/>
       <c r="B48" s="149"/>
       <c r="C48" s="149"/>
@@ -18688,7 +18688,7 @@
       <c r="AP48" s="149"/>
       <c r="AQ48" s="149"/>
     </row>
-    <row r="49" spans="1:52">
+    <row r="49" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A49" s="149"/>
       <c r="B49" s="149"/>
       <c r="C49" s="149"/>
@@ -18733,7 +18733,7 @@
       <c r="AP49" s="149"/>
       <c r="AQ49" s="149"/>
     </row>
-    <row r="50" spans="1:52">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A50" s="149"/>
       <c r="B50" s="149"/>
       <c r="C50" s="149"/>
@@ -18778,7 +18778,7 @@
       <c r="AP50" s="149"/>
       <c r="AQ50" s="149"/>
     </row>
-    <row r="51" spans="1:52">
+    <row r="51" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A51" s="146" t="s">
         <v>31</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="52" spans="1:52">
+    <row r="52" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A52" s="146" t="s">
         <v>1</v>
       </c>
@@ -19124,7 +19124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:52">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A53" s="146" t="s">
         <v>36</v>
       </c>
@@ -19312,7 +19312,7 @@
         <v>16249341.611082315</v>
       </c>
     </row>
-    <row r="54" spans="1:52">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A54" s="146" t="s">
         <v>3</v>
       </c>
@@ -19500,7 +19500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:52">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A55" s="146" t="s">
         <v>4</v>
       </c>
@@ -19688,7 +19688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:52">
+    <row r="56" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A56" s="146" t="s">
         <v>5</v>
       </c>
@@ -19876,7 +19876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:52">
+    <row r="57" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A57" s="146" t="s">
         <v>6</v>
       </c>
@@ -20064,7 +20064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:52">
+    <row r="58" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A58" s="146" t="s">
         <v>7</v>
       </c>
@@ -20252,7 +20252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:52">
+    <row r="59" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A59" s="146" t="s">
         <v>8</v>
       </c>
@@ -20440,7 +20440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:52">
+    <row r="60" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A60" s="146" t="s">
         <v>134</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>56642.645021644887</v>
       </c>
     </row>
-    <row r="61" spans="1:52">
+    <row r="61" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A61" s="146" t="s">
         <v>135</v>
       </c>
@@ -20799,7 +20799,7 @@
         <v>252.61731601727661</v>
       </c>
     </row>
-    <row r="62" spans="1:52">
+    <row r="62" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A62" s="146" t="s">
         <v>11</v>
       </c>
@@ -20987,7 +20987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:52">
+    <row r="63" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A63" s="146" t="s">
         <v>171</v>
       </c>
@@ -21155,7 +21155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:52">
+    <row r="64" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A64" s="146" t="s">
         <v>114</v>
       </c>
@@ -21343,7 +21343,7 @@
         <v>2387.9870129870251</v>
       </c>
     </row>
-    <row r="65" spans="1:52">
+    <row r="65" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A65" s="146" t="s">
         <v>14</v>
       </c>
@@ -21531,7 +21531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:52">
+    <row r="66" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A66" s="146" t="s">
         <v>15</v>
       </c>
@@ -21719,7 +21719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:52">
+    <row r="67" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A67" s="146" t="s">
         <v>16</v>
       </c>
@@ -21907,7 +21907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:52">
+    <row r="68" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A68" s="146" t="s">
         <v>51</v>
       </c>
@@ -22095,7 +22095,7 @@
         <v>101052.20346320339</v>
       </c>
     </row>
-    <row r="69" spans="1:52">
+    <row r="69" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A69" s="146" t="s">
         <v>136</v>
       </c>
@@ -22255,7 +22255,7 @@
         <v>22.458008658024482</v>
       </c>
     </row>
-    <row r="70" spans="1:52">
+    <row r="70" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A70" s="146" t="s">
         <v>59</v>
       </c>
@@ -22443,7 +22443,7 @@
         <v>16462405.359307408</v>
       </c>
     </row>
-    <row r="71" spans="1:52">
+    <row r="71" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A71" s="146" t="s">
         <v>20</v>
       </c>
@@ -22631,7 +22631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:52">
+    <row r="72" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A72" s="146" t="s">
         <v>21</v>
       </c>
@@ -22819,7 +22819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:52">
+    <row r="73" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A73" s="149"/>
       <c r="B73" s="149"/>
       <c r="C73" s="149"/>
@@ -22864,7 +22864,7 @@
       <c r="AP73" s="149"/>
       <c r="AQ73" s="149"/>
     </row>
-    <row r="74" spans="1:52">
+    <row r="74" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A74" s="149"/>
       <c r="B74" s="149"/>
       <c r="C74" s="149"/>
@@ -22909,7 +22909,7 @@
       <c r="AP74" s="149"/>
       <c r="AQ74" s="149"/>
     </row>
-    <row r="75" spans="1:52">
+    <row r="75" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A75" s="149"/>
       <c r="B75" s="149"/>
       <c r="C75" s="149"/>
@@ -22954,7 +22954,7 @@
       <c r="AP75" s="149"/>
       <c r="AQ75" s="149"/>
     </row>
-    <row r="76" spans="1:52" ht="68" customHeight="1">
+    <row r="76" spans="1:52" ht="68" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="153"/>
       <c r="B76" s="154" t="s">
         <v>172</v>
@@ -23001,7 +23001,7 @@
       <c r="AP76" s="149"/>
       <c r="AQ76" s="149"/>
     </row>
-    <row r="77" spans="1:52">
+    <row r="77" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A77" s="149"/>
       <c r="B77" s="149"/>
       <c r="C77" s="149"/>
@@ -23046,7 +23046,7 @@
       <c r="AP77" s="149"/>
       <c r="AQ77" s="149"/>
     </row>
-    <row r="78" spans="1:52" ht="71" customHeight="1">
+    <row r="78" spans="1:52" ht="71" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="156"/>
       <c r="B78" s="159" t="s">
         <v>173</v>
@@ -23093,7 +23093,7 @@
       <c r="AP78" s="149"/>
       <c r="AQ78" s="149"/>
     </row>
-    <row r="79" spans="1:52">
+    <row r="79" spans="1:52" x14ac:dyDescent="0.4">
       <c r="A79" s="149"/>
       <c r="B79" s="149"/>
       <c r="C79" s="149"/>
@@ -23138,7 +23138,7 @@
       <c r="AP79" s="149"/>
       <c r="AQ79" s="149"/>
     </row>
-    <row r="80" spans="1:52" ht="78" customHeight="1">
+    <row r="80" spans="1:52" ht="78" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="158"/>
       <c r="B80" s="159" t="s">
         <v>174</v>
@@ -23185,7 +23185,7 @@
       <c r="AP80" s="149"/>
       <c r="AQ80" s="149"/>
     </row>
-    <row r="81" spans="1:43">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.4">
       <c r="A81" s="149"/>
       <c r="B81" s="149"/>
       <c r="C81" s="149"/>
@@ -23238,25 +23238,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DC08D71-B78F-774E-8A28-46D984F940EA}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>175</v>
       </c>
       <c r="B2" s="161">
-        <v>0.17960000000000001</v>
+        <v>179.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>177</v>
       </c>
@@ -23264,7 +23264,7 @@
         <v>4.2766000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>178</v>
       </c>
@@ -23272,7 +23272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>179</v>
       </c>
@@ -23280,7 +23280,7 @@
         <v>5.9273999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>180</v>
       </c>
@@ -23288,10 +23288,10 @@
         <v>8.5245999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B7" s="162"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="38" t="s">
         <v>182</v>
       </c>
@@ -23299,21 +23299,21 @@
         <v>5800000</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="38" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>175</v>
       </c>
       <c r="B12" s="162">
         <f>B2*$B$8</f>
-        <v>1041680</v>
+        <v>1041680000</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>177</v>
       </c>
@@ -23322,7 +23322,7 @@
         <v>24804280</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>178</v>
       </c>
@@ -23331,7 +23331,7 @@
         <v>5800000</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>179</v>
       </c>
@@ -23340,7 +23340,7 @@
         <v>34378920</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>180</v>
       </c>
@@ -23357,7 +23357,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B189A75B-B529-A24C-89B4-38ED16AFA0A9}">
   <dimension ref="A1:AH73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
@@ -23365,12 +23365,12 @@
     <col min="4" max="33" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -23471,7 +23471,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -23604,7 +23604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -23737,140 +23737,140 @@
         <v>3.5355975202159352E+16</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="164">
         <f>'Data Computation and Processing'!U4*Conversion!$B$12</f>
-        <v>2926774962240</v>
+        <v>2926774962240000</v>
       </c>
       <c r="C5" s="164">
         <f>'Data Computation and Processing'!V4*Conversion!$B$12</f>
-        <v>2544648196080</v>
+        <v>2544648196080000</v>
       </c>
       <c r="D5" s="164">
         <f>'Data Computation and Processing'!W4*Conversion!$B$12</f>
-        <v>3093384465846.0942</v>
+        <v>3093384465846094.5</v>
       </c>
       <c r="E5" s="164">
         <f>'Data Computation and Processing'!X4*Conversion!$B$12</f>
-        <v>3089928864255.6533</v>
+        <v>3089928864255653.5</v>
       </c>
       <c r="F5" s="164">
         <f>'Data Computation and Processing'!Y4*Conversion!$B$12</f>
-        <v>3086473262665.2114</v>
+        <v>3086473262665211.5</v>
       </c>
       <c r="G5" s="164">
         <f>'Data Computation and Processing'!Z4*Conversion!$B$12</f>
-        <v>3083017661074.7705</v>
+        <v>3083017661074770.5</v>
       </c>
       <c r="H5" s="164">
         <f>'Data Computation and Processing'!AA4*Conversion!$B$12</f>
-        <v>3079562059484.3281</v>
+        <v>3079562059484328.5</v>
       </c>
       <c r="I5" s="164">
         <f>'Data Computation and Processing'!AB4*Conversion!$B$12</f>
-        <v>3076106457893.8872</v>
+        <v>3076106457893887.5</v>
       </c>
       <c r="J5" s="164">
         <f>'Data Computation and Processing'!AC4*Conversion!$B$12</f>
-        <v>3072650856303.4453</v>
+        <v>3072650856303445</v>
       </c>
       <c r="K5" s="164">
         <f>'Data Computation and Processing'!AD4*Conversion!$B$12</f>
-        <v>3069195254713.0044</v>
+        <v>3069195254713004</v>
       </c>
       <c r="L5" s="164">
         <f>'Data Computation and Processing'!AE4*Conversion!$B$12</f>
-        <v>3065739653122.562</v>
+        <v>3065739653122562</v>
       </c>
       <c r="M5" s="164">
         <f>'Data Computation and Processing'!AF4*Conversion!$B$12</f>
-        <v>3062284051532.1211</v>
+        <v>3062284051532121</v>
       </c>
       <c r="N5" s="164">
         <f>'Data Computation and Processing'!AG4*Conversion!$B$12</f>
-        <v>3058828449941.6792</v>
+        <v>3058828449941679</v>
       </c>
       <c r="O5" s="164">
         <f>'Data Computation and Processing'!AH4*Conversion!$B$12</f>
-        <v>3055372848351.2383</v>
+        <v>3055372848351238</v>
       </c>
       <c r="P5" s="164">
         <f>'Data Computation and Processing'!AI4*Conversion!$B$12</f>
-        <v>3051917246760.7959</v>
+        <v>3051917246760796</v>
       </c>
       <c r="Q5" s="164">
         <f>'Data Computation and Processing'!AJ4*Conversion!$B$12</f>
-        <v>3048461645170.354</v>
+        <v>3048461645170354</v>
       </c>
       <c r="R5" s="164">
         <f>'Data Computation and Processing'!AK4*Conversion!$B$12</f>
-        <v>3045006043579.9131</v>
+        <v>3045006043579913</v>
       </c>
       <c r="S5" s="164">
         <f>'Data Computation and Processing'!AL4*Conversion!$B$12</f>
-        <v>3041550441989.4712</v>
+        <v>3041550441989471</v>
       </c>
       <c r="T5" s="164">
         <f>'Data Computation and Processing'!AM4*Conversion!$B$12</f>
-        <v>3038094840399.0298</v>
+        <v>3038094840399030</v>
       </c>
       <c r="U5" s="164">
         <f>'Data Computation and Processing'!AN4*Conversion!$B$12</f>
-        <v>3034639238808.5879</v>
+        <v>3034639238808588</v>
       </c>
       <c r="V5" s="164">
         <f>'Data Computation and Processing'!AO4*Conversion!$B$12</f>
-        <v>3031183637218.147</v>
+        <v>3031183637218147</v>
       </c>
       <c r="W5" s="164">
         <f>'Data Computation and Processing'!AP4*Conversion!$B$12</f>
-        <v>3027728035627.7051</v>
+        <v>3027728035627705</v>
       </c>
       <c r="X5" s="164">
         <f>'Data Computation and Processing'!AQ4*Conversion!$B$12</f>
-        <v>3024272434037.2637</v>
+        <v>3024272434037264</v>
       </c>
       <c r="Y5" s="164">
         <f>'Data Computation and Processing'!AR4*Conversion!$B$12</f>
-        <v>3020816832446.8218</v>
+        <v>3020816832446822</v>
       </c>
       <c r="Z5" s="164">
         <f>'Data Computation and Processing'!AS4*Conversion!$B$12</f>
-        <v>3017361230856.3809</v>
+        <v>3017361230856381</v>
       </c>
       <c r="AA5" s="164">
         <f>'Data Computation and Processing'!AT4*Conversion!$B$12</f>
-        <v>3013905629265.939</v>
+        <v>3013905629265939</v>
       </c>
       <c r="AB5" s="164">
         <f>'Data Computation and Processing'!AU4*Conversion!$B$12</f>
-        <v>3010450027675.4976</v>
+        <v>3010450027675498</v>
       </c>
       <c r="AC5" s="164">
         <f>'Data Computation and Processing'!AV4*Conversion!$B$12</f>
-        <v>3006994426085.0557</v>
+        <v>3006994426085056</v>
       </c>
       <c r="AD5" s="164">
         <f>'Data Computation and Processing'!AW4*Conversion!$B$12</f>
-        <v>3003538824494.6147</v>
+        <v>3003538824494615</v>
       </c>
       <c r="AE5" s="164">
         <f>'Data Computation and Processing'!AX4*Conversion!$B$12</f>
-        <v>3000083222904.1729</v>
+        <v>3000083222904172.5</v>
       </c>
       <c r="AF5" s="164">
         <f>'Data Computation and Processing'!AY4*Conversion!$B$12</f>
-        <v>2996627621313.731</v>
+        <v>2996627621313730.5</v>
       </c>
       <c r="AG5" s="164">
         <f>'Data Computation and Processing'!AZ4*Conversion!$B$12</f>
-        <v>2993172019723.2896</v>
+        <v>2993172019723289.5</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -24072,7 +24072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -24173,7 +24173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -24274,7 +24274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -24375,7 +24375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="V11" s="164">
         <f>'Data Computation and Processing'!AO10*Conversion!$B$14</f>
-        <v>424952429004.32812</v>
+        <v>424952429004.32813</v>
       </c>
       <c r="W11" s="164">
         <f>'Data Computation and Processing'!AP10*Conversion!$B$14</f>
@@ -24509,7 +24509,7 @@
       </c>
       <c r="AH11" s="3"/>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -24643,7 +24643,7 @@
       </c>
       <c r="AH12" s="3"/>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -24745,7 +24745,7 @@
       </c>
       <c r="AH13" s="3"/>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="AH14" s="3"/>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -25013,7 +25013,7 @@
       </c>
       <c r="AH15" s="3"/>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -25115,7 +25115,7 @@
       </c>
       <c r="AH16" s="3"/>
     </row>
-    <row r="17" spans="1:34">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="AH17" s="3"/>
     </row>
-    <row r="18" spans="1:34">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -25319,7 +25319,7 @@
       </c>
       <c r="AH18" s="3"/>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -25453,7 +25453,7 @@
       </c>
       <c r="AH19" s="3"/>
     </row>
-    <row r="20" spans="1:34">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -25587,7 +25587,7 @@
       </c>
       <c r="AH20" s="3"/>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P21" s="164">
         <f>'Data Computation and Processing'!AI20*Conversion!$B$16</f>
-        <v>110524569519487.62</v>
+        <v>110524569519487.63</v>
       </c>
       <c r="Q21" s="164">
         <f>'Data Computation and Processing'!AJ20*Conversion!$B$16</f>
@@ -25705,7 +25705,7 @@
       </c>
       <c r="AD21" s="164">
         <f>'Data Computation and Processing'!AW20*Conversion!$B$16</f>
-        <v>116655864572590.12</v>
+        <v>116655864572590.13</v>
       </c>
       <c r="AE21" s="164">
         <f>'Data Computation and Processing'!AX20*Conversion!$B$16</f>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="AH21" s="3"/>
     </row>
-    <row r="22" spans="1:34">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="AH22" s="3"/>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -25925,7 +25925,7 @@
       </c>
       <c r="AH23" s="3"/>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.4">
       <c r="B24" s="165"/>
       <c r="C24" s="165"/>
       <c r="D24" s="165"/>
@@ -25960,7 +25960,7 @@
       <c r="AG24" s="165"/>
       <c r="AH24" s="3"/>
     </row>
-    <row r="25" spans="1:34">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.4">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -25995,7 +25995,7 @@
       <c r="AG25" s="3"/>
       <c r="AH25" s="3"/>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>55</v>
       </c>
@@ -26033,7 +26033,7 @@
       <c r="AG26" s="3"/>
       <c r="AH26" s="3"/>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -26135,7 +26135,7 @@
       </c>
       <c r="AH27" s="3"/>
     </row>
-    <row r="28" spans="1:34">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
@@ -26269,7 +26269,7 @@
       </c>
       <c r="AH28" s="3"/>
     </row>
-    <row r="29" spans="1:34">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>2</v>
       </c>
@@ -26403,141 +26403,141 @@
       </c>
       <c r="AH29" s="3"/>
     </row>
-    <row r="30" spans="1:34">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B30" s="164">
         <f>'Data Computation and Processing'!U29*Conversion!$B$12</f>
-        <v>161835607682.80524</v>
+        <v>161835607682805.22</v>
       </c>
       <c r="C30" s="164">
         <f>'Data Computation and Processing'!V29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="D30" s="164">
         <f>'Data Computation and Processing'!W29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="E30" s="164">
         <f>'Data Computation and Processing'!X29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="F30" s="164">
         <f>'Data Computation and Processing'!Y29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="G30" s="164">
         <f>'Data Computation and Processing'!Z29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="H30" s="164">
         <f>'Data Computation and Processing'!AA29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="I30" s="164">
         <f>'Data Computation and Processing'!AB29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="J30" s="164">
         <f>'Data Computation and Processing'!AC29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="K30" s="164">
         <f>'Data Computation and Processing'!AD29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="L30" s="164">
         <f>'Data Computation and Processing'!AE29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="M30" s="164">
         <f>'Data Computation and Processing'!AF29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="N30" s="164">
         <f>'Data Computation and Processing'!AG29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="O30" s="164">
         <f>'Data Computation and Processing'!AH29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="P30" s="164">
         <f>'Data Computation and Processing'!AI29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Q30" s="164">
         <f>'Data Computation and Processing'!AJ29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="R30" s="164">
         <f>'Data Computation and Processing'!AK29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="S30" s="164">
         <f>'Data Computation and Processing'!AL29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="T30" s="164">
         <f>'Data Computation and Processing'!AM29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="U30" s="164">
         <f>'Data Computation and Processing'!AN29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="V30" s="164">
         <f>'Data Computation and Processing'!AO29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="W30" s="164">
         <f>'Data Computation and Processing'!AP29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="X30" s="164">
         <f>'Data Computation and Processing'!AQ29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Y30" s="164">
         <f>'Data Computation and Processing'!AR29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Z30" s="164">
         <f>'Data Computation and Processing'!AS29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AA30" s="164">
         <f>'Data Computation and Processing'!AT29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AB30" s="164">
         <f>'Data Computation and Processing'!AU29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AC30" s="164">
         <f>'Data Computation and Processing'!AV29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AD30" s="164">
         <f>'Data Computation and Processing'!AW29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AE30" s="164">
         <f>'Data Computation and Processing'!AX29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AF30" s="164">
         <f>'Data Computation and Processing'!AY29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AG30" s="164">
         <f>'Data Computation and Processing'!AZ29*Conversion!$B$12</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AH30" s="3"/>
     </row>
-    <row r="31" spans="1:34">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="AH31" s="3"/>
     </row>
-    <row r="32" spans="1:34">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
@@ -26741,7 +26741,7 @@
       </c>
       <c r="AH32" s="3"/>
     </row>
-    <row r="33" spans="1:34">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -26843,7 +26843,7 @@
       </c>
       <c r="AH33" s="3"/>
     </row>
-    <row r="34" spans="1:34">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="AH34" s="3"/>
     </row>
-    <row r="35" spans="1:34">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>8</v>
       </c>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="AH35" s="3"/>
     </row>
-    <row r="36" spans="1:34">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>9</v>
       </c>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="AH36" s="3"/>
     </row>
-    <row r="37" spans="1:34">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>10</v>
       </c>
@@ -27315,7 +27315,7 @@
       </c>
       <c r="AH37" s="3"/>
     </row>
-    <row r="38" spans="1:34">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>11</v>
       </c>
@@ -27417,7 +27417,7 @@
       </c>
       <c r="AH38" s="3"/>
     </row>
-    <row r="39" spans="1:34">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
@@ -27551,7 +27551,7 @@
       </c>
       <c r="AH39" s="3"/>
     </row>
-    <row r="40" spans="1:34">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
@@ -27685,7 +27685,7 @@
       </c>
       <c r="AH40" s="3"/>
     </row>
-    <row r="41" spans="1:34">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="AH41" s="3"/>
     </row>
-    <row r="42" spans="1:34">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -27888,7 +27888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:34">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
@@ -28021,7 +28021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:34">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>17</v>
       </c>
@@ -28154,7 +28154,7 @@
         <v>41644100432.900337</v>
       </c>
     </row>
-    <row r="45" spans="1:34">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>18</v>
       </c>
@@ -28287,7 +28287,7 @@
         <v>5113500952.3809404</v>
       </c>
     </row>
-    <row r="46" spans="1:34">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -28420,7 +28420,7 @@
         <v>13893393080</v>
       </c>
     </row>
-    <row r="47" spans="1:34">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
         <v>20</v>
       </c>
@@ -28521,7 +28521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:34">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
@@ -28622,12 +28622,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:33">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:33">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
@@ -28728,7 +28728,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="53" spans="1:33">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>1</v>
       </c>
@@ -28861,7 +28861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>2</v>
       </c>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="I54" s="164">
         <f>'Data Computation and Processing'!AB53*Conversion!$B$13</f>
-        <v>187791097922324.62</v>
+        <v>187791097922324.63</v>
       </c>
       <c r="J54" s="164">
         <f>'Data Computation and Processing'!AC53*Conversion!$B$13</f>
@@ -28915,7 +28915,7 @@
       </c>
       <c r="N54" s="164">
         <f>'Data Computation and Processing'!AG53*Conversion!$B$13</f>
-        <v>232637373175367.12</v>
+        <v>232637373175367.13</v>
       </c>
       <c r="O54" s="164">
         <f>'Data Computation and Processing'!AH53*Conversion!$B$13</f>
@@ -28959,7 +28959,7 @@
       </c>
       <c r="Y54" s="164">
         <f>'Data Computation and Processing'!AR53*Conversion!$B$13</f>
-        <v>331299178732064.12</v>
+        <v>331299178732064.13</v>
       </c>
       <c r="Z54" s="164">
         <f>'Data Computation and Processing'!AS53*Conversion!$B$13</f>
@@ -28994,7 +28994,7 @@
         <v>403053219136936.88</v>
       </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
         <v>3</v>
       </c>
@@ -29127,7 +29127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:33">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
         <v>4</v>
       </c>
@@ -29228,7 +29228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
         <v>5</v>
       </c>
@@ -29329,7 +29329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:33">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>6</v>
       </c>
@@ -29430,7 +29430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:33">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>7</v>
       </c>
@@ -29531,7 +29531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:33">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
         <v>8</v>
       </c>
@@ -29632,7 +29632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:33">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>9</v>
       </c>
@@ -29765,7 +29765,7 @@
         <v>328527341125.54034</v>
       </c>
     </row>
-    <row r="62" spans="1:33">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>10</v>
       </c>
@@ -29898,7 +29898,7 @@
         <v>1465180432.9002044</v>
       </c>
     </row>
-    <row r="63" spans="1:33">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>11</v>
       </c>
@@ -29999,7 +29999,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:33">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>12</v>
       </c>
@@ -30132,7 +30132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:33">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>13</v>
       </c>
@@ -30265,7 +30265,7 @@
         <v>82096414480.519897</v>
       </c>
     </row>
-    <row r="66" spans="1:33">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>14</v>
       </c>
@@ -30366,7 +30366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:33">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>15</v>
       </c>
@@ -30467,7 +30467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:33">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>16</v>
       </c>
@@ -30568,7 +30568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:33">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>17</v>
       </c>
@@ -30701,7 +30701,7 @@
         <v>586102780086.57971</v>
       </c>
     </row>
-    <row r="70" spans="1:33">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
         <v>18</v>
       </c>
@@ -30834,7 +30834,7 @@
         <v>130256450.21654201</v>
       </c>
     </row>
-    <row r="71" spans="1:33">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -30880,7 +30880,7 @@
       </c>
       <c r="L71" s="164">
         <f>'Data Computation and Processing'!AE70*Conversion!$B$16</f>
-        <v>444290582369335.12</v>
+        <v>444290582369335.13</v>
       </c>
       <c r="M71" s="164">
         <f>'Data Computation and Processing'!AF70*Conversion!$B$16</f>
@@ -30916,7 +30916,7 @@
       </c>
       <c r="U71" s="164">
         <f>'Data Computation and Processing'!AN70*Conversion!$B$16</f>
-        <v>602714092872700.62</v>
+        <v>602714092872700.63</v>
       </c>
       <c r="V71" s="164">
         <f>'Data Computation and Processing'!AO70*Conversion!$B$16</f>
@@ -30924,7 +30924,7 @@
       </c>
       <c r="W71" s="164">
         <f>'Data Computation and Processing'!AP70*Conversion!$B$16</f>
-        <v>637919317429000.12</v>
+        <v>637919317429000.13</v>
       </c>
       <c r="X71" s="164">
         <f>'Data Computation and Processing'!AQ70*Conversion!$B$16</f>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="AB71" s="164">
         <f>'Data Computation and Processing'!AU70*Conversion!$B$16</f>
-        <v>725932378819760.62</v>
+        <v>725932378819760.63</v>
       </c>
       <c r="AC71" s="164">
         <f>'Data Computation and Processing'!AV70*Conversion!$B$16</f>
@@ -30960,14 +30960,14 @@
       </c>
       <c r="AF71" s="164">
         <f>'Data Computation and Processing'!AY70*Conversion!$B$16</f>
-        <v>796342827932365.62</v>
+        <v>796342827932365.63</v>
       </c>
       <c r="AG71" s="164">
         <f>'Data Computation and Processing'!AZ70*Conversion!$B$16</f>
         <v>813945440210521.25</v>
       </c>
     </row>
-    <row r="72" spans="1:33">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
         <v>20</v>
       </c>
@@ -31068,7 +31068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:33">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
         <v>21</v>
       </c>
@@ -31180,12 +31180,12 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AG23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="38" customFormat="1">
+    <row r="1" spans="1:33" s="38" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -31286,7 +31286,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -31552,140 +31552,140 @@
         <v>3.5355975202159352E+16</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="162">
         <f>BFPIaE!B5</f>
-        <v>2926774962240</v>
+        <v>2926774962240000</v>
       </c>
       <c r="C4" s="162">
         <f>BFPIaE!C5</f>
-        <v>2544648196080</v>
+        <v>2544648196080000</v>
       </c>
       <c r="D4" s="162">
         <f>BFPIaE!D5</f>
-        <v>3093384465846.0942</v>
+        <v>3093384465846094.5</v>
       </c>
       <c r="E4" s="162">
         <f>BFPIaE!E5</f>
-        <v>3089928864255.6533</v>
+        <v>3089928864255653.5</v>
       </c>
       <c r="F4" s="162">
         <f>BFPIaE!F5</f>
-        <v>3086473262665.2114</v>
+        <v>3086473262665211.5</v>
       </c>
       <c r="G4" s="162">
         <f>BFPIaE!G5</f>
-        <v>3083017661074.7705</v>
+        <v>3083017661074770.5</v>
       </c>
       <c r="H4" s="162">
         <f>BFPIaE!H5</f>
-        <v>3079562059484.3281</v>
+        <v>3079562059484328.5</v>
       </c>
       <c r="I4" s="162">
         <f>BFPIaE!I5</f>
-        <v>3076106457893.8872</v>
+        <v>3076106457893887.5</v>
       </c>
       <c r="J4" s="162">
         <f>BFPIaE!J5</f>
-        <v>3072650856303.4453</v>
+        <v>3072650856303445</v>
       </c>
       <c r="K4" s="162">
         <f>BFPIaE!K5</f>
-        <v>3069195254713.0044</v>
+        <v>3069195254713004</v>
       </c>
       <c r="L4" s="162">
         <f>BFPIaE!L5</f>
-        <v>3065739653122.562</v>
+        <v>3065739653122562</v>
       </c>
       <c r="M4" s="162">
         <f>BFPIaE!M5</f>
-        <v>3062284051532.1211</v>
+        <v>3062284051532121</v>
       </c>
       <c r="N4" s="162">
         <f>BFPIaE!N5</f>
-        <v>3058828449941.6792</v>
+        <v>3058828449941679</v>
       </c>
       <c r="O4" s="162">
         <f>BFPIaE!O5</f>
-        <v>3055372848351.2383</v>
+        <v>3055372848351238</v>
       </c>
       <c r="P4" s="162">
         <f>BFPIaE!P5</f>
-        <v>3051917246760.7959</v>
+        <v>3051917246760796</v>
       </c>
       <c r="Q4" s="162">
         <f>BFPIaE!Q5</f>
-        <v>3048461645170.354</v>
+        <v>3048461645170354</v>
       </c>
       <c r="R4" s="162">
         <f>BFPIaE!R5</f>
-        <v>3045006043579.9131</v>
+        <v>3045006043579913</v>
       </c>
       <c r="S4" s="162">
         <f>BFPIaE!S5</f>
-        <v>3041550441989.4712</v>
+        <v>3041550441989471</v>
       </c>
       <c r="T4" s="162">
         <f>BFPIaE!T5</f>
-        <v>3038094840399.0298</v>
+        <v>3038094840399030</v>
       </c>
       <c r="U4" s="162">
         <f>BFPIaE!U5</f>
-        <v>3034639238808.5879</v>
+        <v>3034639238808588</v>
       </c>
       <c r="V4" s="162">
         <f>BFPIaE!V5</f>
-        <v>3031183637218.147</v>
+        <v>3031183637218147</v>
       </c>
       <c r="W4" s="162">
         <f>BFPIaE!W5</f>
-        <v>3027728035627.7051</v>
+        <v>3027728035627705</v>
       </c>
       <c r="X4" s="162">
         <f>BFPIaE!X5</f>
-        <v>3024272434037.2637</v>
+        <v>3024272434037264</v>
       </c>
       <c r="Y4" s="162">
         <f>BFPIaE!Y5</f>
-        <v>3020816832446.8218</v>
+        <v>3020816832446822</v>
       </c>
       <c r="Z4" s="162">
         <f>BFPIaE!Z5</f>
-        <v>3017361230856.3809</v>
+        <v>3017361230856381</v>
       </c>
       <c r="AA4" s="162">
         <f>BFPIaE!AA5</f>
-        <v>3013905629265.939</v>
+        <v>3013905629265939</v>
       </c>
       <c r="AB4" s="162">
         <f>BFPIaE!AB5</f>
-        <v>3010450027675.4976</v>
+        <v>3010450027675498</v>
       </c>
       <c r="AC4" s="162">
         <f>BFPIaE!AC5</f>
-        <v>3006994426085.0557</v>
+        <v>3006994426085056</v>
       </c>
       <c r="AD4" s="162">
         <f>BFPIaE!AD5</f>
-        <v>3003538824494.6147</v>
+        <v>3003538824494615</v>
       </c>
       <c r="AE4" s="162">
         <f>BFPIaE!AE5</f>
-        <v>3000083222904.1729</v>
+        <v>3000083222904172.5</v>
       </c>
       <c r="AF4" s="162">
         <f>BFPIaE!AF5</f>
-        <v>2996627621313.731</v>
+        <v>2996627621313730.5</v>
       </c>
       <c r="AG4" s="162">
         <f>BFPIaE!AG5</f>
-        <v>2993172019723.2896</v>
+        <v>2993172019723289.5</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -31818,7 +31818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -31951,7 +31951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -32084,7 +32084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -32217,7 +32217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -32350,7 +32350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -32436,7 +32436,7 @@
       </c>
       <c r="V10" s="162">
         <f>BFPIaE!V11</f>
-        <v>424952429004.32812</v>
+        <v>424952429004.32813</v>
       </c>
       <c r="W10" s="162">
         <f>BFPIaE!W11</f>
@@ -32483,7 +32483,7 @@
         <v>560975271861.47253</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -32616,7 +32616,7 @@
         <v>1128856636363.6367</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -32749,7 +32749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
@@ -32882,7 +32882,7 @@
         <v>1018580204438.1804</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -33015,7 +33015,7 @@
         <v>56971544896.544769</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
@@ -33148,7 +33148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -33281,7 +33281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -33414,7 +33414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -33547,7 +33547,7 @@
         <v>56857799220.77507</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
@@ -33680,7 +33680,7 @@
         <v>4252291341.9905119</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="P20" s="162">
         <f>BFPIaE!P21</f>
-        <v>110524569519487.62</v>
+        <v>110524569519487.63</v>
       </c>
       <c r="Q20" s="162">
         <f>BFPIaE!Q21</f>
@@ -33798,7 +33798,7 @@
       </c>
       <c r="AD20" s="162">
         <f>BFPIaE!AD21</f>
-        <v>116655864572590.12</v>
+        <v>116655864572590.13</v>
       </c>
       <c r="AE20" s="162">
         <f>BFPIaE!AE21</f>
@@ -33813,7 +33813,7 @@
         <v>117969713512540.53</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
@@ -33946,7 +33946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -34079,7 +34079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B23" s="162"/>
       <c r="C23" s="162"/>
       <c r="D23" s="162"/>
@@ -34124,12 +34124,12 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AG24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -34230,7 +34230,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -34363,7 +34363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -34397,7 +34397,7 @@
       </c>
       <c r="I3" s="163">
         <f>BFPIaE!I54</f>
-        <v>187791097922324.62</v>
+        <v>187791097922324.63</v>
       </c>
       <c r="J3" s="163">
         <f>BFPIaE!J54</f>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="N3" s="163">
         <f>BFPIaE!N54</f>
-        <v>232637373175367.12</v>
+        <v>232637373175367.13</v>
       </c>
       <c r="O3" s="163">
         <f>BFPIaE!O54</f>
@@ -34461,7 +34461,7 @@
       </c>
       <c r="Y3" s="163">
         <f>BFPIaE!Y54</f>
-        <v>331299178732064.12</v>
+        <v>331299178732064.13</v>
       </c>
       <c r="Z3" s="163">
         <f>BFPIaE!Z54</f>
@@ -34496,7 +34496,7 @@
         <v>403053219136936.88</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -34629,7 +34629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -34762,7 +34762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -34895,7 +34895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -35028,7 +35028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -35161,7 +35161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -35294,7 +35294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -35427,7 +35427,7 @@
         <v>328527341125.54034</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -35560,7 +35560,7 @@
         <v>1465180432.9002044</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -35693,7 +35693,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -35826,7 +35826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -35959,7 +35959,7 @@
         <v>82096414480.519897</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -36092,7 +36092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -36225,7 +36225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -36358,7 +36358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -36491,7 +36491,7 @@
         <v>586102780086.57971</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -36624,7 +36624,7 @@
         <v>130256450.21654201</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -36670,7 +36670,7 @@
       </c>
       <c r="L20" s="163">
         <f>BFPIaE!L71</f>
-        <v>444290582369335.12</v>
+        <v>444290582369335.13</v>
       </c>
       <c r="M20" s="163">
         <f>BFPIaE!M71</f>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="U20" s="163">
         <f>BFPIaE!U71</f>
-        <v>602714092872700.62</v>
+        <v>602714092872700.63</v>
       </c>
       <c r="V20" s="163">
         <f>BFPIaE!V71</f>
@@ -36714,7 +36714,7 @@
       </c>
       <c r="W20" s="163">
         <f>BFPIaE!W71</f>
-        <v>637919317429000.12</v>
+        <v>637919317429000.13</v>
       </c>
       <c r="X20" s="163">
         <f>BFPIaE!X71</f>
@@ -36734,7 +36734,7 @@
       </c>
       <c r="AB20" s="163">
         <f>BFPIaE!AB71</f>
-        <v>725932378819760.62</v>
+        <v>725932378819760.63</v>
       </c>
       <c r="AC20" s="163">
         <f>BFPIaE!AC71</f>
@@ -36750,14 +36750,14 @@
       </c>
       <c r="AF20" s="163">
         <f>BFPIaE!AF71</f>
-        <v>796342827932365.62</v>
+        <v>796342827932365.63</v>
       </c>
       <c r="AG20" s="163">
         <f>BFPIaE!AG71</f>
         <v>813945440210521.25</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -36890,7 +36890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -37023,7 +37023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B23" s="163"/>
       <c r="C23" s="163"/>
       <c r="D23" s="163"/>
@@ -37057,7 +37057,7 @@
       <c r="AF23" s="163"/>
       <c r="AG23" s="163"/>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B24" s="163"/>
       <c r="C24" s="163"/>
       <c r="D24" s="163"/>
@@ -37102,12 +37102,12 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:AG23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -37208,7 +37208,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -37341,7 +37341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -37474,140 +37474,140 @@
         <v>2.5340899115575584E+16</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="163">
         <f>BFPIaE!B30</f>
-        <v>161835607682.80524</v>
+        <v>161835607682805.22</v>
       </c>
       <c r="C4" s="163">
         <f>BFPIaE!C30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="D4" s="163">
         <f>BFPIaE!D30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="E4" s="163">
         <f>BFPIaE!E30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="F4" s="163">
         <f>BFPIaE!F30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="G4" s="163">
         <f>BFPIaE!G30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="H4" s="163">
         <f>BFPIaE!H30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="I4" s="163">
         <f>BFPIaE!I30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="J4" s="163">
         <f>BFPIaE!J30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="K4" s="163">
         <f>BFPIaE!K30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="L4" s="163">
         <f>BFPIaE!L30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="M4" s="163">
         <f>BFPIaE!M30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="N4" s="163">
         <f>BFPIaE!N30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="O4" s="163">
         <f>BFPIaE!O30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="P4" s="163">
         <f>BFPIaE!P30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Q4" s="163">
         <f>BFPIaE!Q30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="R4" s="163">
         <f>BFPIaE!R30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="S4" s="163">
         <f>BFPIaE!S30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="T4" s="163">
         <f>BFPIaE!T30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="U4" s="163">
         <f>BFPIaE!U30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="V4" s="163">
         <f>BFPIaE!V30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="W4" s="163">
         <f>BFPIaE!W30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="X4" s="163">
         <f>BFPIaE!X30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Y4" s="163">
         <f>BFPIaE!Y30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="Z4" s="163">
         <f>BFPIaE!Z30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AA4" s="163">
         <f>BFPIaE!AA30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AB4" s="163">
         <f>BFPIaE!AB30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AC4" s="163">
         <f>BFPIaE!AC30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AD4" s="163">
         <f>BFPIaE!AD30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AE4" s="163">
         <f>BFPIaE!AE30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AF4" s="163">
         <f>BFPIaE!AF30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
       <c r="AG4" s="163">
         <f>BFPIaE!AG30</f>
-        <v>151985730275.88763</v>
+        <v>151985730275887.63</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -37740,7 +37740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -37873,7 +37873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -38006,7 +38006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -38139,7 +38139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -38272,7 +38272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -38405,7 +38405,7 @@
         <v>367418701.29870152</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -38538,7 +38538,7 @@
         <v>1648505627.7056284</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -38671,7 +38671,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -38804,7 +38804,7 @@
         <v>543812007.27304566</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -38937,7 +38937,7 @@
         <v>113918718561.81731</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -39070,7 +39070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -39203,7 +39203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -39336,7 +39336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -39469,7 +39469,7 @@
         <v>41644100432.900337</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -39602,7 +39602,7 @@
         <v>5113500952.3809404</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -39735,7 +39735,7 @@
         <v>13893393080</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -39868,7 +39868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -40001,7 +40001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.4">
       <c r="B23" s="163"/>
       <c r="C23" s="163"/>
       <c r="D23" s="163"/>
